--- a/workspaces/nasdaq_hourly_24hrs/vix/vix_ret_5.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/vix/vix_ret_5.xlsx
@@ -625,76 +625,76 @@
         <v>29</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.335547039470356</v>
+        <v>8.368660142892317</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.154077444094845</v>
+        <v>1.187536436521917</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.00341397400739</v>
+        <v>10.03862072438853</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.413196718873536</v>
+        <v>-4.377253540871195</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.078989523144003</v>
+        <v>2.144299134104635</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.163829230598367</v>
+        <v>-1.098718957707156</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.928460886536953</v>
+        <v>4.994541178110516</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.210035818922812</v>
+        <v>-2.143638469072819</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.169324899703923</v>
+        <v>-2.102935046900377</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.94056317652197</v>
+        <v>-2.873240299829938</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.636314052294239</v>
+        <v>7.703409861701964</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.924751496659958</v>
+        <v>3.99219204992697</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.678752914418091</v>
+        <v>9.747560690660059</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.023146693210727</v>
+        <v>6.09223571556241</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5.367920121964922</v>
+        <v>5.437811532235806</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>2.523290827334328</v>
+        <v>2.5925217758762</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.39030699470549</v>
+        <v>2.459733966831003</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>5.728347603308691</v>
+        <v>5.797944588921837</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.945968229011903</v>
+        <v>6.015353257400442</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.753583827584194</v>
+        <v>-0.6843872905113244</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-1.296464053045504</v>
+        <v>-1.226593054084645</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-1.372775037891159</v>
+        <v>-1.302773079420191</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-1.098384794638299</v>
+        <v>-1.02866132969573</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-1.174631982255271</v>
+        <v>-1.104777634547219</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>17.1713951766783</v>
+        <v>17.20458133829161</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.026781770015155</v>
+        <v>4.060260312887394</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>18.62344875669048</v>
+        <v>18.65872081317199</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>24.3333278187822</v>
+        <v>24.36947732999329</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.35481264391261</v>
+        <v>14.4202017687785</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>14.54553137673349</v>
+        <v>14.61073899253097</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>23.40856223458896</v>
+        <v>23.47475310134335</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>19.92928589457722</v>
+        <v>19.99580732283233</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>23.18783716913252</v>
+        <v>23.25436116739806</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>25.63645131355917</v>
+        <v>25.70391582591145</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>19.49096873296062</v>
+        <v>19.55811782573712</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.79087906090443</v>
+        <v>12.85835497755433</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11.67369868211133</v>
+        <v>11.74251178233288</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.240747502057268</v>
+        <v>8.309841685208639</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>7.586261410592094</v>
+        <v>7.656157348143672</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.746419005793847</v>
+        <v>1.815644860262879</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>8.051118051961481</v>
+        <v>8.120557182963822</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>4.728864376863129</v>
+        <v>4.798457288982746</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-1.495602398058772</v>
+        <v>-1.426232646986456</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.530952403832735</v>
+        <v>-4.461763030150919</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-5.074975273734026</v>
+        <v>-5.005109683939139</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.928597653643948</v>
+        <v>-1.858596919073214</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.654383533913695</v>
+        <v>-1.584660678802194</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.49500094321899</v>
+        <v>1.564855290925536</v>
       </c>
     </row>
     <row r="8">
@@ -789,2208 +789,2208 @@
         <v>40</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.760575867210655</v>
+        <v>8.793690550738233</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>28.29714945270069</v>
+        <v>28.33082562934044</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14.4542242926627</v>
+        <v>14.48946481635395</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.26542347544531</v>
+        <v>11.30147752291792</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.934501462287386</v>
+        <v>5.999826383946569</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.122717753724203</v>
+        <v>6.187864577189757</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12.81618865836278</v>
+        <v>12.88231052146003</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.05645750109713</v>
+        <v>10.12291729822441</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.612321462401823</v>
+        <v>7.678756171036568</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.354867632197902</v>
+        <v>4.422219090256668</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.629424832248418</v>
+        <v>4.696499196816262</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.35329088656492</v>
+        <v>4.420725581744868</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.725235924243911</v>
+        <v>5.79402130418493</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.998988778906998</v>
+        <v>8.068078740388515</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>7.344525374617554</v>
+        <v>7.414417362284645</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.446871104331585</v>
+        <v>5.516104645286561</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>7.80931830194811</v>
+        <v>7.878754425710511</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>12.69780632791125</v>
+        <v>12.7674149803008</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>12.91772191422135</v>
+        <v>12.98711648390407</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>8.114871405189774</v>
+        <v>8.184077761841834</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>7.574722782467525</v>
+        <v>7.644601076176279</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.002638369934196</v>
+        <v>5.072643347349377</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>7.778204938604482</v>
+        <v>7.847930866839832</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.204678362573667</v>
+        <v>5.274532710280944</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.09696</t>
+          <t>X ≈ -0.09698</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.978711976372061</v>
+        <v>2.013370687658785</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.566106662134111</v>
+        <v>8.601240189866054</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>11.69800024723889</v>
+        <v>11.73491413530243</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.639924207672443</v>
+        <v>8.677705866311726</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.949691397036716</v>
+        <v>6.018215520257996</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.831735191012172</v>
+        <v>3.900059692981415</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.666024781648396</v>
+        <v>7.735340480950619</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.367486655720185</v>
+        <v>7.437190173808588</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.780931485048534</v>
+        <v>2.85060117462195</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.2915909109892</v>
+        <v>4.362250495495118</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.371708435896885</v>
+        <v>-2.301371568311744</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-11.94145094567268</v>
+        <v>-11.87076222315623</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.429183357109494</v>
+        <v>-10.72195692129799</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.969696240920229</v>
+        <v>-8.637978851025494</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-6.628393099363052</v>
+        <v>-9.329319534745501</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-6.036439212384025</v>
+        <v>-8.716631171018562</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-10.81322716583036</v>
+        <v>-12.12113205153429</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.957663037612591</v>
+        <v>-3.888095125566693</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-6.064797921229122</v>
+        <v>-5.995441817733145</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-5.879542333322696</v>
+        <v>-5.810359385781474</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-6.423977018267301</v>
+        <v>-6.354116342511688</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-6.50188902406984</v>
+        <v>-6.431893951085719</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.7454543195367975</v>
+        <v>0.8151770878366094</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.655786753707034</v>
+        <v>-1.585932405999223</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.08529</t>
+          <t>X ≈ -0.08533</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>57</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.416886473556183</v>
+        <v>9.450014781205049</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>16.05936915061387</v>
+        <v>16.09295577765467</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.401337551443604</v>
+        <v>9.43655016504993</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.20719394005021</v>
+        <v>5.243214970339466</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.590828989672708</v>
+        <v>6.656178993265705</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2024561457756207</v>
+        <v>-0.1373288737718497</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.519359862506889</v>
+        <v>2.585441016782774</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.990899294637913</v>
+        <v>4.05734796306033</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.28676532441721</v>
+        <v>2.35319610097158</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.726439243772283</v>
+        <v>-3.659100269211841</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.453900580559981</v>
+        <v>-3.38683545109707</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2346493583878768</v>
+        <v>-0.1672061445109705</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.141570701640163</v>
+        <v>2.211228941701641</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.669731284411327</v>
+        <v>3.741511774427899</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.26471576351917</v>
+        <v>1.33573338286859</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.640798326238723</v>
+        <v>-1.572365978509723</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>6.97736832279989</v>
+        <v>7.049147547205052</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1295863498850665</v>
+        <v>-0.06001401866236478</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.665143564280157</v>
+        <v>-1.595782891745536</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.2736101440065966</v>
+        <v>0.3427995752726218</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.021624325226519</v>
+        <v>-1.951760968323867</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-3.851471397081937</v>
+        <v>-3.781475949619562</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.577945782286669</v>
+        <v>-3.508225461001309</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-5.409356725145798</v>
+        <v>-5.339502377438919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.07361</t>
+          <t>X ≈ -0.07367</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>99</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8.885492278410446</v>
+        <v>8.918612862987843</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.529391928668097</v>
+        <v>1.562857064728881</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.11480984471558</v>
+        <v>4.149976433577628</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6081219539890057</v>
+        <v>-0.5721522395938763</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.051167299807588</v>
+        <v>4.116485008137481</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2205305642600806</v>
+        <v>0.2856431940334119</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.554969191142774</v>
+        <v>-1.488928954253296</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.831341519402329</v>
+        <v>-1.764940993437449</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.807429324273599</v>
+        <v>-4.741051320214105</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.560812942161967</v>
+        <v>-2.493483414142744</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.7314166776961173</v>
+        <v>0.7984875338733701</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.593366702295192</v>
+        <v>-6.525962365657222</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.708055295849867</v>
+        <v>-6.641292964894149</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.921993422402217</v>
+        <v>-5.8563967627422</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-7.587630803516277</v>
+        <v>-7.522388161346733</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.95876077942755</v>
+        <v>-1.890586801006073</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.085741084942065</v>
+        <v>-1.016509841260536</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1826727852067265</v>
+        <v>-0.1131076893553811</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.98348967694082</v>
+        <v>-1.914135943150626</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.797063023833303</v>
+        <v>-1.727881863702486</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-3.34930323691168</v>
+        <v>-3.279445457849306</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-3.426325312974733</v>
+        <v>-3.356332224968547</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.152724167988829</v>
+        <v>-3.083005011316843</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1993620414673103</v>
+        <v>-0.1295076937597983</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06193</t>
+          <t>X ≈ -0.062</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>130</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12.38266673117336</v>
+        <v>12.41581669618211</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.178263503340339</v>
+        <v>5.211748280879291</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.09924441204349</v>
+        <v>9.134443976292225</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.102535567668362</v>
+        <v>6.138544281801707</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.505618939517952</v>
+        <v>6.570931295461122</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.719432606249384</v>
+        <v>-1.654362239664813</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1941911691557578</v>
+        <v>-0.1281691857003935</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2956277965184597</v>
+        <v>0.3620155385110166</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.635569847613944</v>
+        <v>2.701965505962839</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.930386209852472</v>
+        <v>4.997733725489084</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.139919641600358</v>
+        <v>2.206978225018098</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.397330441649594</v>
+        <v>3.464758452973484</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.575776622564078</v>
+        <v>4.646265797715067</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.354978605669857</v>
+        <v>4.427351030232408</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.700113283089109</v>
+        <v>3.772734192583563</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.075044637290489</v>
+        <v>-1.006359362963892</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.627306682909435</v>
+        <v>2.69779202484672</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.058760689318966</v>
+        <v>4.128326252593197</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>6.58013961485063</v>
+        <v>6.649503204538782</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.160385295886812</v>
+        <v>2.229565718626006</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.387087296783676</v>
+        <v>2.45694662370164</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.080650420002776</v>
+        <v>3.150645256685216</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.818455066399977</v>
+        <v>1.8881744027127</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.5645524066576684</v>
+        <v>-0.4946980589507461</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05026</t>
+          <t>X ≈ -0.05034</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>177</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12.88079472607917</v>
+        <v>12.91395214193256</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.507571648546197</v>
+        <v>7.541067130561274</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.56784802793797</v>
+        <v>10.60305601958239</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.744491902686129</v>
+        <v>8.780512063260247</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.137995958674075</v>
+        <v>6.203271925749988</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.522261072642486</v>
+        <v>3.587329848229501</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.05626908317913148</v>
+        <v>0.009713386231652521</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.602882002671713</v>
+        <v>3.669256279642461</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.083893059042225</v>
+        <v>3.150259420563799</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.751935149213352</v>
+        <v>1.819234989975953</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.277133803915106</v>
+        <v>4.344176587026034</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.439318877266473</v>
+        <v>3.506721940428335</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.006685464249252</v>
+        <v>4.077133643943853</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.785949829100687</v>
+        <v>3.858253487398855</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>6.510064063012145</v>
+        <v>6.585028304024441</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>7.669803780835771</v>
+        <v>7.744806680062396</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.847304319085339</v>
+        <v>5.919075956915208</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>4.61713005925742</v>
+        <v>4.686682540442035</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.143123057772449</v>
+        <v>3.212466381508698</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.152474380096621</v>
+        <v>6.221652397145817</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>4.483609766825303</v>
+        <v>4.55346419025512</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>3.280180640515859</v>
+        <v>3.350170346679739</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.556125340998236</v>
+        <v>3.625842804195628</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.786599266527901</v>
+        <v>1.856453614235313</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.03859</t>
+          <t>X ≈ -0.03868</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.024930743449254</v>
+        <v>8.882471978982096</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.052282644937684</v>
+        <v>2.883155209628825</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.7360936591244851</v>
+        <v>-0.914883226739164</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.858623545512501</v>
+        <v>-3.043443587053623</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.281893128486537</v>
+        <v>-2.432874606978622</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.978665079825184</v>
+        <v>-4.138919882246562</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.280941879808076</v>
+        <v>-4.438106209969725</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.032188316436887</v>
+        <v>-5.191323049542838</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.105504631191408</v>
+        <v>-3.255722242465964</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.880554088667374</v>
+        <v>-4.029926989792443</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.662983715842472</v>
+        <v>-2.808192136460143</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.77887386050125</v>
+        <v>1.656460985572153</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6534414971787186</v>
+        <v>0.5328103182055344</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.9848883109434396</v>
+        <v>-1.1128084267201</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.8919992814735593</v>
+        <v>-1.29763962083792</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.6464662728311694</v>
+        <v>0.248288875362519</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>1.93030656598178</v>
+        <v>1.540635955984477</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>4.190643212615356</v>
+        <v>3.811957663993162</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.354768493716783</v>
+        <v>5.257427890508644</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5.544204289568555</v>
+        <v>5.446628954106629</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>5.477732020469084</v>
+        <v>5.383026141741432</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.877684000294984</v>
+        <v>5.785307562350347</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>8.049820036255618</v>
+        <v>7.966133996674827</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>7.977190210914337</v>
+        <v>7.893580329327996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.02691</t>
+          <t>X ≈ -0.02701</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.360651337847166</v>
+        <v>3.600772394585569</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>8.081762237469157</v>
+        <v>7.97860405323641</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.118952282327491</v>
+        <v>4.008085999170241</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.32337459455178</v>
+        <v>2.571796649566132</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.236741432987593</v>
+        <v>1.874841921160794</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.870009763447264</v>
+        <v>2.787702519414879</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.0728677262197408</v>
+        <v>-0.1622707535040675</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.3520482161088836</v>
+        <v>-0.4411588255570607</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4137909865726712</v>
+        <v>0.6906231242766481</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.897341914954701</v>
+        <v>2.823606604429656</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.828903944451156</v>
+        <v>4.919356378872131</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.309549366652163</v>
+        <v>3.186018871931005</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.188505527059988</v>
+        <v>2.060418361741604</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.865923699906979</v>
+        <v>4.752170440658361</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4.571846518506057</v>
+        <v>4.670871442501088</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>5.529604241956328</v>
+        <v>5.844364468502661</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.034863418346617</v>
+        <v>5.345593935656282</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.932261618996876</v>
+        <v>5.240405456251196</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.06248037456637</v>
+        <v>4.363562471384007</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.436897749608512</v>
+        <v>2.731278767356891</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.712111873322655</v>
+        <v>4.013904040938854</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>4.728134815447866</v>
+        <v>5.034147627274272</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>5.732167864466497</v>
+        <v>6.040666871535592</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.477405635300364</v>
+        <v>3.778182345316871</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01523</t>
+          <t>X ≈ -0.01535</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9363887566995146</v>
+        <v>1.416881935872546</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.02942632987301863</v>
+        <v>0.5088931345301972</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8286293195378818</v>
+        <v>-0.6350702266099688</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.213960210124419</v>
+        <v>0.971944895397904</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.296389638263307</v>
+        <v>0.637890647884511</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.202380307657791</v>
+        <v>1.116075861402031</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.459043482887104</v>
+        <v>2.374830781837517</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.028449436762422</v>
+        <v>1.100725075930384</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3758860966635638</v>
+        <v>-0.7245347302048728</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5890708053432618</v>
+        <v>0.8268265432343398</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.876098997706471</v>
+        <v>-0.6433913934641708</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5837144355310144</v>
+        <v>0.5330296197285662</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.621119871652553</v>
+        <v>0.5763510530181861</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.7575742153370939</v>
+        <v>-0.8068854382726443</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.545186585660133</v>
+        <v>-0.590830820312334</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2420045112084921</v>
+        <v>-0.2890683193422205</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.9557546903384306</v>
+        <v>-1.005362933126641</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.060713690806857</v>
+        <v>-1.110663055370033</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.133884632729362</v>
+        <v>-1.185558421729695</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.816273932494958</v>
+        <v>-1.870700441543818</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.487812929374897</v>
+        <v>-1.539055587844764</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.144718727507367</v>
+        <v>-2.197552241204257</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.579985727356309</v>
+        <v>-1.632275505794496</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-3.109275125798931</v>
+        <v>-2.874155336366854</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.003559</t>
+          <t>X ≈ -0.003682</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>377</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.611148272483547</v>
+        <v>-5.104148177485961</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.618546265009371</v>
+        <v>-3.848271595572129</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.623539486625106</v>
+        <v>-1.32551370169827</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.097140356920342</v>
+        <v>1.13583140631355</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.05292108510629845</v>
+        <v>0.2791015162383914</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.433237637145702</v>
+        <v>-0.8413744905267748</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3575154303479806</v>
+        <v>0.2369944177280203</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3670443433493986</v>
+        <v>0.2266760706108641</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3246473463564072</v>
+        <v>0.5323735405124594</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.749741621518055</v>
+        <v>1.344243314672639</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2977638556079398</v>
+        <v>0.033626119387975</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.04701693313450761</v>
+        <v>0.5503207376718962</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6386258583072646</v>
+        <v>-0.3036379313905329</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.440989038561511</v>
+        <v>-2.109523834018269</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.4589281097457203</v>
+        <v>-0.1215425164108552</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.186428515602785</v>
+        <v>-0.851649124258266</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.057178911396534</v>
+        <v>-0.7220145879330957</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.483281719030359</v>
+        <v>-2.14949665164341</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-3.060135989101816</v>
+        <v>-2.72661759777408</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.079022321728083</v>
+        <v>-1.745458918623214</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-3.680260370437303</v>
+        <v>-3.34582045660251</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.963028655405445</v>
+        <v>-2.62822555064411</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.54523852887602</v>
+        <v>-4.475570394965295</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.705135961034387</v>
+        <v>-1.900533602716969</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.008115</t>
+          <t>X ≈ 0.00798</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.108488728817548</v>
+        <v>2.074946663162379</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.00569788512617464</v>
+        <v>0.08863525837188035</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.2266143414591895</v>
+        <v>-0.4296968444624909</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.418314556099446</v>
+        <v>-1.731948295785223</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.374047680163251</v>
+        <v>-2.968966908754645</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1053615328426858</v>
+        <v>-0.0517841530838794</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.62025770681069</v>
+        <v>2.508765113013737</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.245609818463961</v>
+        <v>2.839178887428758</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.796300454267019</v>
+        <v>1.973054001227851</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.520653451837084</v>
+        <v>2.7169439247429</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.895967037816234</v>
+        <v>1.781322561224329</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.019860139084571</v>
+        <v>0.899702080149801</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.09597712917985</v>
+        <v>1.298123270272036</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.2785476397558782</v>
+        <v>0.4720225027662011</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.415592050040289</v>
+        <v>1.637178851857414</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>2.011630396902675</v>
+        <v>2.231403494137311</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.347713108566168</v>
+        <v>2.401264149823987</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.247117958009916</v>
+        <v>2.600314834431231</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.068188459734237</v>
+        <v>3.424021448145254</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>5.361716135390324</v>
+        <v>5.743999364325333</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>5.427680102249731</v>
+        <v>5.988252905530196</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>5.055831579313711</v>
+        <v>5.308995508054487</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.228702112988721</v>
+        <v>4.06544123849541</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.758895230042981</v>
+        <v>4.603801002963301</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.01979</t>
+          <t>X ≈ 0.01964</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.068369617097552</v>
+        <v>-4.404400119023705</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.755521704762565</v>
+        <v>-5.077539769102216</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-7.662420155583703</v>
+        <v>-7.585549682387928</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.940560646759053</v>
+        <v>-5.024165184325263</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.670037011066576</v>
+        <v>-5.353869062634075</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.26520696674492</v>
+        <v>-2.621273650594617</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.4086109110116</v>
+        <v>-4.121410477645782</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.906779014001401</v>
+        <v>-6.211707683798231</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.647017536856595</v>
+        <v>-4.715819047482071</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.198019422702174</v>
+        <v>-3.311831316613819</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.29415584069524</v>
+        <v>-3.038277061290096</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.090927805949718</v>
+        <v>-1.858483076620878</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.440937118489288</v>
+        <v>-5.168766775122556</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5850606049503284</v>
+        <v>-1.376527276345648</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.8729873621987636</v>
+        <v>-1.669421648083997</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.033199973896181</v>
+        <v>-3.995721425741557</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.427347799878426</v>
+        <v>-3.399102337295012</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.273130291417218</v>
+        <v>-4.59934445498898</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-4.171158789207858</v>
+        <v>-5.113797430791941</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-5.100887995388511</v>
+        <v>-6.183338962900478</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.827678701155911</v>
+        <v>-4.166278869915551</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.15971523961187</v>
+        <v>-3.147249639059254</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.747873670210467</v>
+        <v>-5.068428325086678</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-4.571441040411976</v>
+        <v>-5.879313443565735</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.03147</t>
+          <t>X ≈ 0.03131</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>194</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-8.042046987331837</v>
+        <v>-7.499891309900946</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.806744146708311</v>
+        <v>-5.772661517765108</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.665458519568034</v>
+        <v>-4.14024799859866</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.381531038047839</v>
+        <v>-4.836111772219375</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-8.786034274768397</v>
+        <v>-8.729409786638179</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-9.109088611530872</v>
+        <v>-9.054712557759366</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-9.89284295444439</v>
+        <v>-9.326064656844174</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-7.325737898688601</v>
+        <v>-7.044291997837959</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.249396412779269</v>
+        <v>-4.449476235094103</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.061270747638254</v>
+        <v>-6.253011698237131</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.720751675103145</v>
+        <v>-2.911243489004001</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.041664947253309</v>
+        <v>-4.954223967839802</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.105467658827344</v>
+        <v>-4.018957326194219</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.837279312030454</v>
+        <v>-4.755568186785574</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-5.477016242933608</v>
+        <v>-4.388621441902039</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.417609160327252</v>
+        <v>-5.335275694217422</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-9.6272972290148</v>
+        <v>-8.553403998813081</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-7.689329410816505</v>
+        <v>-6.603381215682987</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-6.450000852434137</v>
+        <v>-5.872390230604942</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.807647152497374</v>
+        <v>-6.711911754561783</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-5.267544866006311</v>
+        <v>-4.171098282550247</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-6.376739080635183</v>
+        <v>-5.278718949426406</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-5.590968955625335</v>
+        <v>-5.521326537913247</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-4.125218544643396</v>
+        <v>-3.539900279410404</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.04315</t>
+          <t>X ≈ 0.04297</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>157</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-7.767871198017247</v>
+        <v>-7.734193576416594</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.074157299543081</v>
+        <v>-1.79219653304812</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.506471836364781</v>
+        <v>-3.217616659386906</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.961133358160822</v>
+        <v>-3.29661982345057</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.0671387484836</v>
+        <v>-2.375230956116738</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.366551920415759</v>
+        <v>0.9589366756486086</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.413106746261064</v>
+        <v>-1.074241248227956</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2039416679273813</v>
+        <v>0.5366790369842462</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.638964505047554</v>
+        <v>5.00196374421288</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1817750115732153</v>
+        <v>-0.8158126930544611</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.17925966776653</v>
+        <v>-1.454494402929285</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.708282688359148</v>
+        <v>-2.998062765463814</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.922268671109371</v>
+        <v>-1.856740053816374</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.140886131369903</v>
+        <v>-2.076885416278529</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.177592162622211</v>
+        <v>-2.105391022012604</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-3.472492217933706</v>
+        <v>-3.411453862272936</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.87158145845661</v>
+        <v>-4.814825812352645</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-5.612626209493854</v>
+        <v>-5.554054608411271</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-4.133080243625528</v>
+        <v>-4.068708414384744</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.313607160575735</v>
+        <v>-3.246117254924677</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-3.856116436807049</v>
+        <v>-3.787984794263423</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-7.110692553807986</v>
+        <v>-7.041944505182684</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.664200942294052</v>
+        <v>-2.322892405526595</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.833538197936456</v>
+        <v>-1.126741175069945</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.05482</t>
+          <t>X ≈ 0.05464</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-4.969166450795839</v>
+        <v>-5.464298212245431</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.593558529720163</v>
+        <v>-4.006368145424567</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.071716561674748</v>
+        <v>-5.416839961885742</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-7.583417474268799</v>
+        <v>-8.776157073378677</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.2456441514852301</v>
+        <v>-1.104874294778071</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.340959803314334</v>
+        <v>-4.482983789620612</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.028747648252704</v>
+        <v>-5.264564788272857</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.248271038122866</v>
+        <v>-6.436914841945026</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-5.167684425899417</v>
+        <v>-6.39417690448397</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.344377167025961</v>
+        <v>-8.071619093269057</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-8.814351337609281</v>
+        <v>-10.48063103620573</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-10.02862172915969</v>
+        <v>-11.6592160861109</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-7.499101366259346</v>
+        <v>-9.206318985691745</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-7.723857956545274</v>
+        <v>-8.905957743188232</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-10.20724515183762</v>
+        <v>-11.36204428858512</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.028096701630488</v>
+        <v>-6.287075896847448</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-9.751378465242468</v>
+        <v>-10.89840191478715</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-12.63442715948155</v>
+        <v>-13.68905342941913</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-11.52274844152888</v>
+        <v>-12.57683424861367</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-11.36430374368966</v>
+        <v>-12.38787337942398</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-10.9863265648434</v>
+        <v>-12.03409174750892</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-9.598136879364539</v>
+        <v>-11.23301888457445</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-10.26731244986425</v>
+        <v>-11.87888334412725</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-9.795321637426902</v>
+        <v>-11.97771954197187</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.06649</t>
+          <t>X ≈ 0.0663</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-20.59051205310593</v>
+        <v>-18.05203849056763</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-5.671306189751732</v>
+        <v>-3.375922042730068</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.287707160070617</v>
+        <v>-0.1951612252703043</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.128556962426643</v>
+        <v>0.2229326102929079</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.002204829510596</v>
+        <v>2.199643894650507</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.994344502607866</v>
+        <v>4.698486779626705</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-7.253740288338292</v>
+        <v>-5.430745631672195</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.010194222681676</v>
+        <v>-2.227953965681969</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.922018728795038</v>
+        <v>-2.14072749646332</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.245172850910222</v>
+        <v>-5.760204873047769</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.959148726578846</v>
+        <v>-5.482002203116409</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.912209108456189</v>
+        <v>-4.60544405207051</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.879515994752673</v>
+        <v>-4.567774527406797</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.924247044902749</v>
+        <v>-3.621116766051088</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-7.932541519969696</v>
+        <v>-6.613352329979747</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-7.333593184609718</v>
+        <v>-6.017584398780251</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-5.114435356990278</v>
+        <v>-3.816028260153026</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-6.435779962736696</v>
+        <v>-5.09551064805904</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-3.859762883255478</v>
+        <v>-2.53862195450413</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.768483709273163</v>
+        <v>-1.184039506733768</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-8.264065070652066</v>
+        <v>-7.579078956276454</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-7.152050201482638</v>
+        <v>-6.506325417441538</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-4.957475536253604</v>
+        <v>-5.07665940272819</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-7.414369256474515</v>
+        <v>-6.784290819131385</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.07817</t>
+          <t>X ≈ 0.07797</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.444744922506402</v>
+        <v>1.550732602561155</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-13.33941478855908</v>
+        <v>-15.14950604317816</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-17.8821108737794</v>
+        <v>-18.09820925102059</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.035068572238956</v>
+        <v>-5.387166957564688</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-6.496950477720915</v>
+        <v>-6.404230121918253</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.467520942154998</v>
+        <v>-0.2089040690273976</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.7070988120919992</v>
+        <v>-0.9695526541948354</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.116650893157811</v>
+        <v>-2.745938863805904</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.093800831121612</v>
+        <v>-2.723022933593526</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3115526804177264</v>
+        <v>-1.986930614612348</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.594832475024667</v>
+        <v>-3.22342657177655</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.904935928618471</v>
+        <v>5.548776786264263</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.342750272600277</v>
+        <v>5.940813131659972</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.569976400839032</v>
+        <v>4.215369073121238</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.459351222030698</v>
+        <v>5.058495749015698</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.393938088476482</v>
+        <v>1.133596707448362</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-3.3959622881016</v>
+        <v>-3.514963580113886</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.162253784934599</v>
+        <v>0.9041244925008485</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.74954379562039</v>
+        <v>-1.894904907993023</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>4.263256414560601e-14</v>
+        <v>-0.2005987073159332</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>4.144299591002046</v>
+        <v>3.782331505462565</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.505844535359437</v>
+        <v>2.199330692271417</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.218119701841566</v>
+        <v>0.9564255695642601</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.142178362573098</v>
+        <v>0.8805933163409847</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.08985</t>
+          <t>X ≈ 0.08963</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.071032228760799</v>
+        <v>4.309557380226657</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8.760139858412408</v>
+        <v>8.957135245473246</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>8.937112578313275</v>
+        <v>9.113063138973864</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.730140265533542</v>
+        <v>5.755441798335021</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.587276433382513</v>
+        <v>3.651394040289105</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.341309263656143</v>
+        <v>-3.049488499142733</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.501938934362535</v>
+        <v>-2.200860278602434</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.842502674548257</v>
+        <v>-2.542149940344615</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.676968420191201</v>
+        <v>-2.374506324451851</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.766223425834589</v>
+        <v>-1.433797105618737</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.223720793740476</v>
+        <v>0.5854265399074379</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9032874938207485</v>
+        <v>0.2646249918000549</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.116952538252114</v>
+        <v>2.537173606188723</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.874926028995418</v>
+        <v>2.295068657412514</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.562418932165663</v>
+        <v>-0.04516042654324082</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.5581059706727345</v>
+        <v>-1.195937507964402</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.9510413438597141</v>
+        <v>0.3417181052683844</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.881502351560272</v>
+        <v>0.2263643652823717</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>6.539651119633767</v>
+        <v>3.890531608275658</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>6.7266949152542</v>
+        <v>4.077377418243685</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>6.183494506256288</v>
+        <v>3.513805177947937</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>9.497369959088253</v>
+        <v>7.955253321779772</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>6.382314617095808</v>
+        <v>5.867606342814</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>6.30637327782734</v>
+        <v>5.791774089590724</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.1015</t>
+          <t>X ≈ 0.1013</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-22.343590194124</v>
+        <v>-22.90373527458059</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-20.63243124875333</v>
+        <v>-21.18538205459211</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-20.03233071781462</v>
+        <v>-20.60471084095625</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.079457364341025</v>
+        <v>-5.098664439717957</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-6.528060482698379</v>
+        <v>-7.429988168302657</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-8.424229203025007</v>
+        <v>-7.256551129938302</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.21957133158763</v>
+        <v>2.136303518791884</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.142316647264266</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5.26746724890824</v>
+        <v>-4.222869723638098</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.957969326344397</v>
+        <v>-2.954969073144028</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.683610059229061</v>
+        <v>-2.680909430982176</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-14.37937062937063</v>
+        <v>-13.16374046708322</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9205285145243778</v>
+        <v>-0.001188248225112432</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-5.308551992225397</v>
+        <v>-4.30389977773293</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-8.050816564596154</v>
+        <v>-7.002859401844105</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-3.289089848307988</v>
+        <v>-2.326839826839887</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-8.583205943409133</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.444833625218912</v>
+        <v>-0.5247813411078681</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-3.312043795620433</v>
+        <v>-2.349706286714159</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-9.375</v>
+        <v>-8.285309456337963</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.668200408998011</v>
+        <v>-2.70540664471222</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-5.827488797973956</v>
+        <v>-4.822068932651931</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-5.55271363149177</v>
+        <v>-4.547594220169827</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-7.711988304093509</v>
+        <v>-6.664242799923649</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.1132</t>
+          <t>X ≈ 0.1129</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4586088616272406</v>
+        <v>1.325133696751166</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.911755711183844</v>
+        <v>7.828721079985023</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>11.21766928218545</v>
+        <v>13.35667352121776</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>12.66257319709922</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>26.80527285063478</v>
+        <v>26.01862882638791</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>16.99243746364165</v>
+        <v>16.07099833643922</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>12.88623799825444</v>
+        <v>11.91814729078364</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.274350019402448</v>
+        <v>8.191659983961515</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.649199417758318</v>
+        <v>1.33659544173819</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.457969326344354</v>
+        <v>-2.884596096367176</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-9.507088178343132</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.870629370629374</v>
+        <v>0.5589900044157119</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-9.25386184785777</v>
+        <v>-10.9089996486473</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-6.141885325558789</v>
+        <v>-7.681802663024918</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-6.800816564595991</v>
+        <v>-8.339945960605377</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>-0.8490073145245631</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>10.32681645754309</v>
+        <v>9.361903134704875</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>10.22183304144775</v>
+        <v>9.257062430883693</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>6.024677949739051</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>3.958333333333329</v>
+        <v>2.763247897638053</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.415132924335524</v>
+        <v>2.220701729672179</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>10.00584453535954</v>
+        <v>9.041407492401</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>13.61395303517489</v>
+        <v>12.76415806695192</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>10.204678362573</v>
+        <v>9.240049951659536</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.1249</t>
+          <t>X ≈ 0.1247</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-23.96350924735729</v>
+        <v>-20.73316228101973</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-27.8931444703044</v>
+        <v>-24.78547619116582</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-27.86279048792954</v>
+        <v>-26.65620248462236</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-14.78348035284678</v>
+        <v>-20.37510888501735</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-8.252198413732899</v>
+        <v>-13.75405411946947</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.168482076588276</v>
+        <v>-1.189407803728585</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.941348208642303</v>
+        <v>-3.475941379167189</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.228373007908097</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-9.074938513276216</v>
+        <v>-10.8555227848627</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-9.848773924045645</v>
+        <v>-11.62843846089919</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-13.02269051899922</v>
+        <v>-11.35437881873732</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.956956836267182</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-7.529723916823286</v>
+        <v>-5.613433146184242</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.30280486578868</v>
+        <v>-2.263083451202263</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-4.961736104825981</v>
+        <v>-2.921226748782821</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-4.3666760552046</v>
+        <v>-2.32683982683983</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-4.500769749353566</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.157477303379842</v>
+        <v>-2.565597667638485</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.941354140448027</v>
+        <v>-2.349706286714159</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.7543103448275943</v>
+        <v>-2.162860476746076</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-4.745786615894552</v>
+        <v>-6.276835216140732</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-4.821741671537069</v>
+        <v>-6.352681177549833</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-4.546966505054989</v>
+        <v>-6.07820646506778</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-4.622907844323457</v>
+        <v>-6.154038718291055</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.1366</t>
+          <t>X ≈ 0.1363</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-9.934562613718271</v>
+        <v>-17.03553014001689</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.009296920395208</v>
+        <v>-12.01925036031629</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>13.30100261551866</v>
+        <v>5.697468150298342</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-12.4127906976745</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.528060482698464</v>
+        <v>-0.9068318972471516</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.09089586969159313</v>
+        <v>-0.7198657111498505</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8637620017457053</v>
+        <v>4.063741160515356</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>11.35768335273573</v>
+        <v>14.89664082687338</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>17.64919941775845</v>
+        <v>20.49368356434366</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>23.12536400698902</v>
+        <v>25.27632344386272</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>17.14972327410436</v>
+        <v>14.43927197491352</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.370629370629374</v>
+        <v>3.04941146035442</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.49613815214223</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>15.52478134110788</v>
+        <v>12.81628162816281</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>14.86585010207057</v>
+        <v>12.15813833058225</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>15.46091015169196</v>
+        <v>12.75252525252525</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>21.57681645754303</v>
+        <v>18.17416367110334</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>15.22183304144775</v>
+        <v>18.06932296728216</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>9.187956204379567</v>
+        <v>12.72965879265092</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>21.875</v>
+        <v>24.02761571373007</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>15.08179959100205</v>
+        <v>17.92951399020848</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>8.755844535359351</v>
+        <v>12.29811247324381</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>9.030619701841566</v>
+        <v>12.57258718572587</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>15.20467836257301</v>
+        <v>18.05231048805816</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.1482</t>
+          <t>X ≈ 0.1479</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>21</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-22.34407214466703</v>
+        <v>-25.06941854200336</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-11.15215406325216</v>
+        <v>-11.11848105463882</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-12.59185452733841</v>
+        <v>-12.55650010366992</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6147966601586745</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>10.32577079697505</v>
+        <v>10.39124539996132</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>18.79815954321192</v>
+        <v>18.86489479512736</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.553961322520273</v>
+        <v>4.620667691327775</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.9817788501539226</v>
+        <v>-0.9141527466134818</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>13.57829470267571</v>
+        <v>13.64562118126273</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.2992007992008</v>
+        <v>13.36687177781474</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.412804818808887</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.191448007774603</v>
+        <v>7.260726072607326</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>16.05632629254676</v>
+        <v>16.12639229883623</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>16.6513863421682</v>
+        <v>16.72077922077928</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>16.51729264801922</v>
+        <v>16.58686208380175</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>11.65040447001918</v>
+        <v>11.72011661807581</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>11.86652763295093</v>
+        <v>11.93600799900006</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>12.05357142857143</v>
+        <v>12.12285380896816</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>11.51037101957355</v>
+        <v>11.5803076410022</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>11.43441596393087</v>
+        <v>11.50446167959303</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.109440267335138</v>
+        <v>2.179294615042416</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.1599</t>
+          <t>X ≈ 0.1596</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>15</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-27.00745473908413</v>
+        <v>-26.9741804467653</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-34.00929692039517</v>
+        <v>-33.97562391178182</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-8.782330717814645</v>
+        <v>-8.746976294146158</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-9.496124031007753</v>
+        <v>-9.459930313588849</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-23.19472714936514</v>
+        <v>-23.12905411946946</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-9.674229203025106</v>
+        <v>-9.608754600038836</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.78042866841237</v>
+        <v>-3.714036617262423</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.058983313930931</v>
+        <v>-3.992248062015499</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.64919941775841</v>
+        <v>2.715905786565912</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.791302659677726</v>
+        <v>-4.723676556137285</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.516943392562389</v>
+        <v>-4.449616913975362</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.870629370629374</v>
+        <v>1.938300349243306</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.412804818808887</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.85811467444112</v>
+        <v>13.92739273927384</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>13.1991834354039</v>
+        <v>13.26924944169337</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.4609101516918628</v>
+        <v>0.5303030303029388</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>13.55516637478108</v>
+        <v>13.6248785228377</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.104622871046381</v>
+        <v>7.174103237095515</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>6.748466257668618</v>
+        <v>6.81840287909727</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>13.61395303517489</v>
+        <v>13.68369829683698</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>13.53801169590634</v>
+        <v>13.60786604361362</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.1715</t>
+          <t>X ≈ 0.1713</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>13</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1720324404030507</v>
+        <v>0.2053067327218798</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-7.855450766548969</v>
+        <v>-7.821777757935628</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.602843538327363</v>
+        <v>-1.567489114658876</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-25.39355992844365</v>
+        <v>-25.35736621102474</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-25.75882971346764</v>
+        <v>-25.69315668357196</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.494742023537782</v>
+        <v>-2.429267420551511</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-10.95991584789955</v>
+        <v>-10.89352379674961</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-18.93077818572575</v>
+        <v>-18.86404293381032</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-18.88926212070322</v>
+        <v>-18.82255575189572</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-19.66309753147259</v>
+        <v>-19.59547142793215</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-27.08104595666495</v>
+        <v>-27.01371947807793</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-19.66783216783222</v>
+        <v>-19.60016118921828</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-20.79232338631936</v>
+        <v>-20.7233232560744</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-21.01368019735371</v>
+        <v>-20.94440213252099</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-29.36491912869866</v>
+        <v>-29.29485312240919</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-21.07755138676958</v>
+        <v>-21.0081585081585</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-13.51933738861081</v>
+        <v>-13.44976795282829</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-13.62432080470604</v>
+        <v>-13.55460865664942</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-13.40819764177433</v>
+        <v>-13.33871727572519</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-13.22115384615385</v>
+        <v>-13.15187146575712</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-13.76435425515185</v>
+        <v>-13.6944176337232</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-13.84030931079441</v>
+        <v>-13.77026359513225</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-13.56553414431233</v>
+        <v>-13.49578888265025</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-21.33378317588843</v>
+        <v>-21.26392882818116</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.1832</t>
+          <t>X ≈ 0.183</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>15</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>32.99254526091588</v>
+        <v>33.0258195532347</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>19.32403641293821</v>
+        <v>19.35770942155155</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>11.2176692821854</v>
+        <v>11.25302370585388</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>23.47193951730144</v>
+        <v>23.53761254719711</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>23.65910413030822</v>
+        <v>23.72457873329449</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>22.88623799825429</v>
+        <v>22.95263004940424</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>22.60768335273573</v>
+        <v>22.67441860465117</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>15.9825327510917</v>
+        <v>16.0492391198992</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>15.4830566074376</v>
+        <v>15.55038308602463</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.2039627039628</v>
+        <v>15.27163368257673</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>14.07947148547562</v>
+        <v>14.14847161572057</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.191448007774632</v>
+        <v>7.260726072607355</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>13.66014979087632</v>
+        <v>13.72971922665884</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.888499708114409</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.4379562043795175</v>
+        <v>0.5074365704286521</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.6250000000000426</v>
+        <v>0.6942823803967713</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.08179959100208833</v>
+        <v>0.1517362124307411</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.005844535359479153</v>
+        <v>0.07589025102164015</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.2806197018416086</v>
+        <v>0.3503649635036936</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-6.461988304093566</v>
+        <v>-6.392133956386289</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.195</t>
+          <t>X ≈ 0.1946</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>11</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-8.219575951205343</v>
+        <v>-8.186301658886514</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.5361576250594169</v>
+        <v>0.5698306336727583</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.9035428390267199</v>
+        <v>-0.8681884153582331</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.473572938689216</v>
+        <v>7.50976665610812</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.108303153665169</v>
+        <v>7.173976183560846</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.795441324237068</v>
+        <v>-1.729966721250797</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-2.568307456291166</v>
+        <v>-2.501915405141219</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.244046989099367</v>
+        <v>6.310782241014799</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11.89625512769618</v>
+        <v>-11.82954875888868</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-12.67009053846561</v>
+        <v>-12.60246443492517</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-21.4866403622593</v>
+        <v>-21.41931388367227</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-3.583916083916144</v>
+        <v>-3.516245105302211</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-13.79931639331232</v>
+        <v>-13.73031626306736</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-14.02067320434667</v>
+        <v>-13.95139513951395</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-5.588695352474943</v>
+        <v>-5.518629346185477</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-4.993635302853562</v>
+        <v>-4.924242424242486</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-5.127728997002357</v>
+        <v>-5.058159561219831</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-5.232712413097765</v>
+        <v>-5.163000265041141</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-5.016589250165822</v>
+        <v>-4.947108884116687</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-4.829545454545517</v>
+        <v>-4.760263074148789</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-5.372745863543344</v>
+        <v>-5.302809242114691</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-5.448700919186081</v>
+        <v>-5.37865520352392</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-5.173925752703823</v>
+        <v>-5.104180491041738</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-5.249867091972362</v>
+        <v>-5.180012744265085</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3346</v>
+        <v>3350</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2161219993987658</v>
+        <v>-0.216595705190052</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2088218610127015</v>
+        <v>-0.209313117001237</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2366421721260465</v>
+        <v>-0.2371374728270084</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.191311196783154</v>
+        <v>-0.1918788793652979</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.302206099340367</v>
+        <v>-0.3032897977122602</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3064131110709951</v>
+        <v>-0.3074877750189486</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2894979517903096</v>
+        <v>-0.2906131938390004</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1644760761756245</v>
+        <v>-0.1657477649269694</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1654390826879322</v>
+        <v>-0.166709369451965</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1782074215824849</v>
+        <v>-0.1794831356061692</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1843047104149349</v>
+        <v>-0.1855669585783986</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1782092237720576</v>
+        <v>-0.1794866822855496</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2428401022515772</v>
+        <v>-0.2440702864911231</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2380315313593471</v>
+        <v>-0.2392739273927376</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.2235686758727908</v>
+        <v>-0.2248460232267391</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2069491208184786</v>
+        <v>-0.208231811864934</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2040514219678613</v>
+        <v>-0.2053418397694671</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2017946435164504</v>
+        <v>-0.2030912824860849</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1767856637195138</v>
+        <v>-0.1781073938037849</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1511194029850813</v>
+        <v>-0.1524677686790028</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.139161890037073</v>
+        <v>-0.1405393616820376</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.2271303750348324</v>
+        <v>-0.228405691699173</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.08388582549634549</v>
+        <v>-0.08532587505200695</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1718906750838087</v>
+        <v>-0.173228483749476</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3317</v>
+        <v>3321</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2908878728166684</v>
+        <v>-0.2915648167812535</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2207374714583139</v>
+        <v>-0.2215108396908434</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3261693437383073</v>
+        <v>-0.3268685742179258</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1543999275215882</v>
+        <v>-0.1553308922579077</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3230245114754453</v>
+        <v>-0.3246629019045812</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2989168591969218</v>
+        <v>-0.3005784994098093</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3351177305999329</v>
+        <v>-0.3367647978096571</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1465920748070175</v>
+        <v>-0.1484762110515589</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1479194297806501</v>
+        <v>-0.1498016474868891</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1540565874271493</v>
+        <v>-0.155960414208252</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2526791282981335</v>
+        <v>-0.2544559461689246</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2140807525307338</v>
+        <v>-0.2159150722988485</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3295830017039236</v>
+        <v>-0.3313203010461905</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2927720102597249</v>
+        <v>-0.2945626294841972</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.2724541673220884</v>
+        <v>-0.2742941018501668</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2308191716163108</v>
+        <v>-0.2326888591532565</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.2267334822884948</v>
+        <v>-0.228614106674442</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2536409278570915</v>
+        <v>-0.2554941853077679</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.230315920846202</v>
+        <v>-0.232190609366846</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.145852152965972</v>
+        <v>-0.1478228827611616</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1290437824919337</v>
+        <v>-0.1310556046571492</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2171141871473381</v>
+        <v>-0.2190239831041936</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.07501622341461456</v>
+        <v>-0.07708837785698108</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1631238683584613</v>
+        <v>-0.1650939082080356</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3286</v>
+        <v>3290</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4556263921515225</v>
+        <v>-0.4564221209779973</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.260808407698633</v>
+        <v>-0.2618557958397503</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.5049393258178227</v>
+        <v>-0.5057601459532179</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3854162270150141</v>
+        <v>-0.3864157113733384</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4614946733187324</v>
+        <v>-0.4635962772210434</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.438958823686832</v>
+        <v>-0.4410802751697389</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5591147114035948</v>
+        <v>-0.5611286442758328</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.335987149989883</v>
+        <v>-0.3382855695775149</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3680680769402045</v>
+        <v>-0.3703271937669612</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3973632657383348</v>
+        <v>-0.3996249015771554</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.4389399571779364</v>
+        <v>-0.4411397719832379</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3367690526574734</v>
+        <v>-0.3391072824950356</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4428215081550135</v>
+        <v>-0.4450858921053893</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3732769113193086</v>
+        <v>-0.3756375637563707</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3465929935288159</v>
+        <v>-0.3490187203759447</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2494723619692465</v>
+        <v>-0.2519892680596101</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3048264212908549</v>
+        <v>-0.3072841097075099</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.3006456948827534</v>
+        <v>-0.3031150046703814</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.2183792559668376</v>
+        <v>-0.2209397573406449</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1044832826747708</v>
+        <v>-0.1071748145030895</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.08238405144247452</v>
+        <v>-0.08512986713200377</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.2009681167086868</v>
+        <v>-0.2035751195737845</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.06011653180613763</v>
+        <v>-0.06288328930704523</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1787665552601325</v>
+        <v>-0.1813943413913606</v>
       </c>
     </row>
     <row r="9">
@@ -3430,2211 +3430,2211 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3246</v>
+        <v>3250</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5691963522176025</v>
+        <v>-0.5702696615529561</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6127240929777429</v>
+        <v>-0.6137657210727383</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.6892789883992236</v>
+        <v>-0.6903167608739125</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.528987880773002</v>
+        <v>-0.5302667050261576</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.5403116312436396</v>
+        <v>-0.543146094589261</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5198174383191301</v>
+        <v>-0.5226672887372388</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.7239366876176021</v>
+        <v>-0.7265863570848907</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4640517790852314</v>
+        <v>-0.467038835642775</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4664092912266113</v>
+        <v>-0.4693928351799244</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4559243365693462</v>
+        <v>-0.45897067378435</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5013967013483125</v>
+        <v>-0.5043722515992286</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3945639995363734</v>
+        <v>-0.3976898408241354</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5188296096017027</v>
+        <v>-0.5218749037520354</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4764471601206282</v>
+        <v>-0.4795602259612366</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4413695599877983</v>
+        <v>-0.4445687029317682</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.3196675987690085</v>
+        <v>-0.3229811931469371</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.4048158818360008</v>
+        <v>-0.4080353532203418</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.4608237851205104</v>
+        <v>-0.4639830660238715</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.3802535772260924</v>
+        <v>-0.3835004495405769</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2057692307692278</v>
+        <v>-0.2092210000580934</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1767414985639775</v>
+        <v>-0.1802650172034888</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2650914252317023</v>
+        <v>-0.2685131930128435</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1567070613244397</v>
+        <v>-0.1602471558442389</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2451059873961015</v>
+        <v>-0.2485442127965527</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.09113</t>
+          <t>X &gt; -0.09116</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3203</v>
+        <v>3207</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.6034018027731278</v>
+        <v>-0.604911549615359</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.735949107798163</v>
+        <v>-0.7373220834582597</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.8555771486029258</v>
+        <v>-0.8569163644085549</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.6520797383450159</v>
+        <v>-0.6537287632012507</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6274393646860474</v>
+        <v>-0.6311219441179219</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5782366587566088</v>
+        <v>-0.5819679623306016</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8365712000055012</v>
+        <v>-0.8400453075169239</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.5691895101800242</v>
+        <v>-0.5730200789874544</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.5100045623411376</v>
+        <v>-0.5139078780304018</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5196593211603542</v>
+        <v>-0.5236144250406696</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4762879268913665</v>
+        <v>-0.4802777799376585</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2395480336656703</v>
+        <v>-0.2438569401567534</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3992088755577328</v>
+        <v>-0.3851104738317161</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.4027007628448231</v>
+        <v>-0.3701707651324924</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3583093001710225</v>
+        <v>-0.3254404566679696</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.2429204306811386</v>
+        <v>-0.2104377104377164</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.265083853983441</v>
+        <v>-0.2509841658092142</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.413879018383966</v>
+        <v>-0.4180719907010371</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.3039390574658185</v>
+        <v>-0.3082545877282072</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.1295993140006289</v>
+        <v>-0.1341199864671765</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.0928728980809268</v>
+        <v>-0.09748497136992285</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1813629529400984</v>
+        <v>-0.1858735383208767</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1688185004056209</v>
+        <v>-0.1733258095636856</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2261677192252094</v>
+        <v>-0.2306122850423549</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.07945</t>
+          <t>X &gt; -0.0795</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3146</v>
+        <v>3150</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7849518446519568</v>
+        <v>-0.78685783560163</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.040250805423547</v>
+        <v>-1.041869968564114</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.041414446092638</v>
+        <v>-1.043179092084472</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.7582394966630446</v>
+        <v>-0.760435364093901</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.7582217220282104</v>
+        <v>-0.7629873896515349</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5850451423039402</v>
+        <v>-0.5900138125045231</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.8973747825112852</v>
+        <v>-0.9020302981471033</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6518103181503392</v>
+        <v>-0.6568076911768941</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5606771254515124</v>
+        <v>-0.5657888071742434</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4615580956076357</v>
+        <v>-0.4668770621461391</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.4223388101529366</v>
+        <v>-0.4276829268404896</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.239636789066445</v>
+        <v>-0.2452439545541623</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4452433434217724</v>
+        <v>-0.4320918537318406</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.4764860860150719</v>
+        <v>-0.4445726396578777</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.3877156665506618</v>
+        <v>-0.3554997928119619</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.2175933359428015</v>
+        <v>-0.1857932941583158</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.3963043797547812</v>
+        <v>-0.383081787282805</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.4190299027146835</v>
+        <v>-0.4245511349569711</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.2792764201840612</v>
+        <v>-0.2849564565126599</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1369047619047663</v>
+        <v>-0.1427499594891302</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.05792730642570376</v>
+        <v>-0.06393140571074696</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.1148670275376489</v>
+        <v>-0.1208102565926126</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1070510957434436</v>
+        <v>-0.1129800063471933</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1322574289081473</v>
+        <v>-0.1381657024180356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.06777</t>
+          <t>X &gt; -0.06783</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3047</v>
+        <v>3051</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.099154000274915</v>
+        <v>-1.101784613431967</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.123741002560109</v>
+        <v>-1.12638913483616</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.208945199223592</v>
+        <v>-1.211688563418633</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.7631169619484766</v>
+        <v>-0.766544846009829</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.9144834591997721</v>
+        <v>-0.9213183524116459</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.6112190822284091</v>
+        <v>-0.6184274616842131</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.8760088991983537</v>
+        <v>-0.8829863889519203</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.6134861996981158</v>
+        <v>-0.6208505633749297</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4226960070782368</v>
+        <v>-0.4303083126508369</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3933512594379991</v>
+        <v>-0.4011169740282483</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4598254505523656</v>
+        <v>-0.467470168928557</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.03319791101930036</v>
+        <v>-0.04144483206999183</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2417584785414419</v>
+        <v>-0.2306133515997359</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2995562447606233</v>
+        <v>-0.2689677271094126</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.1537834057828249</v>
+        <v>-0.1229458929480103</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1610211085371702</v>
+        <v>-0.1304755107502871</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.3739039091891243</v>
+        <v>-0.3625280746168613</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.4267093758467126</v>
+        <v>-0.4346569694750215</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.2239048703255406</v>
+        <v>-0.2320922253828144</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.08296460176990905</v>
+        <v>-0.09131500094533607</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.04901270575614802</v>
+        <v>0.04040680837044874</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.007274520068577317</v>
+        <v>-0.01582281809074715</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.008094208919587231</v>
+        <v>-0.01660751356057233</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.1300771346372755</v>
+        <v>-0.138446640752079</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.0561</t>
+          <t>X &gt; -0.05617</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.69998934312315</v>
+        <v>-1.703389601535299</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.40459824828072</v>
+        <v>-1.408469882540025</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.668343433527575</v>
+        <v>-1.672146362173315</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.069093934471688</v>
+        <v>-1.073857953375622</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.245170230483055</v>
+        <v>-1.254763218629883</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5618300667595264</v>
+        <v>-0.5723228669777924</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.9063950167525263</v>
+        <v>-0.9165797598600705</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6540020788575802</v>
+        <v>-0.6645933203914254</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5589917085214893</v>
+        <v>-0.5697111186829318</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.6306107284156326</v>
+        <v>-0.6413944786284844</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5756865619612981</v>
+        <v>-0.5864973141572634</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1860839877580602</v>
+        <v>-0.1974894835782521</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4564583630610528</v>
+        <v>-0.4476603524251033</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5069918054585756</v>
+        <v>-0.4779788323659844</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3255374577380366</v>
+        <v>-0.2963243287984341</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.120286429504624</v>
+        <v>-0.09149403153502789</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.5076568666703736</v>
+        <v>-0.4987285583314289</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.6266103386411999</v>
+        <v>-0.6377339358799787</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.5271361980844986</v>
+        <v>-0.5383597385255072</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1829424854501909</v>
+        <v>-0.1946065084921571</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.05518671036781342</v>
+        <v>-0.0671420365433093</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.144892018254815</v>
+        <v>-0.1567474499705384</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.08949681632155659</v>
+        <v>-0.1013804163731393</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.1107141639952971</v>
+        <v>-0.122591562229033</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.04442</t>
+          <t>X &gt; -0.04451</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2740</v>
+        <v>2744</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.641886708177452</v>
+        <v>-2.646272068224008</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.980311413148748</v>
+        <v>-1.985754157802035</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.458783538885022</v>
+        <v>-2.463950597439627</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.703037253149404</v>
+        <v>-1.70950791436124</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.722111987957803</v>
+        <v>-1.735839100756429</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.8256563921880513</v>
+        <v>-0.8406386580097518</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9613119110016086</v>
+        <v>-0.9763297186276532</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.9289905760950603</v>
+        <v>-0.9441455722886474</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7943167464261549</v>
+        <v>-0.809665486557094</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.7845197139413003</v>
+        <v>-0.8001158401237376</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.8891716731876187</v>
+        <v>-0.9045473434974411</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4202797202797157</v>
+        <v>-0.4364273196020036</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7447709387668624</v>
+        <v>-0.7395293529197531</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.7843095679830299</v>
+        <v>-0.7576847801059117</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.7671073369981798</v>
+        <v>-0.7402016669943734</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.623514884698146</v>
+        <v>-0.596969696969694</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.9181780819546077</v>
+        <v>-0.9127050157653471</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.96534831324999</v>
+        <v>-0.9811820832228975</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.7642295879701564</v>
+        <v>-0.7803044262973842</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.5922011661807645</v>
+        <v>-0.6084832673470828</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.3483863368142224</v>
+        <v>-0.3651913449045736</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.366146711905337</v>
+        <v>-0.3829589842296741</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3249986856082714</v>
+        <v>-0.3418026139098203</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.2332778418064692</v>
+        <v>-0.2502486308274996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.03275</t>
+          <t>X &gt; -0.03284</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2529</v>
+        <v>2534</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.615274799238442</v>
+        <v>-3.601692845616775</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.40019173986137</v>
+        <v>-2.389254934108457</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.602511322447491</v>
+        <v>-2.592326346392703</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.606624161932075</v>
+        <v>-1.598960759165742</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.675408223366439</v>
+        <v>-1.678073727312594</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5625939828992301</v>
+        <v>-0.5673004350067004</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6843479238849071</v>
+        <v>-0.6894421640965405</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5866518164224033</v>
+        <v>-0.5921695382620626</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6014892874757933</v>
+        <v>-0.6069536007082874</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5262107961606759</v>
+        <v>-0.5324519326926236</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.7411786557893763</v>
+        <v>-0.7467867252961113</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6037599122705402</v>
+        <v>-0.6098711017987668</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8614268596781045</v>
+        <v>-0.8449718671014068</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.7675748448653366</v>
+        <v>-0.7282546436461743</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.7566873289774918</v>
+        <v>-0.6940051514824788</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.7294721896561001</v>
+        <v>-0.6670187499254041</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.155833384728261</v>
+        <v>-1.116020565910361</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.395523960524635</v>
+        <v>-1.378403609235292</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.274750977940876</v>
+        <v>-1.280668982938771</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.104174891433082</v>
+        <v>-1.110288147578053</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.8344721309568826</v>
+        <v>-0.8415629598199885</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.8870831612031864</v>
+        <v>-0.8941412947197307</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.023728124245388</v>
+        <v>-1.030305647936189</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.9182951447420464</v>
+        <v>-0.9251515833265671</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02107</t>
+          <t>X &gt; -0.02118</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2254</v>
+        <v>2260</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.466374926877556</v>
+        <v>-4.474912082703256</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.679045929642157</v>
+        <v>-3.646243147618407</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.422565666419587</v>
+        <v>-3.392553329881309</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.086104933020387</v>
+        <v>-2.104618958277491</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.030705985343964</v>
+        <v>-2.108825447525739</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9813899146850602</v>
+        <v>-0.9740574303657752</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.7589517634403222</v>
+        <v>-0.7533558660887181</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6152747046594129</v>
+        <v>-0.6104779167050651</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7253588861285536</v>
+        <v>-0.7642704248878758</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9439024534617957</v>
+        <v>-0.9393369057773668</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.420758387406998</v>
+        <v>-1.43374389810235</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.081204478243805</v>
+        <v>-1.070080771180159</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.233534848299655</v>
+        <v>-1.197218293076183</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.45489165933401</v>
+        <v>-1.392695560946819</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.406796826784934</v>
+        <v>-1.344437092522959</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.493112836813793</v>
+        <v>-1.456451936584386</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.911131353160194</v>
+        <v>-1.899419846188792</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.167547489525703</v>
+        <v>-2.180860991511075</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.92592161766558</v>
+        <v>-1.964969610586749</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.536204605845882</v>
+        <v>-1.576035640804683</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.38917958489516</v>
+        <v>-1.430234622743846</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.572169649037725</v>
+        <v>-1.612880748094234</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.847983402371291</v>
+        <v>-1.887582847199575</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.454594042040924</v>
+        <v>-1.495378794144408</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.009397</t>
+          <t>X &gt; -0.009514</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1910</v>
+        <v>1917</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.439438124338544</v>
+        <v>-5.529103709396786</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.34695925805746</v>
+        <v>-4.389702586730024</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.889745825229696</v>
+        <v>-3.885937108922555</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.680462215345941</v>
+        <v>-2.655094389581947</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.629931584569569</v>
+        <v>-2.600282735332591</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.374697221745762</v>
+        <v>-1.348035374589223</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.338527870632277</v>
+        <v>-1.31306792672445</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.911317167826482</v>
+        <v>-0.9166556039632567</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7883005822416251</v>
+        <v>-0.7713801501232851</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.219998160806789</v>
+        <v>-1.25534841491195</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.51885410994992</v>
+        <v>-1.575158039516488</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.381064219782303</v>
+        <v>-1.356917945974992</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.567566902573773</v>
+        <v>-1.514554905340326</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.580481816786858</v>
+        <v>-1.497511873976151</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.561976891155062</v>
+        <v>-1.479276399444323</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.718443341530147</v>
+        <v>-1.665326522246396</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.083199191909237</v>
+        <v>-2.059389340805552</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.366893472122186</v>
+        <v>-2.372346589892082</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.068571210764034</v>
+        <v>-2.104426072651421</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.48576280041798</v>
+        <v>-1.523312622206085</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.371415254789909</v>
+        <v>-1.410763787569302</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.469050862130103</v>
+        <v>-1.508268164819988</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.896251046457756</v>
+        <v>-1.933263816475495</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.156578181929525</v>
+        <v>-1.248680643918895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.002279</t>
+          <t>X &gt; 0.00215</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1533</v>
+        <v>1540</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.643133671728847</v>
+        <v>-5.633135031169758</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.526092786028194</v>
+        <v>-4.522247705994005</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.447058147247908</v>
+        <v>-4.512742059911872</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.609461673757153</v>
+        <v>-3.583132717538192</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.26367780655108</v>
+        <v>-3.305170957957429</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.360300785603712</v>
+        <v>-1.472068591012302</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.57978141922144</v>
+        <v>-1.692531240918335</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.045166388196911</v>
+        <v>-1.196549137284322</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9023235893705959</v>
+        <v>-1.090545826337362</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.704402529976043</v>
+        <v>-1.891741974686887</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.819148321226464</v>
+        <v>-1.968996758936605</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.709137166335609</v>
+        <v>-1.823819883465163</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.796014895847399</v>
+        <v>-1.810993671041018</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.368863276272144</v>
+        <v>-1.347688166874939</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.833241986126566</v>
+        <v>-1.811656707173945</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.849278037795386</v>
+        <v>-1.864518976169457</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.335521204794624</v>
+        <v>-2.38678562771004</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.338270922164988</v>
+        <v>-2.426901412437374</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.824722599261527</v>
+        <v>-1.952110355137634</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.339866623292131</v>
+        <v>-1.468930054836434</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.8036170756646186</v>
+        <v>-0.9370518627475306</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.10164732131809</v>
+        <v>-1.234096778809786</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.244804026971991</v>
+        <v>-1.31089395927377</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.021675192547576</v>
+        <v>-1.089103653355991</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.01395</t>
+          <t>X &gt; 0.01381</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1201</v>
+        <v>1212</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-7.785963511013954</v>
+        <v>-7.719150539206844</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.778844245498007</v>
+        <v>-5.770077419122728</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.613742030280271</v>
+        <v>-5.617724593465837</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.938737979387767</v>
+        <v>-4.084113320124793</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.233167566718237</v>
+        <v>-3.396156872263134</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.76546305847981</v>
+        <v>-1.856435996656302</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.740824708016333</v>
+        <v>-2.829515732741534</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.231292700113158</v>
+        <v>-2.288726358493797</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.648321243398655</v>
+        <v>-1.919638848978764</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.872361385897747</v>
+        <v>-3.138977102585372</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.846141076598791</v>
+        <v>-2.983934660762344</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.463531092563343</v>
+        <v>-2.560878632694298</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.595466479784982</v>
+        <v>-2.652404856478874</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.82426745955383</v>
+        <v>-1.840151120375189</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.731337656407511</v>
+        <v>-2.745004944271543</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.91657329201665</v>
+        <v>-2.972986443381181</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-3.630137184841082</v>
+        <v>-3.68256147509549</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.605838872388198</v>
+        <v>-3.787402178916672</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.177300843713304</v>
+        <v>-3.407037113781833</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-3.192427385892117</v>
+        <v>-3.420943957051826</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.526173830924868</v>
+        <v>-2.811226750532263</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.80379802490657</v>
+        <v>-3.004834625419917</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.481443526111839</v>
+        <v>-2.765875761970378</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.343198406785774</v>
+        <v>-2.629757718762527</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.02563</t>
+          <t>X &gt; 0.02548</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-8.853825422664116</v>
+        <v>-8.682863920154652</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-6.072788983887186</v>
+        <v>-5.971422231109514</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.025268570921938</v>
+        <v>-5.04560931202203</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.938214426487974</v>
+        <v>-3.810807506571301</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.820433364054402</v>
+        <v>-2.826981762602578</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.621913897263262</v>
+        <v>-1.634071055734942</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.549006163104515</v>
+        <v>-2.453916941092061</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.175525999017715</v>
+        <v>-1.148179072223179</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.074204837560785</v>
+        <v>-1.106691890308475</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.066063043064311</v>
+        <v>-3.088722363043559</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.004696321209892</v>
+        <v>-2.968135432493881</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.857805134162959</v>
+        <v>-2.765089481265171</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.065363445301863</v>
+        <v>-1.92081081623423</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.180223983705751</v>
+        <v>-1.974942717201657</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-3.265140313264894</v>
+        <v>-3.05771446488837</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.88307280890443</v>
+        <v>-2.675641767998457</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-3.975632956727466</v>
+        <v>-3.764972917714786</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.701407896718557</v>
+        <v>-3.551342283956345</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.891819676090009</v>
+        <v>-2.910822452925864</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.644230769230774</v>
+        <v>-2.617819530431298</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.439567930365477</v>
+        <v>-2.417265910711556</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.988807871057674</v>
+        <v>-2.963429621454495</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.11766723605993</v>
+        <v>-2.096443547134648</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.703145860363662</v>
+        <v>-1.684998706120055</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.03731</t>
+          <t>X &gt; 0.03714</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-9.066930992967841</v>
+        <v>-8.990913163630118</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-6.142630253728456</v>
+        <v>-6.023180054450208</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.382241710248948</v>
+        <v>-5.281367828537647</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.559319402614342</v>
+        <v>-3.543815523301873</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.254362218345996</v>
+        <v>-1.289973659699342</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.34359610891795</v>
+        <v>0.2982839125774674</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.6211247862169174</v>
+        <v>-0.6643912271915084</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4390086539405473</v>
+        <v>0.3871845620979784</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.02185357325435433</v>
+        <v>-0.2362218730085957</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.017253442675489</v>
+        <v>-2.264732925422685</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.81671967891586</v>
+        <v>-2.982950247308693</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.021988079035054</v>
+        <v>-2.195032984090027</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.267284666649715</v>
+        <v>-1.374447832432566</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.220185101845146</v>
+        <v>-1.250860380155657</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.684485468399224</v>
+        <v>-2.711142715169373</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.955197230858381</v>
+        <v>-1.98306595365419</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.491975488765689</v>
+        <v>-2.518052609348246</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.654511044573752</v>
+        <v>-2.756583152741619</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.957736931555829</v>
+        <v>-2.139622253100711</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.288746630727765</v>
+        <v>-1.551706924416109</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.697176150237844</v>
+        <v>-1.960563252809948</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.099418622535296</v>
+        <v>-2.360522064908785</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.205866784644918</v>
+        <v>-1.204594822019146</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.06731081198712</v>
+        <v>-1.201977356833716</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.04898</t>
+          <t>X &gt; 0.0488</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-9.417364648994038</v>
+        <v>-9.326465842528961</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.97037983071661</v>
+        <v>-7.152881436865393</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-5.618488909904983</v>
+        <v>-5.832403429824495</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.450926290894756</v>
+        <v>-3.609818456765574</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7653486182916893</v>
+        <v>-1.000202578853205</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.5351652508516196</v>
+        <v>0.1218851306009938</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4074801681294034</v>
+        <v>-0.5549584834794032</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.502420194841001</v>
+        <v>0.3472685203341328</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.493415183260304</v>
+        <v>-1.634853066722492</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.512391095051875</v>
+        <v>-2.651604484065217</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.258439991201847</v>
+        <v>-3.391058355416803</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.836853622567901</v>
+        <v>-1.980618569675606</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.090596541735323</v>
+        <v>-1.245672528423626</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9718172983479079</v>
+        <v>-1.030306076292909</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.821224727861399</v>
+        <v>-2.87288253800206</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.545892569396479</v>
+        <v>-1.601676665128444</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.85005429075629</v>
+        <v>-1.904798539838573</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.856531524139982</v>
+        <v>-2.009639243659755</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.37091751575695</v>
+        <v>-1.624543125002774</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.7425213675213627</v>
+        <v>-1.099287839569428</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.114781605579147</v>
+        <v>-1.472629269802809</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.7475801221748029</v>
+        <v>-1.110550426944499</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.5427079139388837</v>
+        <v>-0.9060017597561085</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8606137336468294</v>
+        <v>-1.222065929175407</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.06066</t>
+          <t>X &gt; 0.06047</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-10.43087816250755</v>
+        <v>-10.22520925334966</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.967630253728458</v>
+        <v>-7.88508893235791</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.970918052539716</v>
+        <v>-5.929106878338544</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.50934602126523</v>
+        <v>-2.407588715792706</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.9957014012788363</v>
+        <v>-0.975845009738606</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.190484883446395</v>
+        <v>1.19345840134438</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4176187513923679</v>
+        <v>0.5409876377618303</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.812704273237827</v>
+        <v>1.925977856210416</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6562399127855727</v>
+        <v>-0.5273374566773725</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.639280344475502</v>
+        <v>-1.390343222803956</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.992536140121665</v>
+        <v>-1.741283580642033</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.02962518652896051</v>
+        <v>0.2716336825766419</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3695691144853228</v>
+        <v>0.6068049490538527</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.5666223452919823</v>
+        <v>0.8023927392739267</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.138333998347832</v>
+        <v>-0.8974172249732959</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.7524789696469654</v>
+        <v>-0.5113636363636331</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.04975258011387496</v>
+        <v>0.1880525599922223</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.5991915320137906</v>
+        <v>0.7082118561710402</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.9421578850518344</v>
+        <v>0.9241032370953661</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.67763157894737</v>
+        <v>1.527615713730057</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.134431169949416</v>
+        <v>0.9850695457640271</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.269002430096279</v>
+        <v>1.244992547472535</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.673024765132709</v>
+        <v>1.647436093210764</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.175142497594194</v>
+        <v>1.280822018456476</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.07233</t>
+          <t>X &gt; 0.07213</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-8.242649324532522</v>
+        <v>-8.528065158544749</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-8.462223129046521</v>
+        <v>-8.862841956894563</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-6.979609629379219</v>
+        <v>-7.172436930662023</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.591362126245848</v>
+        <v>-2.977982370683726</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.426019666371943</v>
+        <v>-1.664407654822988</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.8019612731654604</v>
+        <v>0.433439492788267</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.069911467642051</v>
+        <v>1.835878780368709</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.066867026205117</v>
+        <v>2.826702868610553</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.04715860143184614</v>
+        <v>-0.1774952286625577</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2164727277049394</v>
+        <v>-0.4427966915010799</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.7074195830385861</v>
+        <v>-0.9301583691361017</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.309404880833455</v>
+        <v>1.329163293405742</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.715525907244277</v>
+        <v>1.728843866143542</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.749271137026241</v>
+        <v>1.761572096295929</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.325033775539957</v>
+        <v>0.3420074789184184</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.6649917843450197</v>
+        <v>0.6825872942624187</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.04110217182874</v>
+        <v>1.056284370482913</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.114416161652358</v>
+        <v>1.966672093057674</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.976417742841107</v>
+        <v>1.674949260784032</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.419871794871796</v>
+        <v>2.115602177351036</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.158722667925119</v>
+        <v>2.84209154237994</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.08276761228251</v>
+        <v>2.925763024558492</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.101132522354384</v>
+        <v>3.105467004319976</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.025191183085916</v>
+        <v>3.029634751096701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.08401</t>
+          <t>X &gt; 0.0838</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>326</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-10.34078807241746</v>
+        <v>-10.56855795680546</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-7.504737649878408</v>
+        <v>-7.590081743107085</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.839241286920284</v>
+        <v>-4.960470755374708</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.504254112308558</v>
+        <v>-2.490233343891873</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4304995070887045</v>
+        <v>-0.704811695227022</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6712992522595371</v>
+        <v>0.5634845083705784</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.337457510449411</v>
+        <v>2.403849561599358</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.888171157613783</v>
+        <v>3.954906409529215</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.2711506372705585</v>
+        <v>0.3378570060780604</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.197806724718383</v>
+        <v>-0.1301806211779422</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5332035551640217</v>
+        <v>-0.4658770765769944</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4072147364830272</v>
+        <v>0.4748857150969599</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.8071137618983286</v>
+        <v>0.8761138921432874</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.195513048424949</v>
+        <v>1.264791113257672</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.6829303857343092</v>
+        <v>-0.6128643794448436</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.5218857614480541</v>
+        <v>0.5912786400591301</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.912182311201569</v>
+        <v>1.981751746984095</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.301343744811668</v>
+        <v>2.181789091943401</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.707894854686309</v>
+        <v>2.397680472867727</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.894938650306742</v>
+        <v>2.584526282835753</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.965235173824134</v>
+        <v>2.651736212430698</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.19602858443919</v>
+        <v>3.072832147046057</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.47080375092132</v>
+        <v>3.540549012583405</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.394862411652852</v>
+        <v>3.46471675936013</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.09568</t>
+          <t>X &gt; 0.09546</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-13.52542252099243</v>
+        <v>-13.78844858944673</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-11.09884915920109</v>
+        <v>-11.17119586750134</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-7.883454313320215</v>
+        <v>-8.006235553405361</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.102865604041455</v>
+        <v>-4.274745128403666</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.097348872211569</v>
+        <v>-1.64757263798797</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.337006752031165</v>
+        <v>1.345396577160763</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.185863466419093</v>
+        <v>3.400391243434086</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.15449983213648</v>
+        <v>5.360985768830275</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.7016338746872037</v>
+        <v>0.9248610104464703</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.07220153608222546</v>
+        <v>0.1519453344099801</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.9214377745848665</v>
+        <v>-0.6933980085027258</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.297595662764202</v>
+        <v>0.5203899014821118</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2966999498950429</v>
+        <v>0.516630819700616</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.8244068092726735</v>
+        <v>1.041820599970443</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.9581199353826122</v>
+        <v>-0.7357256826847376</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.7605356198567534</v>
+        <v>0.9780642243328757</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.124569266531793</v>
+        <v>2.336684400788243</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.394117685642506</v>
+        <v>2.604978025325266</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.861177178162336</v>
+        <v>2.074600749533175</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.048220973782769</v>
+        <v>2.261446559501202</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.2540842351968</v>
+        <v>2.465169048251589</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.803597344348198</v>
+        <v>2.016188758484283</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.827436181242312</v>
+        <v>3.036932127682761</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.751494841973845</v>
+        <v>2.961099874459485</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.1074</t>
+          <t>X &gt; 0.1071</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>219</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-11.59267344194989</v>
+        <v>-11.74895522154007</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-9.009296920395123</v>
+        <v>-8.930578866736738</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.220686882198159</v>
+        <v>-5.187398616921371</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.107996177126473</v>
+        <v>-4.090397885232882</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.09294408351157557</v>
+        <v>-0.353790167734914</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.476455728481838</v>
+        <v>3.270033278749139</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.616831605560236</v>
+        <v>3.683223656710183</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.534623992005137</v>
+        <v>6.601359243920569</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.009930011365668</v>
+        <v>2.07663638017317</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.7794735960300372</v>
+        <v>0.847099699570478</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3160301505532601</v>
+        <v>-0.2487036719662328</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.514464987067733</v>
+        <v>3.582135965681665</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.5634897503157461</v>
+        <v>0.6324898805607049</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.168616957546234</v>
+        <v>2.237895022378957</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.5964437093765156</v>
+        <v>0.6665097156659812</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.648124763564098</v>
+        <v>1.717517642175174</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.710378101378652</v>
+        <v>4.779947537161178</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.235531671584738</v>
+        <v>3.305243819641362</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.995033829950344</v>
+        <v>3.064514195999479</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.551940639269404</v>
+        <v>4.621223019666132</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.552119225705248</v>
+        <v>3.6220558471339</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.476164170062638</v>
+        <v>3.546209885724799</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>4.664181345677186</v>
+        <v>4.733926607339271</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5.04486101097492</v>
+        <v>5.114715358682197</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.119</t>
+          <t>X &gt; 0.1188</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-13.35998528009635</v>
+        <v>-13.74447405643715</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-11.37771797302671</v>
+        <v>-11.48857727965743</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7.829949765433646</v>
+        <v>-8.017809627479444</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-6.427340962224683</v>
+        <v>-6.647430313588842</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.147108101746078</v>
+        <v>-4.379054119469451</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.331061802265992</v>
+        <v>1.31620176994381</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.145497257513547</v>
+        <v>2.426314259930557</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.09974684479922</v>
+        <v>6.358629130966953</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.90845867701762</v>
+        <v>2.189589997092185</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.134623266248191</v>
+        <v>1.416674321055694</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.8798820042630098</v>
+        <v>1.164418173743925</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.775391275391279</v>
+        <v>4.043563507138046</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.121799527803603</v>
+        <v>2.394085650808243</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.487744304070837</v>
+        <v>3.751954142782701</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.770612006832479</v>
+        <v>2.04117926625478</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.836571527353328</v>
+        <v>2.109250398724086</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.818879949606519</v>
+        <v>4.080596419641346</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.126594946209657</v>
+        <v>2.396808347399116</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.342718109141472</v>
+        <v>2.612699728323442</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>4.646164021164026</v>
+        <v>4.904808696186208</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.573863083065532</v>
+        <v>3.835946738746486</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.439706969221866</v>
+        <v>2.707469198390015</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.243582664804528</v>
+        <v>3.508259700345754</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.225842383737124</v>
+        <v>4.485059026069855</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.1307</t>
+          <t>X &gt; 0.1305</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-11.4380965610303</v>
+        <v>-12.53655263490436</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-8.384296920395123</v>
+        <v>-9.190347838162147</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-4.198997384481267</v>
+        <v>-4.796359010195488</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.912790697674424</v>
+        <v>-4.274745128403666</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.403060482698464</v>
+        <v>-2.758683749099077</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.784104130308329</v>
+        <v>1.749270091319289</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.886237998254295</v>
+        <v>3.446457209898071</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.982683352735734</v>
+        <v>7.489233419465975</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.899199417758375</v>
+        <v>4.444300848294262</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.125364006988946</v>
+        <v>3.671385172257772</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.399723274104282</v>
+        <v>3.328160863802417</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.995629370629374</v>
+        <v>4.901263312206268</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.87113815214223</v>
+        <v>3.77810124535015</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.899781341107875</v>
+        <v>4.79159027013813</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.990850102070574</v>
+        <v>2.898879071323002</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.960910151691955</v>
+        <v>2.875982042648708</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.326816457543032</v>
+        <v>5.211200708140368</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.721833041447752</v>
+        <v>3.254508152467338</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>3.470399533391664</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>5.625</v>
+        <v>6.12638114582883</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>5.081799591002046</v>
+        <v>5.5838349778628</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.755844535359429</v>
+        <v>4.273421115219129</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.655619701841566</v>
+        <v>5.165179778318461</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>5.829678362573098</v>
+        <v>6.323915426329769</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.1424</t>
+          <t>X &gt; 0.1421</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>144</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-11.60515588850942</v>
+        <v>-11.9741804467653</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-8.87040803150623</v>
+        <v>-8.836735022892888</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.143441828925702</v>
+        <v>-6.108087405257216</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-4.079457364341081</v>
+        <v>-4.043263646922178</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.055838260476243</v>
+        <v>-2.990165230580565</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.992437463641657</v>
+        <v>2.057912066627928</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.302904664920959</v>
+        <v>3.369296716070906</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.496572241624619</v>
+        <v>6.563307493540051</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.371421639980589</v>
+        <v>2.438128008788091</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.9031417847667171</v>
+        <v>0.970767888307158</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.871945496326497</v>
+        <v>1.939271974913524</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.065073815073816</v>
+        <v>5.132744793687749</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.24613815214223</v>
+        <v>3.315138282387188</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.719225785552318</v>
+        <v>3.788503850385041</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.671405657626131</v>
+        <v>1.741471663915597</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.572021262803069</v>
+        <v>1.641414141414145</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.521260901987475</v>
+        <v>3.590830337770001</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.332944152558866</v>
+        <v>1.40265630061549</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.243511759935124</v>
+        <v>2.312992125984259</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.819444444444443</v>
+        <v>3.888726824841171</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>3.970688479890931</v>
+        <v>4.040625101319584</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.200288979803879</v>
+        <v>3.27033469546604</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>4.169508590730452</v>
+        <v>4.239253852392537</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>4.788011695906441</v>
+        <v>4.857866043613718</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.1541</t>
+          <t>X &gt; 0.1538</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-9.771682381360549</v>
+        <v>-9.73840808904172</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.480841635842282</v>
+        <v>-8.44716862722894</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.042493319440609</v>
+        <v>-5.007138895772123</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-6.569294762715067</v>
+        <v>-6.533101045296164</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.682532027413913</v>
+        <v>-3.616858997518236</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.5696732359993746</v>
+        <v>0.6351478389856453</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.235831494189256</v>
+        <v>2.302223545339203</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.396301238914596</v>
+        <v>4.463036490830028</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.998792913693329</v>
+        <v>2.065499282500831</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.2249575029239</v>
+        <v>1.292583606464341</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1266994901233645</v>
+        <v>-0.05937301153633712</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.659247256808236</v>
+        <v>3.726918235422168</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.534756038321092</v>
+        <v>2.603756168566051</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.126407357368031</v>
+        <v>3.195685422200754</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.7845564019944646</v>
+        <v>-0.7144903957049991</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.002504482454391</v>
+        <v>-0.9331116038433152</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.302426213640594</v>
+        <v>1.37199564942312</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4285734626172868</v>
+        <v>-0.3588613145606629</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.6005578303958359</v>
+        <v>0.6700381964449704</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.413617886178862</v>
+        <v>2.482900266575591</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.683425607262201</v>
+        <v>2.753362228690854</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.794462421538299</v>
+        <v>1.86450813720046</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.695253848183029</v>
+        <v>3.764999109845114</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.245328769077155</v>
+        <v>5.315183116784432</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.1657</t>
+          <t>X &gt; 0.1654</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>108</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.377825109454498</v>
+        <v>-7.344550817135669</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.935222846321047</v>
+        <v>-4.901549837707705</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.523071458555329</v>
+        <v>-4.487717034886842</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.162790697674417</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.9725049271429071</v>
+        <v>-0.9068318972472298</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.992437463641657</v>
+        <v>2.057912066627928</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.071423183439478</v>
+        <v>3.137815234589425</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.570646315698696</v>
+        <v>5.637381567614128</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.90845867701762</v>
+        <v>1.975165045825122</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.060549192174122</v>
+        <v>2.128175295714563</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.907666407666412</v>
+        <v>3.975337386280344</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.857249263253344</v>
+        <v>1.926249393498303</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.635892452218989</v>
+        <v>1.705170517051712</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-2.726742490522021</v>
+        <v>-2.656676484232555</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-1.205756514974709</v>
+        <v>-1.136363636363633</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1.437927568654146</v>
+        <v>1.507497004436672</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-2.370759551144843</v>
+        <v>-2.301047403088219</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.3027845363611803</v>
+        <v>-0.2333041703120458</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>1.736111111111114</v>
+        <v>1.805393491507843</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.118836628039084</v>
+        <v>2.188773249467737</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>1.116955646470551</v>
+        <v>1.187001362132712</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.317656738878604</v>
+        <v>2.387402000540689</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.093567251461984</v>
+        <v>4.163421599169261</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.1774</t>
+          <t>X &gt; 0.1771</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>95</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-8.410963511013954</v>
+        <v>-8.377689218695124</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.535612709868808</v>
+        <v>-4.501939701255466</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.922681595007575</v>
+        <v>-4.887327171339088</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.531211750305999</v>
+        <v>-3.495018032887096</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.419307938354159</v>
+        <v>2.484980968249836</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.606472551360945</v>
+        <v>2.671947154347215</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.991501156149035</v>
+        <v>5.057893207298982</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.923472826419939</v>
+        <v>8.990208078335371</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.754462575653108</v>
+        <v>4.821168944460609</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.033258743831041</v>
+        <v>5.100884847371482</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.254986431999015</v>
+        <v>4.322312910586042</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.133787265366223</v>
+        <v>7.201458243980156</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.956664467931709</v>
+        <v>5.025664598176668</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.735307656897355</v>
+        <v>4.804585721730078</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.9184816810179441</v>
+        <v>0.9885476873074097</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.513541730639325</v>
+        <v>1.582934609250401</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.484711194385135</v>
+        <v>3.554280630167661</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.830798537499625</v>
+        <v>-0.7610863894430011</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.490587783326937</v>
+        <v>1.560068149376072</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.782894736842103</v>
+        <v>3.852177117238831</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>4.292325906791525</v>
+        <v>4.362262528220178</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>3.163739272201539</v>
+        <v>3.2337849878637</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>4.491146017631046</v>
+        <v>4.560891279293131</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.573099415204673</v>
+        <v>7.642953762911951</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.1891</t>
+          <t>X &gt; 0.1888</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>80</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-16.1741214057508</v>
+        <v>-16.14084711343197</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-9.009296920395123</v>
+        <v>-8.975623911781781</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.94899738448126</v>
+        <v>-7.913642960812773</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.162790697674417</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.528060482698457</v>
+        <v>-1.46238745280278</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.340895869691671</v>
+        <v>-1.275421266705401</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.636237998254295</v>
+        <v>1.702630049404242</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.357683352735727</v>
+        <v>6.424418604651159</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.375364006988939</v>
+        <v>4.442990110529379</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.149723274104275</v>
+        <v>2.217049752691302</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.620629370629366</v>
+        <v>5.688300349243299</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.24613815214223</v>
+        <v>3.315138282387188</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.274781341107868</v>
+        <v>4.344059405940591</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.576816457543039</v>
+        <v>1.646385893325565</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.278166958552255</v>
+        <v>-2.208454810495631</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.687956204379574</v>
+        <v>1.757436570428709</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.374999999999993</v>
+        <v>4.444282380396722</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>5.081799591002046</v>
+        <v>5.151736212430698</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>3.755844535359429</v>
+        <v>3.82589025102159</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.280619701841566</v>
+        <v>5.350364963503651</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>10.2046783625731</v>
+        <v>10.27453271028038</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.2008</t>
+          <t>X &gt; 0.2004</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-17.44223734777978</v>
+        <v>-17.40896305546095</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-10.5310360508299</v>
+        <v>-10.49736304221656</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-9.072185790278361</v>
+        <v>-9.036831366609874</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-8.336703741152675</v>
+        <v>-8.300510023733771</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-2.904872076901356</v>
+        <v>-2.839199047005678</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-1.268432101575733</v>
+        <v>-1.202957498589463</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.306527853326756</v>
+        <v>2.372919904476703</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.375799294764711</v>
+        <v>6.442534546680143</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.968039997468509</v>
+        <v>5.034746366276011</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.092755311336767</v>
+        <v>7.160381414877207</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>5.917839216133252</v>
+        <v>5.98516569472028</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7.088020674977201</v>
+        <v>7.155691653591134</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>5.963529456490058</v>
+        <v>6.032529586735016</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.735415319461886</v>
+        <v>0.8054813257513516</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>1.330475369083267</v>
+        <v>1.399868247694343</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.645657037253173</v>
+        <v>2.715226473035699</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-1.807152465798623</v>
+        <v>-1.737440317741999</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.756796784089708</v>
+        <v>2.826277150138843</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>5.842391304347828</v>
+        <v>5.911673684744557</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>5.223235839707264</v>
+        <v>5.293281555369425</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>12.66844647851513</v>
+        <v>12.73830082622241</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.09399453627818</v>
+        <v>10.12726882859701</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.758819021633855</v>
+        <v>9.792492030247196</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.768393919866568</v>
+        <v>9.803748343535055</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.156049882035724</v>
+        <v>6.192243599454628</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.58788154628705</v>
+        <v>11.65355457618273</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.77504615929384</v>
+        <v>11.84052076228011</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.00218002723981</v>
+        <v>11.06857207838976</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.926523932445875</v>
+        <v>4.993259184361307</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.968039997468509</v>
+        <v>5.034746366276011</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.643479949017916</v>
+        <v>5.711106052558357</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.917839216133252</v>
+        <v>5.98516569472028</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.638745312658351</v>
+        <v>5.706416291272284</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.862080181127745</v>
+        <v>8.931080311372703</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.64072337009339</v>
+        <v>8.710001434926113</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>7.981792131056089</v>
+        <v>8.051858137345555</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>6.993483124209689</v>
+        <v>7.063052559992215</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>6.888499708114409</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.655347508727395</v>
+        <v>5.72482787477653</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>4.393115942028977</v>
+        <v>4.462398322425706</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>3.849915533031023</v>
+        <v>3.919852154459676</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>8.121786564344951</v>
+        <v>8.191832280007112</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>1.150184919232878</v>
+        <v>1.219930180894963</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>5.422069666920926</v>
+        <v>5.491924014628204</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>98</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.591184716698187</v>
+        <v>9.624459009017016</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.215192875523243</v>
+        <v>7.248865884136585</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.857125064498334</v>
+        <v>9.892479488166821</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.020882771713339</v>
+        <v>3.057076489132243</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.778061966281129</v>
+        <v>8.843734996176806</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.944818416022613</v>
+        <v>8.010293019008884</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.212768610499189</v>
+        <v>9.279160661649136</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.811764985388798</v>
+        <v>2.87850023730423</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.853281050411432</v>
+        <v>2.919987419218934</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.099853802907305</v>
+        <v>3.167479906447745</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.435437559818567</v>
+        <v>6.502764038405594</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.135935493078357</v>
+        <v>5.203606471692289</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.113485090917742</v>
+        <v>9.1824852211627</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.871720116618071</v>
+        <v>7.940998181450794</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>7.21278887758077</v>
+        <v>7.282854883870236</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.767032600671548</v>
+        <v>5.836425479282624</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>5.632938906522625</v>
+        <v>5.702508342305151</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>6.548363653692647</v>
+        <v>6.618075801749271</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>5.744078653359161</v>
+        <v>5.813559019408295</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.869897959183675</v>
+        <v>2.939180339580403</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.32669755018572</v>
+        <v>2.396634171614373</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>5.31196698433903</v>
+        <v>5.382012700001191</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.4847013344946305</v>
+        <v>0.5544465961567155</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>3.469984485022081</v>
+        <v>3.539838832729359</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>129</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.44215766401665</v>
+        <v>11.47543195633548</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.455819358674638</v>
+        <v>6.48949236728798</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.99286308063502</v>
+        <v>12.02821750430351</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.17829457364342</v>
+        <v>8.214488291062324</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.13860618396819</v>
+        <v>10.20427921386387</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.550576998525372</v>
+        <v>9.616051601511643</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12.65367985871941</v>
+        <v>12.72007190986935</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.948768624053571</v>
+        <v>7.015503875969003</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.765478487525812</v>
+        <v>7.832184856333313</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.591583739220553</v>
+        <v>9.658910217807581</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.986908440396817</v>
+        <v>7.05457941901075</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.738386214157735</v>
+        <v>9.807386344402694</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.966641806224153</v>
+        <v>8.035919871056876</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>7.307710567186852</v>
+        <v>7.377776573476318</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>4.801995423009792</v>
+        <v>4.871388301620868</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.218289325760082</v>
+        <v>6.287858761542608</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>6.113305909664803</v>
+        <v>6.183018057721426</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.003847677247784</v>
+        <v>4.073328043296918</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.090116279069761</v>
+        <v>1.15939865946649</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.5469158700718069</v>
+        <v>0.6168524915004596</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>3.571736008227653</v>
+        <v>3.641781723889814</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.02945781753828669</v>
+        <v>0.04028744412379837</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>2.995376036991701</v>
+        <v>3.065230384698978</v>
       </c>
     </row>
     <row r="9">
@@ -6077,2208 +6077,2208 @@
         <v>169</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10.82292001436754</v>
+        <v>10.85619430668637</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.67117645238594</v>
+        <v>11.70484946099928</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.59833989362525</v>
+        <v>12.63369431729374</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.925966698775291</v>
+        <v>8.962160416194195</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.152412890082601</v>
+        <v>9.218085919978279</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.74786152675803</v>
+        <v>8.8133361297443</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>12.70872320535489</v>
+        <v>12.77511525650484</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.696440749185442</v>
+        <v>7.763176001100874</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.737956814208076</v>
+        <v>7.804663183015577</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.555837379770004</v>
+        <v>7.623463483310445</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.421912623216713</v>
+        <v>8.48923910180374</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.367670790747709</v>
+        <v>6.435341769361642</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.793475430248741</v>
+        <v>8.862475560493699</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.980402642883028</v>
+        <v>8.049680707715751</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>7.321471403845727</v>
+        <v>7.391537410135193</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>4.957951571810291</v>
+        <v>5.027344450421367</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.59900580665547</v>
+        <v>6.668575242437996</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>7.677454343222905</v>
+        <v>7.747166491279529</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>6.118429577160633</v>
+        <v>6.187909943209768</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.755177514792898</v>
+        <v>2.824459895189626</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.211977105794944</v>
+        <v>2.281913727223596</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.911169979146422</v>
+        <v>3.981215694808583</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.819081240303106</v>
+        <v>1.888826501965191</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>3.518287830028719</v>
+        <v>3.588142177735996</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.09113</t>
+          <t>X &lt; -0.09116</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>212</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.942701024155738</v>
+        <v>8.975975316474567</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10.94397410764227</v>
+        <v>10.97764711625561</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>12.30801196131314</v>
+        <v>12.34336638498163</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.790480330362975</v>
+        <v>8.826674047781879</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.425210545338928</v>
+        <v>8.490883575234605</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.677795719093368</v>
+        <v>7.743270322079638</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.57782678330103</v>
+        <v>11.64421883445097</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.560954380773126</v>
+        <v>7.627689632688558</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.667891006543414</v>
+        <v>6.734597375350916</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.828635035026331</v>
+        <v>6.896261138566771</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.168414862889321</v>
+        <v>6.235741341476349</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.618292922031237</v>
+        <v>2.68596390064517</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.065386978433303</v>
+        <v>4.833829871172235</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.147422850541837</v>
+        <v>4.612750994725644</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4.488491611504536</v>
+        <v>3.954607697145086</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>2.725061095088179</v>
+        <v>2.212546020957234</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.062665514146808</v>
+        <v>2.837700447316173</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>5.316172664089265</v>
+        <v>5.385884812145889</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.645503374190888</v>
+        <v>3.714983740240022</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.002358490566039</v>
+        <v>1.071640870962767</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.4591580815680842</v>
+        <v>0.529094702996737</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.798297365548116</v>
+        <v>1.868343081210277</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.601374418822694</v>
+        <v>1.671119680484779</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.468829305969322</v>
+        <v>2.5386836536766</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.07945</t>
+          <t>X &lt; -0.0795</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>269</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.056505900522275</v>
+        <v>9.089780192841104</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.04236359621004</v>
+        <v>12.07603660482339</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.70967420223461</v>
+        <v>11.7450286259031</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.043851368746239</v>
+        <v>8.080045086165143</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.047585273759097</v>
+        <v>8.113258303654774</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.02072774654448</v>
+        <v>6.086202349530751</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.675905894933258</v>
+        <v>9.742297946083205</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.81432541915639</v>
+        <v>6.881060671071822</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.74883041406833</v>
+        <v>5.815536782875832</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.60599131326201</v>
+        <v>4.67361741680245</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.142343200303543</v>
+        <v>4.20966967889057</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.01823084664413</v>
+        <v>2.085901825258063</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.449841855845939</v>
+        <v>4.283772968734048</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.837048999100439</v>
+        <v>4.431697782324363</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3.806370548167223</v>
+        <v>3.4045507947069</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.799200114517234</v>
+        <v>1.415911886391591</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.89558969174378</v>
+        <v>3.729719226658887</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>4.162353487544401</v>
+        <v>4.232065635601025</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.519740590996669</v>
+        <v>2.589220957045804</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.8480483271375547</v>
+        <v>0.9173307075342834</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.06689929375631465</v>
+        <v>0.003037327672338108</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.6006400743928921</v>
+        <v>0.6706857900550531</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.5036680289791207</v>
+        <v>0.5734132906412057</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.7994739016065537</v>
+        <v>0.8693282493138312</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.06777</t>
+          <t>X &lt; -0.06783</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>368</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.028581296951913</v>
+        <v>9.061855589270742</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.233946322848119</v>
+        <v>9.267619331461461</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.68613775065387</v>
+        <v>9.721492174322357</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.729101194217478</v>
+        <v>5.765294911636381</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.985453030815044</v>
+        <v>7.051126060710722</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.469914941119136</v>
+        <v>4.535389544105406</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.670021782038084</v>
+        <v>6.736413833188031</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.499575244627628</v>
+        <v>4.566310496543061</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.919469688028634</v>
+        <v>2.986176056836136</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.686174817799753</v>
+        <v>2.753800921340193</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.230804355185356</v>
+        <v>3.298130833772383</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2915327915327879</v>
+        <v>-0.2238618129188552</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.450745198212687</v>
+        <v>1.355678822927736</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.937824819368743</v>
+        <v>1.675140487021679</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.735415319461886</v>
+        <v>0.4764566489005873</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.7869971082136971</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.555077327108251</v>
+        <v>2.456006489531525</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>2.993572171882533</v>
+        <v>3.063284319939157</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.307521421770879</v>
+        <v>1.377001787820014</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.1358695652173978</v>
+        <v>0.2051519456141264</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.9508091046501264</v>
+        <v>-0.8808724832214736</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.4832858994231657</v>
+        <v>-0.4132401837610047</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.4802498633758319</v>
+        <v>-0.4105046017137468</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.53076531909484</v>
+        <v>0.6006196668021175</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.0561</t>
+          <t>X &lt; -0.05617</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>498</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.925878594249205</v>
+        <v>9.959152886568035</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8.19070307960488</v>
+        <v>8.224376088218222</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9.55100261551874</v>
+        <v>9.586357039187227</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.837209302325583</v>
+        <v>5.873403019744487</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.871939517301534</v>
+        <v>6.937612547197212</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.859104130308317</v>
+        <v>2.924578733294588</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.886237998254295</v>
+        <v>4.952630049404242</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.407683352735731</v>
+        <v>3.474418604651163</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.849199417758363</v>
+        <v>2.915905786565865</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.275364006988937</v>
+        <v>3.342990110529378</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.949723274104272</v>
+        <v>3.0170497526913</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6706293706293707</v>
+        <v>0.7383003492433033</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.269184244326595</v>
+        <v>2.215138282387187</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.57297411219222</v>
+        <v>2.394059405940595</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.512436447452103</v>
+        <v>1.335916108360038</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.3002675814108287</v>
+        <v>0.1303030303030255</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2.575812441478774</v>
+        <v>2.520634390319543</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>3.274041876789113</v>
+        <v>3.343754024845737</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.68695218831531</v>
+        <v>2.756432554364444</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.6651606425702852</v>
+        <v>0.7344430229670138</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.07884297927908079</v>
+        <v>-0.008906357850428037</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.4476116036325237</v>
+        <v>0.5176573192946847</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.1199771315604394</v>
+        <v>0.1897223932225245</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.2448390051433833</v>
+        <v>0.3146933528506608</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.04442</t>
+          <t>X &lt; -0.04451</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>675</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.72765112009854</v>
+        <v>10.76092541241737</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.029107806340477</v>
+        <v>8.062780814953818</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>9.839038066035727</v>
+        <v>9.874392489704213</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.614166466284232</v>
+        <v>6.650360183703135</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.692028143594008</v>
+        <v>6.757701173489686</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.038720083040964</v>
+        <v>3.104194686027235</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.595248337988423</v>
+        <v>3.66164038913837</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.464404179914467</v>
+        <v>3.531139431829899</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.915078295158658</v>
+        <v>2.98178466396616</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.879795321612278</v>
+        <v>2.947421425152719</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.301865076172227</v>
+        <v>3.369191554759254</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.397955810806629</v>
+        <v>1.465626789420561</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.728386672852288</v>
+        <v>2.705832521678175</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.895151711478242</v>
+        <v>2.780174620120803</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.828813065033536</v>
+        <v>2.712873272318689</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.238687929469734</v>
+        <v>2.125576294704807</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.437927568654139</v>
+        <v>3.4141373726155</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>3.629240448855164</v>
+        <v>3.698952596911788</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.808326574749934</v>
+        <v>2.877806940799069</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.106481481481481</v>
+        <v>2.17576386187821</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.118836628039077</v>
+        <v>1.188773249467729</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.191029720544627</v>
+        <v>1.261075436206788</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.021360442582306</v>
+        <v>1.091105704244391</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.649122807017541</v>
+        <v>0.7189771547248185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.03275</t>
+          <t>X &lt; -0.03284</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>10.33037803181951</v>
+        <v>10.323116850532</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.84559621796258</v>
+        <v>6.835186899029033</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.318156721255519</v>
+        <v>7.311582264412451</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.354644622910506</v>
+        <v>4.346375992717455</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.55180453417443</v>
+        <v>4.573648583233251</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.364390969453432</v>
+        <v>1.382236390952251</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.716384229975333</v>
+        <v>1.736413833188024</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.437829584456772</v>
+        <v>1.458202388434948</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.479345649479406</v>
+        <v>1.499689570349652</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.267939934997933</v>
+        <v>1.289836957376224</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.87975701988605</v>
+        <v>1.901734437375985</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.48817717715356</v>
+        <v>1.510372421315374</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.232624638628721</v>
+        <v>2.189012156261064</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.967847857455105</v>
+        <v>1.855320667201852</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.942599537736484</v>
+        <v>1.760240432684363</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.860458684423328</v>
+        <v>1.678951678951684</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>3.080766796143479</v>
+        <v>2.966848125569072</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.765851100138498</v>
+        <v>3.722696431039367</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.417640177291524</v>
+        <v>3.445289677773332</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.92748306997742</v>
+        <v>2.954169386046445</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.158549026667956</v>
+        <v>2.185634517515446</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>2.308327605336856</v>
+        <v>2.335777256671314</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>2.695969588974755</v>
+        <v>2.723246319435859</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.394294615394763</v>
+        <v>2.421425365647615</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02107</t>
+          <t>X &lt; -0.02118</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>8.675792830955899</v>
+        <v>8.730286907186589</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>7.139931209965077</v>
+        <v>7.106850315022349</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6.557863678983573</v>
+        <v>6.527937795200977</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.871514619649773</v>
+        <v>3.92494941149706</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.76353471455711</v>
+        <v>3.932801550633634</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.720853701491848</v>
+        <v>1.71426945494408</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.291040742679684</v>
+        <v>1.285963382737577</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.012486097161123</v>
+        <v>1.007751937984501</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.225528748804685</v>
+        <v>1.306971078662094</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.652379444381737</v>
+        <v>1.650893890598105</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.578907823460497</v>
+        <v>2.612238756127724</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.922175762381947</v>
+        <v>1.903936088074921</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.225071944059685</v>
+        <v>2.155344467954201</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.659032631985674</v>
+        <v>2.535640161954348</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.570415132217008</v>
+        <v>2.446664173708285</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.734811960477479</v>
+        <v>2.66455432118083</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.548177353322529</v>
+        <v>3.531614144832886</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.046122447132504</v>
+        <v>4.084648637780241</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.573184455886896</v>
+        <v>3.665331307270804</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.812769164513348</v>
+        <v>2.90308307064695</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.527966688331929</v>
+        <v>2.619380733569606</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.882674854050215</v>
+        <v>2.974941156975014</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.415847953348894</v>
+        <v>3.508259700345754</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.650845459902982</v>
+        <v>2.742177231419284</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.009397</t>
+          <t>X &lt; -0.009514</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>6.907889176259786</v>
+        <v>7.061604841505073</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.514512603414403</v>
+        <v>5.600254153161885</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.868462932979057</v>
+        <v>4.891194680008965</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.26804980530374</v>
+        <v>3.250473927630509</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.207038855049881</v>
+        <v>3.179759664493432</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.606123997857985</v>
+        <v>1.577461437071925</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.561734686996019</v>
+        <v>1.534472329059646</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.018279379225802</v>
+        <v>1.029856270433662</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8611199475596862</v>
+        <v>0.844638367853193</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.41178784804854</v>
+        <v>1.465219705751679</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.791870391400494</v>
+        <v>1.871993349240739</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.618639980708949</v>
+        <v>1.593243945792743</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.860935763290207</v>
+        <v>1.797221892208022</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.87936301441465</v>
+        <v>1.775214017752148</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.85920558379815</v>
+        <v>1.755305218585804</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>2.055594537074015</v>
+        <v>1.992097050236588</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>2.51950748744337</v>
+        <v>2.497449723112787</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.879640350417858</v>
+        <v>2.899662288639441</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.497756868831395</v>
+        <v>2.558035771493948</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.754568106312291</v>
+        <v>1.812791035523233</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.610038793659854</v>
+        <v>1.669712244388087</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.733419286189999</v>
+        <v>1.793599971394435</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.273975183569142</v>
+        <v>2.334386268430414</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.334246468885389</v>
+        <v>1.459619261545356</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.002279</t>
+          <t>X &lt; 0.00215</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.6106853703212</v>
+        <v>4.630626905656051</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.693191168540821</v>
+        <v>3.712605144421829</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.576942266127524</v>
+        <v>3.653165098572174</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.841446590461182</v>
+        <v>2.834166540423169</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.56043978227239</v>
+        <v>2.60442060658216</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.9987967641186017</v>
+        <v>1.094674173379424</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.17982570360671</v>
+        <v>1.277126337845381</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.7422885461644597</v>
+        <v>0.8707050767997089</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6248220992634046</v>
+        <v>0.7838463385828547</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.281829295807171</v>
+        <v>1.444051681654649</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.3755981415486</v>
+        <v>1.505797098763495</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.287074993971544</v>
+        <v>1.386283364105303</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.361849404796153</v>
+        <v>1.377770978777853</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.013363391028214</v>
+        <v>0.9974564335414442</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.396137030869724</v>
+        <v>1.380419560298435</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.406712489630316</v>
+        <v>1.422970405435869</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.803968423536659</v>
+        <v>1.853057876313336</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.805254933052424</v>
+        <v>1.887289870355438</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.383758542317928</v>
+        <v>1.497324808853399</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.9863177470775781</v>
+        <v>1.098752843408967</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.5493872636906758</v>
+        <v>0.6626462709724734</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.7922419848812225</v>
+        <v>0.9061190961519827</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.9076122629467775</v>
+        <v>0.9677146175749698</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.7254009980672507</v>
+        <v>0.7854427688221506</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.01395</t>
+          <t>X &lt; 0.01381</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2214</v>
+        <v>2207</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.246670673457118</v>
+        <v>4.256264799925432</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.14641865116203</v>
+        <v>3.180132295893166</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.011848700127203</v>
+        <v>3.051368325868943</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.054228662973941</v>
+        <v>2.157827398976991</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.670137715499742</v>
+        <v>1.776890199567418</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8663113375155334</v>
+        <v>0.9254816678318392</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.399751511767811</v>
+        <v>1.462788062948263</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.12119686624925</v>
+        <v>1.165836852166983</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8023525709115233</v>
+        <v>0.9626296907683027</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.469958601583535</v>
+        <v>1.635714918482378</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.455716964956011</v>
+        <v>1.548274334706669</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.248447224551825</v>
+        <v>1.314712459500875</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.32349494059509</v>
+        <v>1.366426126942088</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9038427129490358</v>
+        <v>0.9194096092844717</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.400838815388859</v>
+        <v>1.418737084851898</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.499284869524907</v>
+        <v>1.543419267299868</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.889598752032647</v>
+        <v>1.934847431787098</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.874949572613062</v>
+        <v>1.993672849078841</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.639401552166376</v>
+        <v>1.784610483472186</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.645776874435413</v>
+        <v>1.790296873150353</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.283244938788854</v>
+        <v>1.45667504342299</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.433125474835492</v>
+        <v>1.562070586318377</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.256229457939128</v>
+        <v>1.428751914115338</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.18028811867066</v>
+        <v>1.352919660892063</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.02563</t>
+          <t>X &lt; 0.02548</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.348350504361562</v>
+        <v>3.306944051226665</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.290863593248538</v>
+        <v>2.271865039604322</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.854373402035591</v>
+        <v>1.878442213956205</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.404451373782827</v>
+        <v>1.366372083625556</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9819796779441106</v>
+        <v>0.990404833255873</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.5265740098263976</v>
+        <v>0.5345425741945462</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8782058697402348</v>
+        <v>0.8473668915095089</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3586873687999912</v>
+        <v>0.3512674792492376</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.319882148682062</v>
+        <v>0.3355278211456891</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.072151155583313</v>
+        <v>1.090557460750532</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.048879561770008</v>
+        <v>1.042944404882697</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9944235828480217</v>
+        <v>0.9652404377032937</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6978872474377695</v>
+        <v>0.6462601159215708</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7419977530145587</v>
+        <v>0.6664357629972884</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.153576460219469</v>
+        <v>1.078313533943302</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.008414177456849</v>
+        <v>0.9327175172245603</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.422265511107263</v>
+        <v>1.346466408623471</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.317282095011983</v>
+        <v>1.266172656278442</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.009845048519722</v>
+        <v>1.023149704997593</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.9149718082964142</v>
+        <v>0.911936552101686</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.8392532574001095</v>
+        <v>0.8372200833984351</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.045328822224867</v>
+        <v>1.043632186505462</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.7157526591340684</v>
+        <v>0.7132681893101065</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.559231142589212</v>
+        <v>0.5567907747965037</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.03731</t>
+          <t>X &lt; 0.03714</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.522380268979383</v>
+        <v>2.523026257145311</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.703393812764531</v>
+        <v>1.687565357964871</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.454612589467381</v>
+        <v>1.441796681512116</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9109248644998118</v>
+        <v>0.9151317827847194</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.2689600014728626</v>
+        <v>0.2812787170928885</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1770224991144005</v>
+        <v>-0.1651381072419156</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.09294190886881637</v>
+        <v>0.1061322848736879</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2015565876517442</v>
+        <v>-0.1880487826019106</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.08552487434297973</v>
+        <v>-0.01340070112988201</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4819213840381238</v>
+        <v>0.5559655020282577</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7035808961691288</v>
+        <v>0.7554539286793727</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4836047621282518</v>
+        <v>0.5358385812462956</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2761642618028048</v>
+        <v>0.3078648769414585</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2635873112571332</v>
+        <v>0.2732835760263868</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6721210987111093</v>
+        <v>0.6821847650764568</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.4683784115874019</v>
+        <v>0.4780447249652156</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6181873951597723</v>
+        <v>0.627901950084329</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.6626249727140987</v>
+        <v>0.6949818723583121</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.4678404031094914</v>
+        <v>0.5223842535378225</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.2813317146059049</v>
+        <v>0.3578337822658924</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.3957009362935224</v>
+        <v>0.4733517696483531</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.5065919195148894</v>
+        <v>0.5844915973192855</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2581981771778885</v>
+        <v>0.2606117847452367</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.2196260456822188</v>
+        <v>0.2595738471539732</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.04898</t>
+          <t>X &lt; 0.0488</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2833</v>
+        <v>2831</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.947804103736203</v>
+        <v>1.949870186146093</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.436943416920407</v>
+        <v>1.493950481464786</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.121628054731673</v>
+        <v>1.181503011751424</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6386152777210157</v>
+        <v>0.6795936634307367</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.08234739353219567</v>
+        <v>0.1327585197614098</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1875906657535609</v>
+        <v>-0.1023646363853246</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.008995648623624675</v>
+        <v>0.04021358791989371</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1790865276302043</v>
+        <v>-0.1475377641032338</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2345566863257744</v>
+        <v>0.266064181497228</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4462897373655679</v>
+        <v>0.4787169672699676</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6004274994563872</v>
+        <v>0.6325427104377894</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.306698409023177</v>
+        <v>0.3391457173306591</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1541719787807025</v>
+        <v>0.1879360272779564</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1299981193947914</v>
+        <v>0.1430375595699189</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.5146512304203554</v>
+        <v>0.5280909409296513</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.2492699400517466</v>
+        <v>0.2623199555498559</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.3127021315021068</v>
+        <v>0.3258391561121528</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.3135761607138008</v>
+        <v>0.3480024936680977</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.212126987724659</v>
+        <v>0.2674083318123905</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.08159844742413469</v>
+        <v>0.1575592165549224</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.1594557858485004</v>
+        <v>0.2365119100640385</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.08350073020589122</v>
+        <v>0.1606659486549376</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.04059146322525464</v>
+        <v>0.1172317950119535</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.1058432054957947</v>
+        <v>0.1826923711775876</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.06066</t>
+          <t>X &lt; 0.06047</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.686040920931653</v>
+        <v>1.670384280343406</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.283229288600488</v>
+        <v>1.286643431703837</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.9257067075038563</v>
+        <v>0.931534704161848</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3324731724203076</v>
+        <v>0.3201035273586967</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.0878447626484018</v>
+        <v>0.08583589745102671</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.26644578508931</v>
+        <v>-0.268653077196106</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1401668764918114</v>
+        <v>-0.1607371248766398</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3655641921338884</v>
+        <v>-0.3858386736155879</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.03402326599685068</v>
+        <v>0.01356917972537275</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.194577832810694</v>
+        <v>0.1549779195371741</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2514181893585175</v>
+        <v>0.2116296984907677</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.07579314547777471</v>
+        <v>-0.1152408232405904</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1290314543706685</v>
+        <v>-0.1679125650704378</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1606614821021779</v>
+        <v>-0.199429912472425</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.117038153665959</v>
+        <v>0.07838557918771727</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.05343986306716175</v>
+        <v>0.01452427224398889</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.06041180332653795</v>
+        <v>-0.09920134360586985</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.1653952194218178</v>
+        <v>-0.1838368138912116</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.2210111869247768</v>
+        <v>-0.2194656034843447</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.3396739130434838</v>
+        <v>-0.3182898248360289</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2511939530006728</v>
+        <v>-0.2289571934156669</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.272877422492364</v>
+        <v>-0.2708126721599129</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.3380070826587769</v>
+        <v>-0.3362427863264017</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.2577493830916424</v>
+        <v>-0.2761131088902502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.07233</t>
+          <t>X &lt; 0.07213</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3025</v>
+        <v>3027</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.056496202659183</v>
+        <v>1.107756238523336</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.082687310879514</v>
+        <v>1.15258121642335</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.8584927600653884</v>
+        <v>0.8979941200550741</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2617903079121788</v>
+        <v>0.3165325397970804</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1123076961312535</v>
+        <v>0.1451076162307459</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1751609140849695</v>
+        <v>-0.1281497348184857</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3374462122720203</v>
+        <v>-0.3083824423774857</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.4656960483830588</v>
+        <v>-0.4364002049509352</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.07627786993090524</v>
+        <v>-0.04725210817098002</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.0410008267285491</v>
+        <v>-0.01160021523567423</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.02192353760889176</v>
+        <v>0.05115113517977932</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2381020955979736</v>
+        <v>-0.2414823310332821</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2887992242585611</v>
+        <v>-0.2915810852017415</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.29289093057033</v>
+        <v>-0.2955616813740676</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.1077646736550193</v>
+        <v>-0.1102275963202501</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1527487067706019</v>
+        <v>-0.1554866169109488</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.2012363477374919</v>
+        <v>-0.2038779589171895</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.3392230641628089</v>
+        <v>-0.3221136689581812</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.3211197032111883</v>
+        <v>-0.284642637492091</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.3786315615714742</v>
+        <v>-0.342363377279078</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.4730220734629427</v>
+        <v>-0.4361105511095928</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.4632667959917356</v>
+        <v>-0.4459063143681021</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.4662408401280302</v>
+        <v>-0.4686574935637182</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.4564786622202917</v>
+        <v>-0.4588666950714568</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.08401</t>
+          <t>X &lt; 0.0838</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3089</v>
+        <v>3093</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.08778335615397</v>
+        <v>1.117995330297937</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.7847828736846765</v>
+        <v>0.8008315401320161</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4712085357246636</v>
+        <v>0.4885764023265011</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1938233995254564</v>
+        <v>0.1937632641960789</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.02451895018075589</v>
+        <v>0.004794014378681766</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1412179308833004</v>
+        <v>-0.1299901212742611</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3160815893745763</v>
+        <v>-0.3227882260140333</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4796514845185342</v>
+        <v>-0.4861864806401144</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.09741566928224898</v>
+        <v>-0.1044419275358663</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.04659665086337128</v>
+        <v>-0.05378927755435825</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.01156704847637258</v>
+        <v>-0.01877498957674106</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.110654914623936</v>
+        <v>-0.1177744171118391</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1512149789100619</v>
+        <v>-0.1584271592633613</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1920413905679439</v>
+        <v>-0.1992330803541407</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.007968965119673044</v>
+        <v>0.000432237392296031</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.1206730470156359</v>
+        <v>-0.1279738332013309</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.267882960685796</v>
+        <v>-0.2750150104833509</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.3082251356692467</v>
+        <v>-0.2961202932208451</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.350666937184748</v>
+        <v>-0.3194368145842148</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3707969608794031</v>
+        <v>-0.3396433061945459</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.3774500855826872</v>
+        <v>-0.3460013441303857</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.401790534197346</v>
+        <v>-0.3895266849835721</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4313544081907992</v>
+        <v>-0.4382581780606642</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.4233566001980194</v>
+        <v>-0.4302846191732286</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.09568</t>
+          <t>X &lt; 0.09546</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3148</v>
+        <v>3151</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.138122204220807</v>
+        <v>1.168361338160594</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.9291694727888498</v>
+        <v>0.9455117349059208</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.625474057614035</v>
+        <v>0.6431393735720832</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2766032417195277</v>
+        <v>0.2949871156737984</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.02388141815407607</v>
+        <v>0.07170345628811958</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1817044609740535</v>
+        <v>-0.1832495495336985</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.3365108169115842</v>
+        <v>-0.3554507586765681</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5023040050392353</v>
+        <v>-0.5210345055477603</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1266462983339522</v>
+        <v>-0.1457492987152449</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.06011986397879809</v>
+        <v>-0.07912679310410908</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.01115952845415791</v>
+        <v>-0.007981852871274953</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.09139594582632071</v>
+        <v>-0.1103876052302866</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.08956935023194745</v>
+        <v>-0.1083278782706216</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1338633707350638</v>
+        <v>-0.1525397715348831</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.01789318094292724</v>
+        <v>-0.0007927523994553098</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.1284434604753457</v>
+        <v>-0.1471265360154277</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.2437065218547474</v>
+        <v>-0.2622588185173811</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.266435823485665</v>
+        <v>-0.2849514845532752</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.2217329805237043</v>
+        <v>-0.240345432106146</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.2379441624365413</v>
+        <v>-0.2565892519329012</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.2546015514924065</v>
+        <v>-0.273121111602272</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.216377686862792</v>
+        <v>-0.2349248457116673</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.3036927783108609</v>
+        <v>-0.322223868983663</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2972276094726496</v>
+        <v>-0.3157560869268679</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.1074</t>
+          <t>X &lt; 0.1071</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3196</v>
+        <v>3200</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7865562442336582</v>
+        <v>0.8001466753879143</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6068050379511618</v>
+        <v>0.6065444634900388</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.3172444557425464</v>
+        <v>0.31795070181537</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2115874117783179</v>
+        <v>0.2127442254623304</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.07393917632210645</v>
+        <v>-0.04336351745929079</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3048037726163813</v>
+        <v>-0.2915853947750406</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3132640247771405</v>
+        <v>-0.3174973985286158</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5118683284597765</v>
+        <v>-0.5158799028115197</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2034944470812405</v>
+        <v>-0.2078889257202832</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1184054634160461</v>
+        <v>-0.1229713082634092</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.04410657943265051</v>
+        <v>-0.04874545428037891</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3051811031860794</v>
+        <v>-0.3095203232349064</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1020065313625977</v>
+        <v>-0.1066929228448288</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2113384343132125</v>
+        <v>-0.2159094414114335</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.1029486498795009</v>
+        <v>-0.1077111898637071</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.1757939681582315</v>
+        <v>-0.180420161716917</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3850161993411376</v>
+        <v>-0.3893952105098037</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.2841007499326338</v>
+        <v>-0.2886170063783453</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.2680731614436169</v>
+        <v>-0.2725946308193414</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.375</v>
+        <v>-0.3793755471937814</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3058215406015776</v>
+        <v>-0.3103305999327048</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.3005969905942791</v>
+        <v>-0.3051216165611663</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.382501974730225</v>
+        <v>-0.3869046397453317</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.4085882206559361</v>
+        <v>-0.4129672897196244</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.119</t>
+          <t>X &lt; 0.1188</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3226</v>
+        <v>3229</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7761403743539148</v>
+        <v>0.8066752011263603</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.6565484753548034</v>
+        <v>0.6733908665433432</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4179567270062705</v>
+        <v>0.4361107337685084</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3067102265400052</v>
+        <v>0.3255126594118707</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1745589317853558</v>
+        <v>0.1919563549606096</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1448416156842782</v>
+        <v>-0.1447989623307961</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1911594732227329</v>
+        <v>-0.2081832592833734</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4213110951359482</v>
+        <v>-0.4380621349482112</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1770887649013133</v>
+        <v>-0.1940818829778976</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1308088325172321</v>
+        <v>-0.1476666887305598</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1164082479704405</v>
+        <v>-0.1333512343537322</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2850222661834749</v>
+        <v>-0.3017490182358671</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.1868244675673836</v>
+        <v>-0.2033802361313306</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.2663187825015143</v>
+        <v>-0.2827544254888466</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.1650617990113403</v>
+        <v>-0.1814402844750376</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1698876219629568</v>
+        <v>-0.1864099755665976</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2856178140313617</v>
+        <v>-0.3020071845483585</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1865828001364065</v>
+        <v>-0.2030452278062853</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.1996173022747243</v>
+        <v>-0.2161255817048868</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3347523219814263</v>
+        <v>-0.3511862246140964</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.2712508890227312</v>
+        <v>-0.2876202232128691</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.2048122180482466</v>
+        <v>-0.2212313831473907</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.2523830871265176</v>
+        <v>-0.2688300829359775</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.3098907632793555</v>
+        <v>-0.3262724925688048</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.1307</t>
+          <t>X &lt; 0.1305</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3255</v>
+        <v>3257</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.5523052039531962</v>
+        <v>0.6134987237134979</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4002239828700596</v>
+        <v>0.4478050082914322</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1676082321243584</v>
+        <v>0.199535806728413</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1730871649210002</v>
+        <v>0.1443825742150437</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.0999175258537619</v>
+        <v>0.06996907955374354</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1539114517265077</v>
+        <v>-0.1532838621252566</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2066715371980195</v>
+        <v>-0.236129877290935</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4066853418530769</v>
+        <v>-0.435877759540702</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2559993590000431</v>
+        <v>-0.2853167073216554</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2170189847516539</v>
+        <v>-0.245942937468179</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.2309376806080792</v>
+        <v>-0.2294334277368293</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3087400814673558</v>
+        <v>-0.3070346155777415</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2520247382435628</v>
+        <v>-0.2497331986409677</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3021711856915132</v>
+        <v>-0.2997269423912101</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.2076793096941358</v>
+        <v>-0.2049289620624961</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.2071866917036971</v>
+        <v>-0.2047658824075427</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3230915743392444</v>
+        <v>-0.3205258713803261</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1952169432195205</v>
+        <v>-0.2233184329289628</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.2062155747615364</v>
+        <v>-0.234439579172772</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3384857318195742</v>
+        <v>-0.3667418453009077</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.3110794759101694</v>
+        <v>-0.3390613335815686</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.2459208929488241</v>
+        <v>-0.2739103012950608</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.290633369411502</v>
+        <v>-0.318757197331216</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.3483170291319695</v>
+        <v>-0.3763730311995133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.1424</t>
+          <t>X &lt; 0.1421</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3271</v>
+        <v>3275</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.501402432694384</v>
+        <v>0.5131856336874989</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.3787990407345418</v>
+        <v>0.3768177018063312</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2314400395770662</v>
+        <v>0.2295609226823672</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.1118978468409324</v>
+        <v>0.1101253262695181</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.06768419815260529</v>
+        <v>0.06463136929800584</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1536048997920147</v>
+        <v>-0.1563808780020963</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2098690577067828</v>
+        <v>-0.2126190392956318</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3494203892782579</v>
+        <v>-0.3520171291683454</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.16881640695253</v>
+        <v>-0.1716322073551098</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1033270127979691</v>
+        <v>-0.1062649822039745</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1462572374669762</v>
+        <v>-0.149130295970501</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.285934747555217</v>
+        <v>-0.2886543206684706</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2045017016054871</v>
+        <v>-0.2073814985014337</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2249900700472551</v>
+        <v>-0.2278584022785779</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.1371654994353264</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.1307336421476251</v>
+        <v>-0.1337237744487183</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.2161975754038892</v>
+        <v>-0.2190924735239221</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.119942973199791</v>
+        <v>-0.1229625825163509</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1603343939110289</v>
+        <v>-0.1632951368883724</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2299618320610648</v>
+        <v>-0.2328295439704604</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2358546545691169</v>
+        <v>-0.2387457887895508</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2019159290463008</v>
+        <v>-0.2048543324388845</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.2450526697965785</v>
+        <v>-0.2479256347869452</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2722400110129612</v>
+        <v>-0.275085610330315</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.1541</t>
+          <t>X &lt; 0.1538</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3292</v>
+        <v>3296</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.3530279155161722</v>
+        <v>0.3513192017232001</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.3057302371184534</v>
+        <v>0.3040626463857876</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1501574600705098</v>
+        <v>0.1486120889309746</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1777890124705053</v>
+        <v>0.1761774467649957</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.07115425605115888</v>
+        <v>0.06853260752903623</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.08711943464635397</v>
+        <v>-0.08954317376635856</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1479112915613641</v>
+        <v>-0.1502978105414314</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2278668286427461</v>
+        <v>-0.2301707673295041</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1388259829068872</v>
+        <v>-0.1412370705769916</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1089070153946068</v>
+        <v>-0.1113905541231901</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.05905130985942009</v>
+        <v>-0.06158427571606495</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1995885470461687</v>
+        <v>-0.2019656725221068</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1560719598771456</v>
+        <v>-0.1585538857410285</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1778231410241702</v>
+        <v>-0.1802902613310238</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.03115080674493242</v>
+        <v>-0.03382670555826905</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.02393833315653637</v>
+        <v>-0.02659769608921891</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.1096794503078371</v>
+        <v>-0.1122426262021463</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.04499533938911782</v>
+        <v>-0.04764318118005662</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.08373017717942588</v>
+        <v>-0.08632289639953683</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1516990291262204</v>
+        <v>-0.1542024680881156</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1609925182544103</v>
+        <v>-0.1635108321282601</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.1277316637905344</v>
+        <v>-0.130295315988711</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1991859465034054</v>
+        <v>-0.2016520216343523</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2570470323236194</v>
+        <v>-0.2594478722439035</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.1657</t>
+          <t>X &lt; 0.1654</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3307</v>
+        <v>3311</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2297824981531065</v>
+        <v>0.2283790413370781</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1511116106952954</v>
+        <v>0.1497886294723472</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1098968462879668</v>
+        <v>0.1085659227406524</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.134173534366461</v>
+        <v>0.1327845868414528</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.0337730503472855</v>
+        <v>-0.03596102637636278</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1303695539021987</v>
+        <v>-0.1324353850592743</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1643035179911934</v>
+        <v>-0.1663603352111451</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2451604630933346</v>
+        <v>-0.2471323421477507</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1262370662873877</v>
+        <v>-0.1283515796397836</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1300560472115961</v>
+        <v>-0.1321978593954327</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.07919238854632482</v>
+        <v>-0.08138586704396289</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.190232334703559</v>
+        <v>-0.1923045258695453</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1218546145847128</v>
+        <v>-0.1240549746868567</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1143504044453394</v>
+        <v>-0.1165699225749037</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.02869690544814318</v>
+        <v>0.02627755414317789</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.02174444860970226</v>
+        <v>-0.02408082025436187</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1077037597170758</v>
+        <v>-0.1099432205984954</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.01658100401944296</v>
+        <v>0.01418613011335879</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.05117423040303493</v>
+        <v>-0.05348019676068105</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.1179779522802775</v>
+        <v>-0.1201972576123183</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.1296807715357176</v>
+        <v>-0.1319089293918694</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.09690554019208975</v>
+        <v>-0.09917766325548882</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.1365507939262756</v>
+        <v>-0.1387654712789512</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.1944749485850537</v>
+        <v>-0.1966240399461441</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.1774</t>
+          <t>X &lt; 0.1771</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3320</v>
+        <v>3324</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2295579241923704</v>
+        <v>0.2282894267532711</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1199669934289318</v>
+        <v>0.1188172119480484</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1032324868147612</v>
+        <v>0.1020521064518007</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.03481409274474601</v>
+        <v>0.03369010108419701</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1339305036628318</v>
+        <v>-0.1357347456535152</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1395777151080964</v>
+        <v>-0.1413698005175021</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2063601437894533</v>
+        <v>-0.2081002708591555</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3179761196863282</v>
+        <v>-0.319593371396742</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1993762943855657</v>
+        <v>-0.2011352436827138</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.206219676274408</v>
+        <v>-0.2079985054083124</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.184510149238065</v>
+        <v>-0.186306555369832</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2662253712673817</v>
+        <v>-0.2679346627471091</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.202525912703166</v>
+        <v>-0.2043519724853695</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1959393796128381</v>
+        <v>-0.1977822257330644</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.08608741670383324</v>
+        <v>-0.08808629187998207</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1039936944618916</v>
+        <v>-0.1059514714976828</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1601087002567922</v>
+        <v>-0.1620049802859711</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.03673581002549042</v>
+        <v>-0.03878514082595785</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1033971790790744</v>
+        <v>-0.1053600651976083</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1692238267148056</v>
+        <v>-0.1711022349878846</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1830213539272378</v>
+        <v>-0.1849034028383088</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1506876741529055</v>
+        <v>-0.1526124549315</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1891183288720768</v>
+        <v>-0.1909884199549907</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2772493482702671</v>
+        <v>-0.279017229551151</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.1891</t>
+          <t>X &lt; 0.1888</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3335</v>
+        <v>3339</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.3759083738799376</v>
+        <v>0.3746198705061659</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2057760614338946</v>
+        <v>0.2046795693250374</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1529096476999072</v>
+        <v>0.1518332296634171</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.08162062870412257</v>
+        <v>0.08060754490077926</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.0283586341594102</v>
+        <v>-0.02998721456574316</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.03311179572806111</v>
+        <v>-0.03473017346739482</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1030221449438002</v>
+        <v>-0.1045809160308053</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2153545463988493</v>
+        <v>-0.2167885488510635</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1269199852267135</v>
+        <v>-0.128459150822323</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1670367096428933</v>
+        <v>-0.1685517922442514</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1143149576758873</v>
+        <v>-0.1158858081678815</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1968937844348631</v>
+        <v>-0.1983752699748393</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1385002220359013</v>
+        <v>-0.1400855982098221</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1628120819115537</v>
+        <v>-0.1643759478963673</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.05639870175718187</v>
+        <v>-0.05811017598882273</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.07154572626198075</v>
+        <v>-0.07322251496138676</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.09807881474900881</v>
+        <v>-0.09972887057163859</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.005643761904536859</v>
+        <v>-0.007408472677980171</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.1009659513090639</v>
+        <v>-0.1026112764612535</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.165655884995509</v>
+        <v>-0.1672192648321058</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1818313257145547</v>
+        <v>-0.183392453039076</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1499840531931511</v>
+        <v>-0.1515865523306914</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1870061974390111</v>
+        <v>-0.1885571921849802</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.3050667648631844</v>
+        <v>-0.3064795688451056</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.2008</t>
+          <t>X &lt; 0.2004</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3346</v>
+        <v>3350</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.3478435690191688</v>
+        <v>0.3467010632653285</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2068550986072495</v>
+        <v>0.2058707501399226</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1494582139743414</v>
+        <v>0.1485047698309572</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1057773355994982</v>
+        <v>0.104857025679209</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.0050292791323443</v>
+        <v>-0.006465814334397635</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.03887446660011307</v>
+        <v>-0.04026687240611437</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1110858197653357</v>
+        <v>-0.1124130156388219</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1942202760566474</v>
+        <v>-0.1954566181652382</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1654390826879322</v>
+        <v>-0.166709369451965</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.20796932634439</v>
+        <v>-0.2092096516584903</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1843047104149349</v>
+        <v>-0.1855669585783986</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2079888545046416</v>
+        <v>-0.2092308821665654</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1832630989748409</v>
+        <v>-0.1845641871159316</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2082341535285934</v>
+        <v>-0.2095120226308325</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.07453737930051574</v>
+        <v>-0.07599219768342635</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.08768853644161823</v>
+        <v>-0.08911328893461246</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1145793074435417</v>
+        <v>-0.1159763348543663</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.02279703015128831</v>
+        <v>-0.02430701550159142</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.1171019872050394</v>
+        <v>-0.118494875174882</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.1809701492537314</v>
+        <v>-0.1822829147732108</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1988812092368306</v>
+        <v>-0.2001874380315769</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.167393218523479</v>
+        <v>-0.1687398205774429</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2033958344595987</v>
+        <v>-0.2046932280809557</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3213228328841637</v>
+        <v>-0.3224822150927551</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/vix/vix_ret_5.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/vix/vix_ret_5.xlsx
@@ -622,2375 +622,2375 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.368660142892317</v>
+        <v>7.12112220336234</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.187536436521917</v>
+        <v>3.331324505901023</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.03862072438853</v>
+        <v>9.18342336506867</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.377253540871195</v>
+        <v>-5.603242487679296</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.144299134104635</v>
+        <v>1.223205898750493</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.098718957707156</v>
+        <v>-2.17275256454662</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.994541178110516</v>
+        <v>4.142317073963028</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.143638469072819</v>
+        <v>-3.268097821934859</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.102935046900377</v>
+        <v>-3.141537591199416</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.873240299829938</v>
+        <v>-3.935332017517354</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.703409861701964</v>
+        <v>7.007533808480602</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.99219204992697</v>
+        <v>3.175444947676411</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>9.747560690660059</v>
+        <v>9.184454493958562</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.09223571556241</v>
+        <v>5.379005729917317</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5.437811532235806</v>
+        <v>4.700402710175133</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>2.5925217758762</v>
+        <v>1.698973371593937</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.459733966831003</v>
+        <v>1.595889473380687</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>5.797944588921837</v>
+        <v>5.028880868970433</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>6.015353257400442</v>
+        <v>5.244662893183175</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.6843872905113244</v>
+        <v>-1.673662971552602</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-1.226593054084645</v>
+        <v>-2.241035607068099</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-1.302773079420191</v>
+        <v>-2.31684407542253</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-1.02866132969573</v>
+        <v>-2.073901833399894</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-1.104777634547219</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.1204</t>
+          <t>X ≈ -0.1203</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>17.20458133829161</v>
+        <v>17.30303523604247</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.060260312887394</v>
+        <v>4.246500590364235</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>18.65872081317199</v>
+        <v>19.02784342323529</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>24.36947732999329</v>
+        <v>24.85871269452808</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14.4202017687785</v>
+        <v>14.9691548358922</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>14.61073899253097</v>
+        <v>15.12978962697564</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>23.47475310134335</v>
+        <v>23.9711037585442</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>19.99580732283233</v>
+        <v>20.46553912589663</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>23.25436116739806</v>
+        <v>23.81047811699086</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>25.70391582591145</v>
+        <v>26.23706025115963</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>19.55811782573712</v>
+        <v>20.08937404469157</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.85835497755433</v>
+        <v>13.39170362649786</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11.74251178233288</v>
+        <v>12.28421481344342</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.309841685208639</v>
+        <v>8.82453317895682</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>7.656157348143672</v>
+        <v>8.147029755427063</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.815644860262879</v>
+        <v>2.27354160997568</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>8.120557182963822</v>
+        <v>8.608663111136913</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>4.798457288982746</v>
+        <v>5.258712935240311</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-1.426232646986456</v>
+        <v>-0.9673089785294451</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.461763030150919</v>
+        <v>-3.974999768016097</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-5.005109683939139</v>
+        <v>-4.543064717190624</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.858596919073214</v>
+        <v>-1.395717247303708</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.584660678802194</v>
+        <v>-1.152509539514753</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.564855290925536</v>
+        <v>1.910792282007876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1086</t>
+          <t>X ≈ -0.1087</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>40</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.793690550738233</v>
+        <v>8.891718523890837</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>28.33082562934044</v>
+        <v>28.51829812060382</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14.48946481635395</v>
+        <v>14.85837532374679</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.30147752291792</v>
+        <v>11.7900901282967</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.999826383946569</v>
+        <v>6.548371540672363</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.187864577189757</v>
+        <v>6.706528955759651</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12.88231052146003</v>
+        <v>13.37822452847263</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.12291729822441</v>
+        <v>10.59226177076822</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.678756171036568</v>
+        <v>8.234308984149941</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.422219090256668</v>
+        <v>4.95465287917613</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.696499196816262</v>
+        <v>5.227282962282032</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.420725581744868</v>
+        <v>4.953810110923442</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.79402130418493</v>
+        <v>6.335544590959749</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.068078740388515</v>
+        <v>8.582738737048039</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>7.414417362284645</v>
+        <v>7.905262239095784</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>5.516104645286561</v>
+        <v>5.974047856366468</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>7.878754425710511</v>
+        <v>8.366839335551312</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>12.7674149803008</v>
+        <v>13.22776842582118</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>12.98711648390407</v>
+        <v>13.44619512658802</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>8.184077761841834</v>
+        <v>8.670947218331193</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>7.644601076176279</v>
+        <v>8.106726654513238</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.072643347349377</v>
+        <v>5.535550967149909</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>7.847930866839832</v>
+        <v>8.280102071462402</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.274532710280944</v>
+        <v>5.620469701362715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.09698</t>
+          <t>X ≈ -0.09707</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.013370687658785</v>
+        <v>1.994658514935523</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.601240189866054</v>
+        <v>8.372651893960423</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>11.73491413530243</v>
+        <v>11.54400115808648</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.677705866311726</v>
+        <v>8.751395283663527</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.018215520257996</v>
+        <v>6.271160195373838</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.900059692981415</v>
+        <v>4.21935733787948</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.735340480950619</v>
+        <v>7.849859340729239</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.437190173808588</v>
+        <v>7.550367019899781</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.85060117462195</v>
+        <v>3.256390382898502</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.362250495495118</v>
+        <v>4.677472091535023</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.301371568311744</v>
+        <v>-1.689915381110694</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-11.87076222315623</v>
+        <v>-10.82142772527897</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-10.72195692129799</v>
+        <v>-9.721484112034354</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.637978851025494</v>
+        <v>-7.756286216961364</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-9.329319534745501</v>
+        <v>-8.438684420628441</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-8.716631171018562</v>
+        <v>-7.880926601626392</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-12.12113205153429</v>
+        <v>-12.42192981483893</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.888095125566693</v>
+        <v>-5.904011019439892</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-5.995441817733145</v>
+        <v>-7.910181714952913</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-5.810359385781474</v>
+        <v>-7.697950432385191</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-6.354116342511688</v>
+        <v>-8.267149302098034</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-6.431893951085719</v>
+        <v>-8.344833341878918</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.8151770878366094</v>
+        <v>-1.439177049810638</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.585932405999223</v>
+        <v>-3.82397474308123</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.08533</t>
+          <t>X ≈ -0.08543</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>57</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.450014781205049</v>
+        <v>9.54170440052404</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>16.09295577765467</v>
+        <v>16.2691557454733</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.43655016504993</v>
+        <v>9.798613140978908</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.243214970339466</v>
+        <v>5.727672873044831</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.656178993265705</v>
+        <v>7.199989060857376</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1373288737718497</v>
+        <v>0.3806364762226977</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.585441016782774</v>
+        <v>3.078645885485827</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.05734796306033</v>
+        <v>4.523414813233536</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.35319610097158</v>
+        <v>2.906611190950429</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.659100269211841</v>
+        <v>-3.12507772174353</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.38683545109707</v>
+        <v>-2.854584061361763</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1672061445109705</v>
+        <v>0.3655760830144175</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.211228941701641</v>
+        <v>2.750901544215523</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.741511774427899</v>
+        <v>4.253369729616004</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.33573338286859</v>
+        <v>1.825314115343204</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.572365978509723</v>
+        <v>-1.113762723679798</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>7.049147547205052</v>
+        <v>7.534878568458232</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.06001401866236478</v>
+        <v>0.4001829266887569</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.595782891745536</v>
+        <v>-1.136852857892286</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.3427995752726218</v>
+        <v>0.8296119056172913</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.951760968323867</v>
+        <v>-1.489687105751337</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-3.781475949619562</v>
+        <v>-3.318598357906922</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.508225461001309</v>
+        <v>-3.076074036239625</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-5.339502377438919</v>
+        <v>-4.993565386356977</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.07367</t>
+          <t>X ≈ -0.07379</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8.918612862987843</v>
+        <v>7.448450073389992</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.562857064728881</v>
+        <v>-0.1108113163512243</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.149976433577628</v>
+        <v>4.916164975748543</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5721522395938763</v>
+        <v>-0.8979279394874879</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.116485008137481</v>
+        <v>4.059175019511486</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2856431940334119</v>
+        <v>0.03153120478934568</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.488928954253296</v>
+        <v>-1.807691225216672</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.764940993437449</v>
+        <v>-1.062857727126044</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.741051320214105</v>
+        <v>-4.077695281104866</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.493483414142744</v>
+        <v>-1.727366468678532</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.7984875338733701</v>
+        <v>1.688107141690544</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.525962365657222</v>
+        <v>-5.925805802316304</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.641292964894149</v>
+        <v>-5.990331957581269</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.8563967627422</v>
+        <v>-6.239580468634792</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-7.522388161346733</v>
+        <v>-7.970908927369756</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.890586801006073</v>
+        <v>-2.163556984831551</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.016509841260536</v>
+        <v>-1.217995053668126</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1131076893553811</v>
+        <v>-0.3002787500814037</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.914135943150626</v>
+        <v>-2.187707493724488</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.727881863702486</v>
+        <v>-1.973816389170757</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-3.279445457849306</v>
+        <v>-3.592829339892809</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-3.356332224968547</v>
+        <v>-3.669145229241842</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.083005011316843</v>
+        <v>-3.426789563547175</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1295076937597983</v>
+        <v>-0.4321618775844129</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.062</t>
+          <t>X ≈ -0.06216</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12.41581669618211</v>
+        <v>14.12817248843175</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.211748280879291</v>
+        <v>7.117347550733065</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.134443976292225</v>
+        <v>8.874429808075291</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.138544281801707</v>
+        <v>7.531535393800389</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.570931295461122</v>
+        <v>7.258561200007492</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.654362239664813</v>
+        <v>-0.867482271057888</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1281691857003935</v>
+        <v>0.5967304433145628</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3620155385110166</v>
+        <v>0.2909967240379174</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.701965505962839</v>
+        <v>2.680999153709507</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.997733725489084</v>
+        <v>4.900500789705291</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.206978225018098</v>
+        <v>2.157719309639582</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.464758452973484</v>
+        <v>3.388892340083864</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.646265797715067</v>
+        <v>4.536369809844658</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.427351030232408</v>
+        <v>5.043935925970409</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.772734192583563</v>
+        <v>4.359576033131951</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.006359362963892</v>
+        <v>-0.3651227388719036</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.69779202484672</v>
+        <v>3.754383757843421</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.128326252593197</v>
+        <v>5.135208135696217</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>6.649503204538782</v>
+        <v>6.864161160996545</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.229565718626006</v>
+        <v>2.541775972483364</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.45694662370164</v>
+        <v>2.732741908225066</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.150645256685216</v>
+        <v>3.415544722629626</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.8881744027127</v>
+        <v>2.145568537040802</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.4946980589507461</v>
+        <v>-0.2886212077283687</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05034</t>
+          <t>X ≈ -0.05053</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12.91395214193256</v>
+        <v>13.65045490916122</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.541067130561274</v>
+        <v>8.323606739005193</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.60305601958239</v>
+        <v>11.57934248164742</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.780512063260247</v>
+        <v>8.719349380058503</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.203271925749988</v>
+        <v>6.185068757617024</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.587329848229501</v>
+        <v>4.077519179405819</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.009713386231652521</v>
+        <v>1.016799881490023</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.669256279642461</v>
+        <v>4.665636058557105</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.150259420563799</v>
+        <v>3.663827353046031</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.819234989975953</v>
+        <v>1.161597523772052</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.344176587026034</v>
+        <v>3.702864021702446</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.506721940428335</v>
+        <v>2.285419936488822</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.077133643943853</v>
+        <v>3.992668734265827</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.858253487398855</v>
+        <v>3.175800747067171</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>6.585028304024441</v>
+        <v>5.88476137771476</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>7.744806680062396</v>
+        <v>7.021171418474125</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.919075956915208</v>
+        <v>5.219951501048619</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>4.686682540442035</v>
+        <v>4.284004654016364</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.212466381508698</v>
+        <v>4.263806156124765</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.221652397145817</v>
+        <v>7.080294022393758</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>4.55346419025512</v>
+        <v>5.381098933301914</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>3.350170346679739</v>
+        <v>4.172327514690508</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.625842804195628</v>
+        <v>4.417400430438022</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.856453614235313</v>
+        <v>2.552287883180895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.03868</t>
+          <t>X ≈ -0.03889</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.882471978982096</v>
+        <v>8.060716878452979</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.883155209628825</v>
+        <v>4.553763531846229</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.914883226739164</v>
+        <v>0.5016308813536767</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.043443587053623</v>
+        <v>-2.433892229331171</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.432874606978622</v>
+        <v>-1.783531051916228</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.138919882246562</v>
+        <v>-3.032829786022518</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.438106209969725</v>
+        <v>-4.303380549137358</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.191323049542838</v>
+        <v>-5.080707704587184</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.255722242465964</v>
+        <v>-3.557195601074461</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.029926989792443</v>
+        <v>-3.901913515260944</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.808192136460143</v>
+        <v>-2.691851877016028</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.656460985572153</v>
+        <v>2.149762118083601</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5328103182055344</v>
+        <v>0.0894350440650058</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.1128084267201</v>
+        <v>-1.097181617799386</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.29763962083792</v>
+        <v>-0.8581523872611996</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.248288875362519</v>
+        <v>0.9176789426366696</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>1.540635955984477</v>
+        <v>2.68517279885333</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>3.811957663993162</v>
+        <v>3.95213641182206</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.257427890508644</v>
+        <v>4.167089703344317</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5.446628954106629</v>
+        <v>4.381676148403301</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>5.383026141741432</v>
+        <v>4.545840555819538</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.785307562350347</v>
+        <v>4.938982301970647</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>7.966133996674827</v>
+        <v>7.329319117679994</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>7.893580329327996</v>
+        <v>7.910189327530937</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.02701</t>
+          <t>X ≈ -0.02726</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.600772394585569</v>
+        <v>4.408426485980591</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7.97860405323641</v>
+        <v>7.422785856065261</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.008085999170241</v>
+        <v>4.003785641996352</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.571796649566132</v>
+        <v>3.05440054675708</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.874841921160794</v>
+        <v>3.143157558036584</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.787702519414879</v>
+        <v>2.578060475991435</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1622707535040675</v>
+        <v>0.3348724432301893</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4411588255570607</v>
+        <v>-0.3322922566646156</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.6906231242766481</v>
+        <v>1.246596735335658</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.823606604429656</v>
+        <v>3.352837909156925</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.919356378872131</v>
+        <v>5.805702801040169</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.186018871931005</v>
+        <v>4.078416113574491</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.060418361741604</v>
+        <v>3.171228935544555</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.752170440658361</v>
+        <v>5.831641876913714</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4.670871442501088</v>
+        <v>4.789199665131441</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>5.844364468502661</v>
+        <v>5.713740769329249</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.345593935656282</v>
+        <v>4.519257938820566</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>5.240405456251196</v>
+        <v>5.113327861226566</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.363562471384007</v>
+        <v>4.237341909277781</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.731278767356891</v>
+        <v>2.998020299201798</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.013904040938854</v>
+        <v>4.248337897091183</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>5.034147627274272</v>
+        <v>5.629883301282895</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>6.040666871535592</v>
+        <v>5.873517786561273</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.778182345316871</v>
+        <v>3.893196974089982</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01535</t>
+          <t>X ≈ -0.01562</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.416881935872546</v>
+        <v>1.306469757741546</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5088931345301972</v>
+        <v>-0.4118520647269577</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6350702266099688</v>
+        <v>-2.557313824146433</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.971944895397904</v>
+        <v>-0.5193605178556169</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.637890647884511</v>
+        <v>-0.5020374149600499</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.116075861402031</v>
+        <v>0.8232791039603384</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.374830781837517</v>
+        <v>2.242632843304378</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.100725075930384</v>
+        <v>1.052809101370187</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7245347302048728</v>
+        <v>-1.172827592336823</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8268265432343398</v>
+        <v>0.08877243837433468</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6433913934641708</v>
+        <v>-1.400687107243151</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5330296197285662</v>
+        <v>-0.5028744198927697</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5763510530181861</v>
+        <v>-0.4463496265779909</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.8068854382726443</v>
+        <v>-2.000984343171289</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.590830820312334</v>
+        <v>-1.336463415237972</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2890683193422205</v>
+        <v>-1.068205655586333</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.005362933126641</v>
+        <v>-1.761151706054008</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.110663055370033</v>
+        <v>-2.188762529743983</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.185558421729695</v>
+        <v>-1.974558834807233</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.870700441543818</v>
+        <v>-2.940430457116705</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.539055587844764</v>
+        <v>-2.33013147932607</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.197552241204257</v>
+        <v>-3.118842898770744</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.632275505794496</v>
+        <v>-2.285237912017436</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.874155336366854</v>
+        <v>-3.332332658519292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.003682</t>
+          <t>X ≈ -0.003988</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.104148177485961</v>
+        <v>-5.489339931098819</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.848271595572129</v>
+        <v>-2.992745617458439</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.32551370169827</v>
+        <v>-0.7110024919319997</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.13583140631355</v>
+        <v>1.580096612794712</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2791015162383914</v>
+        <v>0.5144990604400661</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8413744905267748</v>
+        <v>-0.6549171279249677</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2369944177280203</v>
+        <v>-0.4023893475256131</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2266760706108641</v>
+        <v>0.3409368588465611</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5323735405124594</v>
+        <v>0.6149367826556187</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.344243314672639</v>
+        <v>1.547405678072806</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.033626119387975</v>
+        <v>0.1228486750013928</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.5503207376718962</v>
+        <v>1.048471509523011</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3036379313905329</v>
+        <v>0.4612838775604189</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.109523834018269</v>
+        <v>-0.8423591548490634</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1215425164108552</v>
+        <v>1.377861133450644</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.851649124258266</v>
+        <v>0.6199039385499248</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.7220145879330957</v>
+        <v>0.7798757695690384</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.14949665164341</v>
+        <v>-0.4084173065687295</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.72661759777408</v>
+        <v>-0.7216595649112563</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.745458918623214</v>
+        <v>0.5483358511240723</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-3.34582045660251</v>
+        <v>-0.810665378488828</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.62822555064411</v>
+        <v>0.1695810705321108</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.475570394965295</v>
+        <v>-1.697602386142016</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.900533602716969</v>
+        <v>-0.01277568122303308</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.00798</t>
+          <t>X ≈ 0.007645</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.074946663162379</v>
+        <v>2.021697298603264</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.08863525837188035</v>
+        <v>-0.6295887745284361</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4296968444624909</v>
+        <v>-0.3738473735159502</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.731948295785223</v>
+        <v>-2.164785487215852</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.968966908754645</v>
+        <v>-3.644908661970831</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.0517841530838794</v>
+        <v>-1.977563362571622</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.508765113013737</v>
+        <v>2.057789657841745</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.839178887428758</v>
+        <v>1.756015049066406</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.973054001227851</v>
+        <v>1.279714351499763</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.7169439247429</v>
+        <v>2.900581285283401</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.781322561224329</v>
+        <v>1.964357085386226</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.899702080149801</v>
+        <v>1.083545523664213</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.298123270272036</v>
+        <v>1.177112620714951</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4720225027662011</v>
+        <v>0.324648952031076</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.637178851857414</v>
+        <v>1.153068588272923</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>2.231403494137311</v>
+        <v>2.016487410717957</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.401264149823987</v>
+        <v>2.5168366062437</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.600314834431231</v>
+        <v>2.383952501082064</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.424021448145254</v>
+        <v>3.202644335478666</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>5.743999364325333</v>
+        <v>5.532034405915255</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>5.988252905530196</v>
+        <v>4.964589904534492</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>5.308995508054487</v>
+        <v>4.285197775328484</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>4.06544123849541</v>
+        <v>3.622487849730724</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>4.603801002963301</v>
+        <v>4.668808069942777</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.01964</t>
+          <t>X ≈ 0.01928</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.404400119023705</v>
+        <v>-5.675394251752664</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.077539769102216</v>
+        <v>-5.57304250457593</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-7.585549682387928</v>
+        <v>-7.553064456467595</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.024165184325263</v>
+        <v>-4.927149951960857</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5.353869062634075</v>
+        <v>-5.378787531447969</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.621273650594617</v>
+        <v>-2.51586066754237</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.121410477645782</v>
+        <v>-4.389458932008139</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-6.211707683798231</v>
+        <v>-6.494544624040991</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.715819047482071</v>
+        <v>-4.568054563277791</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.311831316613819</v>
+        <v>-3.565544907417944</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.038277061290096</v>
+        <v>-3.293309892813568</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.858483076620878</v>
+        <v>-2.490755156637427</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.168766775122556</v>
+        <v>-5.763920655383203</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.376527276345648</v>
+        <v>-2.055320184442166</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.669421648083997</v>
+        <v>-2.018050105895618</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.995721425741557</v>
+        <v>-4.694156159018405</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-3.399102337295012</v>
+        <v>-4.438324340527622</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.59934445498898</v>
+        <v>-4.57120844568918</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-5.113797430791941</v>
+        <v>-5.076170678975068</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-6.183338962900478</v>
+        <v>-5.940720924563557</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-4.166278869915551</v>
+        <v>-3.630467584217676</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.147249639059254</v>
+        <v>-2.626493415525481</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-5.068428325086678</v>
+        <v>-4.541132311542064</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-5.879313443565735</v>
+        <v>-5.422695766263189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.03131</t>
+          <t>X ≈ 0.03091</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-7.499891309900946</v>
+        <v>-6.976697636477908</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.772661517765108</v>
+        <v>-6.70186538285995</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.14024799859866</v>
+        <v>-6.371281148465613</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.836111772219375</v>
+        <v>-6.443806315444405</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-8.729409786638179</v>
+        <v>-9.917537564600266</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-9.054712557759366</v>
+        <v>-9.76728770595652</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-9.326064656844174</v>
+        <v>-10.56069878135064</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-7.044291997837959</v>
+        <v>-7.386171747873973</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.449476235094103</v>
+        <v>-4.598668370104662</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.253011698237131</v>
+        <v>-6.990464546175062</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.911243489004001</v>
+        <v>-2.462910382634654</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-4.954223967839802</v>
+        <v>-4.867151911574041</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.018957326194219</v>
+        <v>-3.854384454556637</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-4.755568186785574</v>
+        <v>-4.63453340960686</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-4.388621441902039</v>
+        <v>-3.720943110640761</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-5.335275694217422</v>
+        <v>-4.755383772672161</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-8.553403998813081</v>
+        <v>-8.05075354609923</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-6.603381215682987</v>
+        <v>-6.055978076792812</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-5.872390230604942</v>
+        <v>-5.30960095603001</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-6.711911754561783</v>
+        <v>-6.158844298205075</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-4.171098282550247</v>
+        <v>-4.066714331500698</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-5.278718949426406</v>
+        <v>-4.673791747073011</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-5.521326537913247</v>
+        <v>-4.430157261794662</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-3.539900279410404</v>
+        <v>-2.996551575233035</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.04297</t>
+          <t>X ≈ 0.04254</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-7.734193576416594</v>
+        <v>-7.203420394950868</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.79219653304812</v>
+        <v>-1.356689118494593</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.217616659386906</v>
+        <v>-2.607707552657921</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.29661982345057</v>
+        <v>-3.196605474270335</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.375230956116738</v>
+        <v>-2.252651419247748</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9589366756486086</v>
+        <v>0.9530626745552055</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.074241248227956</v>
+        <v>-0.4517754352384813</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5366790369842462</v>
+        <v>0.4628163164748855</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.00196374421288</v>
+        <v>4.859037909085785</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.8158126930544611</v>
+        <v>-0.2053062690603866</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.454494402929285</v>
+        <v>-2.372095644699911</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.998062765463814</v>
+        <v>-3.868189794293166</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.856740053816374</v>
+        <v>-3.15381361906104</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.076885416278529</v>
+        <v>-2.792291582933139</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.105391022012604</v>
+        <v>-3.47444596481823</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-3.411453862272936</v>
+        <v>-4.742410238681494</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.814825812352645</v>
+        <v>-6.675558943089435</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-5.554054608411271</v>
+        <v>-6.808443048251036</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-4.068708414384744</v>
+        <v>-5.374468625983305</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.246117254924677</v>
+        <v>-4.550126083363345</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-3.787984794263423</v>
+        <v>-3.898058389622129</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-7.041944505182684</v>
+        <v>-7.631757496943273</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.322892405526595</v>
+        <v>-3.729586426299001</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.126741175069945</v>
+        <v>-2.062457127905581</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.05464</t>
+          <t>X ≈ 0.05418</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.464298212245431</v>
+        <v>-4.811137973055494</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.006368145424567</v>
+        <v>-3.323024850073246</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-5.416839961885742</v>
+        <v>-3.725256119926179</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-8.776157073378677</v>
+        <v>-7.390015829426602</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.104874294778071</v>
+        <v>-0.6480301098767569</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.482983789620612</v>
+        <v>-3.999868433703234</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.264564788272857</v>
+        <v>-4.794950445935953</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-6.436914841945026</v>
+        <v>-5.977063871800716</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6.39417690448397</v>
+        <v>-5.849134962116608</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-8.071619093269057</v>
+        <v>-7.52237943979209</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-10.48063103620573</v>
+        <v>-9.881723372556181</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-11.6592160861109</v>
+        <v>-10.15830532702748</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-9.206318985691745</v>
+        <v>-7.764425514653681</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-8.905957743188232</v>
+        <v>-8.889852558542984</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-11.36204428858512</v>
+        <v>-11.32639290534027</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-6.287075896847448</v>
+        <v>-6.37912397423991</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-10.89840191478715</v>
+        <v>-9.99177631578948</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-13.68905342941913</v>
+        <v>-13.63343235077564</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-12.57683424861367</v>
+        <v>-12.54177714117372</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-12.38787337942398</v>
+        <v>-13.20438367857084</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-12.03409174750892</v>
+        <v>-12.89463519749543</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-11.23301888457445</v>
+        <v>-12.09260473699467</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-11.87888334412725</v>
+        <v>-12.72616323417243</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-11.97771954197187</v>
+        <v>-12.88830222846185</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.0663</t>
+          <t>X ≈ 0.06581</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>85</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-18.05203849056763</v>
+        <v>-18.24850908105177</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.375922042730068</v>
+        <v>-3.200298269696788</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1951612252703043</v>
+        <v>0.2508899813527776</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.2229326102929079</v>
+        <v>2.011428959015134</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.199643894650507</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.698486779626705</v>
+        <v>5.422216189619746</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.430745631672195</v>
+        <v>-3.608159940260038</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.227953965681969</v>
+        <v>-0.3836686189627798</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.14072749646332</v>
+        <v>-0.255739709278636</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-5.760204873047769</v>
+        <v>-4.581202969203851</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.482002203116409</v>
+        <v>-4.308967954599517</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.60544405207051</v>
+        <v>-3.409079320835495</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.567774527406797</v>
+        <v>-3.347500850050999</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.621116766051088</v>
+        <v>-2.419264323248747</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-6.613352329979747</v>
+        <v>-5.454359881604496</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-6.017584398780251</v>
+        <v>-4.893055862784834</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-3.816028260153026</v>
+        <v>-2.64399509803922</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-5.09551064805904</v>
+        <v>-3.953349791436075</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.53862195450413</v>
+        <v>-1.385946387819757</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.184039506733768</v>
+        <v>0.005110645474431408</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-7.579078956276454</v>
+        <v>-6.444686797082745</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-6.506325417441538</v>
+        <v>-5.343378730802606</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-5.07665940272819</v>
+        <v>-3.923273657288924</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-6.784290819131385</v>
+        <v>-6.438353828049046</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.07797</t>
+          <t>X ≈ 0.07744</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.550732602561155</v>
+        <v>2.339726213065916</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-15.14950604317816</v>
+        <v>-12.61206297557921</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-18.09820925102059</v>
+        <v>-16.80793354805899</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.387166957564688</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-6.404230121918253</v>
+        <v>-7.381776239907722</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2089040690273976</v>
+        <v>3.069275013149188</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9695526541948354</v>
+        <v>-2.137571704965801</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.745938863805904</v>
+        <v>-3.913080383668579</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.723022933593526</v>
+        <v>-5.255739709278636</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.986930614612348</v>
+        <v>-4.581202969203851</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.22342657177655</v>
+        <v>-5.77955618989364</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.548776786264263</v>
+        <v>1.296803032105608</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.940813131659972</v>
+        <v>1.652499149948994</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.215369073121238</v>
+        <v>-0.06632314677822393</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.058495749015698</v>
+        <v>0.7221107066308718</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.133596707448362</v>
+        <v>-0.1871735098435749</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-3.514963580113886</v>
+        <v>-4.702818627450988</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.9041244925008485</v>
+        <v>-0.4239380267302764</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.894904907993023</v>
+        <v>-3.150652270172692</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.2005987073159332</v>
+        <v>-1.46547758981955</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.782331505462565</v>
+        <v>2.378842614682029</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.199330692271417</v>
+        <v>0.8330918574326631</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.9564255695642601</v>
+        <v>-0.3938618925830681</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.8805933163409847</v>
+        <v>-2.026589122166698</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.08963</t>
+          <t>X ≈ 0.08908</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.309557380226657</v>
+        <v>4.084491915957145</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8.957135245473246</v>
+        <v>7.228415588727906</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>9.113063138973864</v>
+        <v>9.363551995310893</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.755441798335021</v>
+        <v>5.381319288028152</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.651394040289105</v>
+        <v>3.410845893691473</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.049488499142733</v>
+        <v>-4.906796771496822</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.200860278602434</v>
+        <v>-4.00696352949236</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.542149940344615</v>
+        <v>-6.006799227138217</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.374506324451851</v>
+        <v>-4.183955063216814</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.433797105618737</v>
+        <v>-1.590176049961585</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5854265399074379</v>
+        <v>0.3769742188800436</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2646249918000549</v>
+        <v>0.1003922644087467</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.537173606188723</v>
+        <v>4.070245909669836</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.295068657412514</v>
+        <v>3.822011848236727</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.04516042654324082</v>
+        <v>1.444942212114384</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.195937507964402</v>
+        <v>-1.383584277540528</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.3417181052683844</v>
+        <v>1.902365819208988</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.2263643652823717</v>
+        <v>1.769481714047387</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.890531608275658</v>
+        <v>5.373774449667778</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>4.077377418243685</v>
+        <v>3.893445640489439</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.513805177947937</v>
+        <v>5.020916393345985</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>7.955253321779772</v>
+        <v>8.335584379865232</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.867606342814</v>
+        <v>5.189388356669077</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>5.791774089590724</v>
+        <v>6.722164616616958</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.1013</t>
+          <t>X ≈ 0.1007</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-22.90373527458059</v>
+        <v>-21.5426267281106</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-21.18538205459211</v>
+        <v>-21.78853356381444</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-20.60471084095625</v>
+        <v>-21.04322766570605</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-5.098664439717957</v>
+        <v>-5.635629864514357</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.429988168302657</v>
+        <v>-7.911188004613606</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.256551129938302</v>
+        <v>-3.754254398615522</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.136303518791884</v>
+        <v>1.450663589151702</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4.222869723638098</v>
+        <v>1.273672055427241</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.954969073144028</v>
+        <v>0.4776205602079031</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.680909430982176</v>
+        <v>-1.250144425187749</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-13.16374046708322</v>
+        <v>-7.52672637965911</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.001188248225112432</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.30389977773293</v>
+        <v>-2.889852558542998</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-7.002859401844105</v>
+        <v>-5.57200694042799</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.326839826839887</v>
+        <v>-3.010702921608392</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-8.583205943409133</v>
+        <v>-9.114583333333279</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.5247813411078681</v>
+        <v>-1.247467438494816</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>-3.033005211349099</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-8.285309456337963</v>
+        <v>-6.818418766290122</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-2.70540664471222</v>
+        <v>-3.38586326767085</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-4.822068932651931</v>
+        <v>-5.461025789626142</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-4.547594220169827</v>
+        <v>-5.217391304347821</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-6.664242799923649</v>
+        <v>-7.379530298637285</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.1129</t>
+          <t>X ≈ 0.1124</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.325133696751166</v>
+        <v>3.124039938556109</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>7.828721079985023</v>
+        <v>6.211466436185482</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>13.35667352121776</v>
+        <v>8.290105667627337</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>12.66257319709922</v>
+        <v>11.03103680215244</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>26.01862882638791</v>
+        <v>20.75547866205306</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>16.07099833643922</v>
+        <v>7.579078934717806</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11.91814729078364</v>
+        <v>10.11733025581847</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.191659983961515</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.33659544173819</v>
+        <v>-6.726327944572752</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.884596096367176</v>
+        <v>-10.85571277312543</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-9.507088178343132</v>
+        <v>-13.91681109185442</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.5589900044157119</v>
+        <v>-4.193393046325617</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-10.9089996486473</v>
+        <v>-11.97495183044311</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-7.681802663024918</v>
+        <v>-12.22318589187617</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-8.339945960605377</v>
+        <v>-9.57200694042799</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.8490073145245631</v>
+        <v>-2.344036254941564</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>9.361903134704875</v>
+        <v>4.218749999999993</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>9.257062430883693</v>
+        <v>4.085865894838307</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>6.024677949739051</v>
+        <v>0.9669947886507444</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>2.763247897638053</v>
+        <v>-2.151752099623515</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.220701729672179</v>
+        <v>-2.719196601004249</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>9.041407492401</v>
+        <v>3.87230754370713</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>12.76415806695192</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>9.240049951659536</v>
+        <v>3.953803034696044</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.1247</t>
+          <t>X ≈ 0.124</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-20.73316228101973</v>
+        <v>-22.29262672811064</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-24.78547619116582</v>
+        <v>-19.41353356381451</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-26.65620248462236</v>
+        <v>-20.66822766570609</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-20.37510888501735</v>
+        <v>-18.13562986451427</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-13.75405411946947</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.189407803728585</v>
+        <v>3.620745601384478</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.475941379167189</v>
+        <v>-0.2993364108481984</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>2.520743145743097</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-10.8555227848627</v>
+        <v>-9.851327944572752</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-11.62843846089919</v>
+        <v>-10.64737943979209</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-11.35437881873732</v>
+        <v>-10.37514442518776</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-4.401726379659053</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.613433146184242</v>
+        <v>-8.641618497109867</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.263083451202263</v>
+        <v>-2.639852558542977</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.921226748782821</v>
+        <v>-6.44700694042799</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-2.32683982683983</v>
+        <v>-2.760702921608328</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.864583333333378</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-2.565597667638485</v>
+        <v>-2.997467438494937</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>-2.783005211349163</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-2.162860476746076</v>
+        <v>-2.568418766290179</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-6.276835216140732</v>
+        <v>-6.260863267670914</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-6.352681177549833</v>
+        <v>-6.336025789626241</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-6.07820646506778</v>
+        <v>-6.092391304347863</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-6.154038718291055</v>
+        <v>-6.254530298637285</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.1363</t>
+          <t>X ≈ 0.1356</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-17.03553014001689</v>
+        <v>-13.54262672811063</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-12.01925036031629</v>
+        <v>-13.78853356381447</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.697468150298342</v>
+        <v>4.956772334293952</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-0.6356298645142644</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9068318972471516</v>
+        <v>-0.9111880046135994</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7198657111498505</v>
+        <v>-0.7542543986155152</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.063741160515356</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>14.89664082687338</v>
+        <v>13.14574314574321</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>20.49368356434366</v>
+        <v>18.27367205542725</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>25.27632344386272</v>
+        <v>22.47762056020791</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>14.43927197491352</v>
+        <v>12.74985557481224</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.04941146035442</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>6.358381502890175</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>12.81628162816281</v>
+        <v>11.11014744145714</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>12.15813833058225</v>
+        <v>10.42799305957201</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>12.75252525252525</v>
+        <v>10.98929707839167</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>18.17416367110334</v>
+        <v>15.88541666666674</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>18.06932296728216</v>
+        <v>15.75253256150506</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>12.72965879265092</v>
+        <v>10.96699478865084</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>24.02761571373007</v>
+        <v>21.18158123370982</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>17.92951399020848</v>
+        <v>15.61413673232909</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>12.29811247324381</v>
+        <v>10.53897421037387</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>12.57258718572587</v>
+        <v>10.78260869565225</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>18.05231048805816</v>
+        <v>15.62046970136264</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.1479</t>
+          <t>X ≈ 0.1472</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-25.06941854200336</v>
+        <v>-23.54262672811056</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-11.11848105463882</v>
+        <v>-8.788533563814362</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-12.55650010366992</v>
+        <v>-10.04322766570605</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>14.36437013548573</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>-0.9111880046135354</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>10.39124539996132</v>
+        <v>9.245745601384407</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>8.450663589151759</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>18.86489479512736</v>
+        <v>18.14574314574314</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.620667691327775</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.9141527466134818</v>
+        <v>-2.522379439792083</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>13.64562118126273</v>
+        <v>12.74985557481217</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.36687177781474</v>
+        <v>12.47327362034095</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>6.358381502890175</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.260726072607326</v>
+        <v>6.110147441457066</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>16.12639229883623</v>
+        <v>15.42799305957201</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>16.72077922077928</v>
+        <v>15.98929707839167</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>16.58686208380175</v>
+        <v>15.88541666666666</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>11.72011661807581</v>
+        <v>10.75253256150506</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>11.93600799900006</v>
+        <v>10.96699478865084</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>12.12285380896816</v>
+        <v>11.18158123370982</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>11.5803076410022</v>
+        <v>10.61413673232909</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>11.50446167959303</v>
+        <v>10.5389742103738</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>5.782608695652179</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.179294615042416</v>
+        <v>0.6204697013628575</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.1596</t>
+          <t>X ≈ 0.1589</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>15</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-26.9741804467653</v>
+        <v>-26.87596006144393</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-33.97562391178182</v>
+        <v>-33.78853356381451</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-8.746976294146158</v>
+        <v>-8.376560999039384</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-9.459930313588849</v>
+        <v>-15.63562986451427</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-23.12905411946946</v>
+        <v>-15.9111880046137</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-9.608754600038836</v>
+        <v>-9.087587731948759</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.714036617262423</v>
+        <v>-3.216003077514998</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.992248062015499</v>
+        <v>-3.520923520923525</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.715905786565912</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.723676556137285</v>
+        <v>-4.189046106458846</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.449616913975362</v>
+        <v>-3.916811091854321</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.938300349243306</v>
+        <v>2.473273620340855</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.92739273927384</v>
+        <v>14.44348077479039</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>13.26924944169337</v>
+        <v>13.7613263929054</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.5303030303029388</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>13.6248785228377</v>
+        <v>14.08586589483845</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.174103237095515</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>6.81840287909727</v>
+        <v>7.280803398995658</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>13.68369829683698</v>
+        <v>14.11594202898542</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>13.60786604361362</v>
+        <v>13.95380303469586</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.1713</t>
+          <t>X ≈ 0.1705</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>13</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2053067327218798</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-7.821777757935628</v>
+        <v>-7.634687409968315</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.567489114658876</v>
+        <v>-1.197073819552202</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-25.35736621102474</v>
+        <v>-17.1740914029758</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-25.69315668357196</v>
+        <v>-25.14195723538284</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.429267420551511</v>
+        <v>5.784207139846018</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-10.89352379674961</v>
+        <v>-10.39549025700198</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-18.86404293381032</v>
+        <v>-10.70041070041071</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-18.82255575189572</v>
+        <v>-10.5724817907266</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-19.59547142793215</v>
+        <v>-11.36853328594583</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-27.01371947807793</v>
+        <v>-18.78860596364929</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-19.60016118921828</v>
+        <v>-11.37288022581285</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-20.7233232560744</v>
+        <v>-12.48777234326367</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-20.94440213252099</v>
+        <v>-12.73600640469678</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-29.29485312240919</v>
+        <v>-21.11046847888958</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-21.0081585081585</v>
+        <v>-12.85685676776217</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-13.44976795282829</v>
+        <v>-5.268429487179489</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-13.55460865664942</v>
+        <v>-5.401313592341147</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-13.33871727572519</v>
+        <v>-12.87915905750301</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-13.15187146575712</v>
+        <v>-12.66457261244403</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-13.6944176337232</v>
+        <v>-13.23201711382471</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-13.77026359513225</v>
+        <v>-13.30717963578005</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-13.49578888265025</v>
+        <v>-13.06354515050162</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-21.26392882818116</v>
+        <v>-13.22568414479097</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.183</t>
+          <t>X ≈ 0.1822</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>15</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>33.0258195532347</v>
+        <v>26.45737327188943</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>19.35770942155155</v>
+        <v>19.54479976951886</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>11.25302370585388</v>
+        <v>11.62343900096067</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>11.03103680215239</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>23.53761254719711</v>
+        <v>24.08881199538639</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>23.72457873329449</v>
+        <v>24.24574560138448</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>22.95263004940424</v>
+        <v>30.11733025581843</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>22.67441860465117</v>
+        <v>23.14574314574314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>16.0492391198992</v>
+        <v>16.60700538876063</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>15.55038308602463</v>
+        <v>16.08318890814563</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.27163368257673</v>
+        <v>15.80660695367433</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>14.14847161572057</v>
+        <v>14.6917148362235</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.260726072607355</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>7.094659726238724</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>7.655963745058386</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>13.72971922665884</v>
+        <v>14.21874999999999</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.5074365704286521</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.6942823803967713</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.1517362124307411</v>
+        <v>7.280803398995801</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0.07589025102164015</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>0.3503649635036936</v>
+        <v>7.449275362318893</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-6.392133956386289</v>
+        <v>-6.046196965303999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.1946</t>
+          <t>X ≈ 0.1938</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>11</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-8.186301658886514</v>
+        <v>1.002827817343913</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.5698306336727583</v>
+        <v>0.7569209816400715</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.8681884153582331</v>
+        <v>-0.4977731202515656</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.50976665610812</v>
+        <v>-1.090175319059732</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.173976183560846</v>
+        <v>-1.365733459159067</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.729966721250797</v>
+        <v>-10.29970894407007</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-2.501915405141219</v>
+        <v>-11.09479095630279</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.310782241014799</v>
+        <v>-2.308802308802321</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11.82954875888868</v>
+        <v>-11.27178249002736</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-12.60246443492517</v>
+        <v>-21.15874307615572</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-21.41931388367227</v>
+        <v>-20.88650806155146</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-3.516245105302211</v>
+        <v>-12.0721809251136</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-13.73031626306736</v>
+        <v>-13.18707304256437</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-13.95139513951395</v>
+        <v>-13.43530710399748</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-5.518629346185477</v>
+        <v>-5.026552394973507</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-4.924242424242486</v>
+        <v>-4.465248376153845</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-5.058159561219831</v>
+        <v>-4.569128787878796</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-5.163000265041141</v>
+        <v>-4.702012893040326</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-4.947108884116687</v>
+        <v>-4.487550665894624</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-4.760263074148789</v>
+        <v>-4.27296422083564</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-5.302809242114691</v>
+        <v>-4.840408722216374</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-5.37865520352392</v>
+        <v>-4.915571244171659</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-5.104180491041738</v>
+        <v>-4.671936758893281</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-5.180012744265085</v>
+        <v>-4.834075753182745</v>
       </c>
     </row>
   </sheetData>
@@ -3184,161 +3184,161 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3350</v>
+        <v>3374</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.216595705190052</v>
+        <v>-0.2308810701771264</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.209313117001237</v>
+        <v>-0.1666254366059832</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2371374728270084</v>
+        <v>-0.2273219219652489</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1918788793652979</v>
+        <v>-0.1848343430057255</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3032897977122602</v>
+        <v>-0.2672151192614081</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3074877750189486</v>
+        <v>-0.3002449646532668</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2906131938390004</v>
+        <v>-0.3122382097276244</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1657477649269694</v>
+        <v>-0.187590187590196</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.166709369451965</v>
+        <v>-0.1609694317371151</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1794831356061692</v>
+        <v>-0.2024266652938636</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1855669585783986</v>
+        <v>-0.2085146643374429</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1794866822855496</v>
+        <v>-0.2024499472904679</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2440702864911231</v>
+        <v>-0.2664338590005215</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2392739273927376</v>
+        <v>-0.2610109509779264</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.2248460232267391</v>
+        <v>-0.2459649658492111</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.208231811864934</v>
+        <v>-0.2289169961204536</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2053418397694671</v>
+        <v>-0.2266803460514666</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2030912824860849</v>
+        <v>-0.194213000625119</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1781073938037849</v>
+        <v>-0.1398415534622117</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1524677686790028</v>
+        <v>-0.08544067274370803</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1405393616820376</v>
+        <v>-0.04325148206238794</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.228405691699173</v>
+        <v>-0.1008362161664778</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.08532587505200695</v>
+        <v>0.04186795491143158</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.173228483749476</v>
+        <v>-0.07306912495619144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.1262</t>
+          <t>X &gt; -0.1261</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3321</v>
+        <v>3346</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2915648167812535</v>
+        <v>-0.2924041101230657</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2215108396908434</v>
+        <v>-0.1958969842420188</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3268685742179258</v>
+        <v>-0.3060729285513091</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1553308922579077</v>
+        <v>-0.1394920154352377</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3246629019045812</v>
+        <v>-0.2796872616715547</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3005784994098093</v>
+        <v>-0.2845754449888886</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3367647978096571</v>
+        <v>-0.349514822980268</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1484762110515589</v>
+        <v>-0.1618118810266438</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1498016474868891</v>
+        <v>-0.1360274387709026</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.155960414208252</v>
+        <v>-0.1711889636016153</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2544559461689246</v>
+        <v>-0.2689000072062058</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2159150722988485</v>
+        <v>-0.2307168501772168</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3313203010461905</v>
+        <v>-0.3455207908244446</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2945626294841972</v>
+        <v>-0.3082077432866726</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.2742941018501668</v>
+        <v>-0.2873571639749315</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2326888591532565</v>
+        <v>-0.2450499699088624</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.228614106674442</v>
+        <v>-0.2419319763396004</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2554941853077679</v>
+        <v>-0.2379208991154584</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.232190609366846</v>
+        <v>-0.1849001680784923</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1478228827611616</v>
+        <v>-0.07215010957376222</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1310556046571492</v>
+        <v>-0.02485998310836379</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2190239831041936</v>
+        <v>-0.0822922173442393</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.07708837785698108</v>
+        <v>0.05957314142450798</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1650939082080356</v>
+        <v>-0.05496365189490149</v>
       </c>
     </row>
     <row r="8">
@@ -3348,2293 +3348,2293 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3290</v>
+        <v>3315</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4564221209779973</v>
+        <v>-0.4569466801777082</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2618557958397503</v>
+        <v>-0.2374397669909811</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.5057601459532179</v>
+        <v>-0.4868727496388985</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3864157113733384</v>
+        <v>-0.3732610489220747</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4635962772210434</v>
+        <v>-0.4222857850575181</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4410802751697389</v>
+        <v>-0.4287218453601938</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5611286442758328</v>
+        <v>-0.5769474552660085</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.3382855695775149</v>
+        <v>-0.3547071694775141</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3703271937669612</v>
+        <v>-0.3599615782063808</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3996249015771554</v>
+        <v>-0.4181439336340844</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.4411397719832379</v>
+        <v>-0.459279040572369</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3391072824950356</v>
+        <v>-0.3581060009394861</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4450858921053893</v>
+        <v>-0.4636269156305772</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3756375637563707</v>
+        <v>-0.3936119570391767</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.3490187203759447</v>
+        <v>-0.3662307671427953</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2519892680596101</v>
+        <v>-0.2686024100224103</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3072841097075099</v>
+        <v>-0.3246977222556708</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.3031150046703814</v>
+        <v>-0.2893223014880135</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.2209397573406449</v>
+        <v>-0.1775835246021771</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1071748145030895</v>
+        <v>-0.03565287294880903</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.08512986713200377</v>
+        <v>0.01739170520431799</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.2035751195737845</v>
+        <v>-0.0700098113325609</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.06288328930704523</v>
+        <v>0.07090785126134591</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1813943413913606</v>
+        <v>-0.07334628657091713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1028</t>
+          <t>X &gt; -0.1029</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3250</v>
+        <v>3275</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5702696615529561</v>
+        <v>-0.5711288506090781</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6137657210727383</v>
+        <v>-0.588654886228781</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.6903167608739125</v>
+        <v>-0.6742956268710998</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5302667050261576</v>
+        <v>-0.5218210633003153</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.543146094589261</v>
+        <v>-0.5074235844557435</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5226672887372388</v>
+        <v>-0.5158699467479266</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.7265863570848907</v>
+        <v>-0.7473923039223607</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.467038835642775</v>
+        <v>-0.4884106069156289</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4693928351799244</v>
+        <v>-0.4649297682809603</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.45897067378435</v>
+        <v>-0.483765879439396</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5043722515992286</v>
+        <v>-0.5287332329736429</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3976898408241354</v>
+        <v>-0.4229843656645329</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5218749037520354</v>
+        <v>-0.5466702317415937</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4795602259612366</v>
+        <v>-0.5032467746768816</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4445687029317682</v>
+        <v>-0.467256635921288</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.3229811931469371</v>
+        <v>-0.3448485201462432</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.4080353532203418</v>
+        <v>-0.4308539000609457</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.4639830660238715</v>
+        <v>-0.454416539378812</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.3835004495405769</v>
+        <v>-0.3439808211052622</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2092210000580934</v>
+        <v>-0.1419930267354417</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1802650172034888</v>
+        <v>-0.08140933234449221</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2685131930128435</v>
+        <v>-0.138474675802577</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1602471558442389</v>
+        <v>-0.02935711631363347</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2485442127965527</v>
+        <v>-0.1428890772632414</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.09116</t>
+          <t>X &gt; -0.09124</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3207</v>
+        <v>3230</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.604911549615359</v>
+        <v>-0.6068751142157325</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.7373220834582597</v>
+        <v>-0.7135028135069632</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.8569163644085549</v>
+        <v>-0.8445195758875315</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.6537287632012507</v>
+        <v>-0.6510144798988833</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6311219441179219</v>
+        <v>-0.6018620581685425</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5819679623306016</v>
+        <v>-0.5818406055120775</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8400453075169239</v>
+        <v>-0.8671682556280373</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.5730200789874544</v>
+        <v>-0.6004059608495851</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.5139078780304018</v>
+        <v>-0.5167747858670495</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5236144250406696</v>
+        <v>-0.5556716716046708</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4802777799376585</v>
+        <v>-0.5125557727054826</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2438569401567534</v>
+        <v>-0.2781144117380165</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3851104738317161</v>
+        <v>-0.418847747341232</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3701707651324924</v>
+        <v>-0.4021982375552753</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3254404566679696</v>
+        <v>-0.3561995924810901</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.2104377104377164</v>
+        <v>-0.2398567202494633</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.2509841658092142</v>
+        <v>-0.2637955668829193</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.4180719907010371</v>
+        <v>-0.3784933964677464</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.3082545877282072</v>
+        <v>-0.238569353543916</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.1341199864671765</v>
+        <v>-0.03672427030997483</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.09748497136992285</v>
+        <v>0.03263348457158344</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1858735383208767</v>
+        <v>-0.02414460150739473</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1733258095636856</v>
+        <v>-0.009715662131789315</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2306122850423549</v>
+        <v>-0.0916046020428638</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.0795</t>
+          <t>X &gt; -0.07961</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3150</v>
+        <v>3173</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.78685783560163</v>
+        <v>-0.789184925857775</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.041869968564114</v>
+        <v>-1.018580512171276</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.043179092084472</v>
+        <v>-1.035713576789327</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.760435364093901</v>
+        <v>-0.7656016778559547</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.7629873896515349</v>
+        <v>-0.7420150722827827</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5900138125045231</v>
+        <v>-0.5991306129683878</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.9020302981471033</v>
+        <v>-0.9380511443905633</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6568076911768941</v>
+        <v>-0.6924506454139561</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5657888071742434</v>
+        <v>-0.5782727375464063</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4668770621461391</v>
+        <v>-0.5095146766919996</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.4276829268404896</v>
+        <v>-0.4704834082386</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2452439545541623</v>
+        <v>-0.2896777140389588</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4320918537318406</v>
+        <v>-0.4757893513811808</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.4445726396578777</v>
+        <v>-0.4858311950493714</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.3554997928119619</v>
+        <v>-0.3953884614839254</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1857932941583158</v>
+        <v>-0.2241578100081938</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.383081787282805</v>
+        <v>-0.4038915094339615</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.4245511349569711</v>
+        <v>-0.3924815938897126</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.2849564565126599</v>
+        <v>-0.2224325241244927</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1427499594891302</v>
+        <v>-0.0522871956260289</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.06393140571074696</v>
+        <v>0.05998056104444771</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.1208102565926126</v>
+        <v>0.0350372024997867</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1129800063471933</v>
+        <v>0.04536862003781295</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1381657024180356</v>
+        <v>-0.003545426276744479</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.06783</t>
+          <t>X &gt; -0.06797</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3051</v>
+        <v>3078</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.101784613431967</v>
+        <v>-1.043432919661711</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.12638913483616</v>
+        <v>-1.046598079943493</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.211688563418633</v>
+        <v>-1.219413532114565</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.766544846009829</v>
+        <v>-0.7615175339784415</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.9213183524116459</v>
+        <v>-0.8901999516591417</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.6184274616842131</v>
+        <v>-0.6185954838868426</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.8829863889519203</v>
+        <v>-0.9112104011551878</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.6208505633749297</v>
+        <v>-0.6810183280771582</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4303083126508369</v>
+        <v>-0.4702658689180552</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.4011169740282483</v>
+        <v>-0.4719266584208057</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.467470168928557</v>
+        <v>-0.5371065733598712</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.04144483206999183</v>
+        <v>-0.1157231434131063</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2306133515997359</v>
+        <v>-0.3055874190910473</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2689677271094126</v>
+        <v>-0.3082463409263596</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.1229458929480103</v>
+        <v>-0.161576101425716</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1304755107502871</v>
+        <v>-0.164299810785252</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.3625280746168613</v>
+        <v>-0.3787648568341453</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.4346569694750215</v>
+        <v>-0.3953273606739245</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.2320922253828144</v>
+        <v>-0.1617758892602907</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.09131500094533607</v>
+        <v>0.007019260964845841</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.04040680837044874</v>
+        <v>0.1727216073696667</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.01582281809074715</v>
+        <v>0.149363820763412</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.01660751356057233</v>
+        <v>0.1525339960743892</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.138446640752079</v>
+        <v>0.00968347654139734</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.05617</t>
+          <t>X &gt; -0.05634</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2921</v>
+        <v>2946</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.703389601535299</v>
+        <v>-1.723219720024346</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.408469882540025</v>
+        <v>-1.412396051175435</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.672146362173315</v>
+        <v>-1.671683498477456</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.073857953375622</v>
+        <v>-1.133100353553054</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.254763218629883</v>
+        <v>-1.255317559269471</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5723228669777924</v>
+        <v>-0.6074437337488376</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.9165797598600705</v>
+        <v>-0.9787759787077945</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6645933203914254</v>
+        <v>-0.7245709373368996</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5697111186829318</v>
+        <v>-0.6114630797078888</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.6413944786284844</v>
+        <v>-0.7126464218806348</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5864973141572634</v>
+        <v>-0.6578523359382586</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1974894835782521</v>
+        <v>-0.2727527577449536</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4476603524251033</v>
+        <v>-0.5225386594914241</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4779788323659844</v>
+        <v>-0.5480589883229641</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.2963243287984341</v>
+        <v>-0.3641531828112008</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.09149403153502789</v>
+        <v>-0.1553016347813667</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.4987285583314289</v>
+        <v>-0.5639568517891504</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.6377339358799787</v>
+        <v>-0.6431313951344961</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.5383597385255072</v>
+        <v>-0.4765836593328956</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1946065084921571</v>
+        <v>-0.1065543595105254</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.0671420365433093</v>
+        <v>0.05801601344133189</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1567474499705384</v>
+        <v>0.003017629641099973</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.1013804163731393</v>
+        <v>0.06323305941193524</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.122591562229033</v>
+        <v>0.02304947054125961</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.04451</t>
+          <t>X &gt; -0.04471</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2744</v>
+        <v>2770</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.646272068224008</v>
+        <v>-2.700030815597152</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.985754157802035</v>
+        <v>-2.031001282609303</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.463950597439627</v>
+        <v>-2.513625943424024</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.70950791436124</v>
+        <v>-1.759104379948589</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.735839100756429</v>
+        <v>-1.728064126696189</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.8406386580097518</v>
+        <v>-0.9051164675810384</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9763297186276532</v>
+        <v>-1.105570690402679</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.9441455722886474</v>
+        <v>-1.067053403502008</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.809665486557094</v>
+        <v>-0.8831060819334127</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.8001158401237376</v>
+        <v>-0.8317319577776985</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9045473434974411</v>
+        <v>-0.9349231225609174</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4364273196020036</v>
+        <v>-0.4352936942738808</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7395293529197531</v>
+        <v>-0.809425483065894</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.7576847801059117</v>
+        <v>-0.7846652386582136</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.7402016669943734</v>
+        <v>-0.7611961296171827</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.596969696969694</v>
+        <v>-0.6112797060351483</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.9127050157653471</v>
+        <v>-0.931454277817835</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.9811820832228975</v>
+        <v>-0.9561913029505931</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.7803044262973842</v>
+        <v>-0.7777781024811077</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.6084832673470828</v>
+        <v>-0.5631916574221236</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.3651913449045736</v>
+        <v>-0.280201529481225</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3829589842296741</v>
+        <v>-0.2618915904920058</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3418026139098203</v>
+        <v>-0.2134216183139017</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.2502486308274996</v>
+        <v>-0.1376530423195987</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.03284</t>
+          <t>X &gt; -0.03307</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2534</v>
+        <v>2556</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.601692845616775</v>
+        <v>-3.600969785286793</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.389254934108457</v>
+        <v>-2.58230788288062</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.592326346392703</v>
+        <v>-2.766077023432786</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.598960759165742</v>
+        <v>-1.702608057660683</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.678073727312594</v>
+        <v>-1.723420182252873</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5673004350067004</v>
+        <v>-0.7269745856770982</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6894421640965405</v>
+        <v>-0.8378354361893727</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5921695382620626</v>
+        <v>-0.731011924459672</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6069536007082874</v>
+        <v>-0.6592190877643276</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5324519326926236</v>
+        <v>-0.5746823281605558</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.7467867252961113</v>
+        <v>-0.7878250187059166</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6098711017987668</v>
+        <v>-0.6517263796590527</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8449718671014068</v>
+        <v>-0.884682193866368</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.7282546436461743</v>
+        <v>-0.7584999393091536</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.6940051514824788</v>
+        <v>-0.7530785086720186</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.6670187499254041</v>
+        <v>-0.7392911108926512</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.116020565910361</v>
+        <v>-1.234254823360715</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.378403609235292</v>
+        <v>-1.367138928522316</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.280668982938771</v>
+        <v>-1.191785031450841</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.110288147578053</v>
+        <v>-0.9771985863918573</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.8415629598199885</v>
+        <v>-0.6842598261378683</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.8941412947197307</v>
+        <v>-0.6973325188906685</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.030305647936189</v>
+        <v>-0.8449343403415597</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.9251515833265671</v>
+        <v>-0.8114551812663962</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02118</t>
+          <t>X &gt; -0.02144</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2260</v>
+        <v>2281</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.474912082703256</v>
+        <v>-4.566591869722799</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.646243147618407</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.392553329881309</v>
+        <v>-3.582259501728721</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.104618958277491</v>
+        <v>-2.276118520709737</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.108825447525739</v>
+        <v>-2.310140427136531</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9740574303657752</v>
+        <v>-1.125433437916833</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.7533558660887181</v>
+        <v>-0.9792184554091818</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6104779167050651</v>
+        <v>-0.7790820290820406</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7642704248878758</v>
+        <v>-0.888986449163923</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9393369057773668</v>
+        <v>-1.048188713632854</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.43374389810235</v>
+        <v>-1.582748363918611</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.070080771180159</v>
+        <v>-1.22199783324924</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.197218293076183</v>
+        <v>-1.373667533887414</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.392695560946819</v>
+        <v>-1.553015064018183</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.344437092522959</v>
+        <v>-1.421261979867083</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.456451936584386</v>
+        <v>-1.517276103028131</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.899419846188792</v>
+        <v>-1.927904981010805</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.180860991511075</v>
+        <v>-2.148431505103176</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.964969610586749</v>
+        <v>-1.846326859026632</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.576035640804683</v>
+        <v>-1.45645557610613</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.430234622743846</v>
+        <v>-1.278939516575385</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.612880748094234</v>
+        <v>-1.460148981208839</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.887582847199575</v>
+        <v>-1.654918704610864</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.495378794144408</v>
+        <v>-1.378653490219925</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.009514</t>
+          <t>X &gt; -0.009805</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1917</v>
+        <v>1942</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.529103709396786</v>
+        <v>-5.591807055979451</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.389702586730024</v>
+        <v>-4.377974875962082</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.885937108922555</v>
+        <v>-3.761176383654771</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.655094389581947</v>
+        <v>-2.582782250353169</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.600282735332591</v>
+        <v>-2.625767060055082</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.348035374589223</v>
+        <v>-1.465605194712083</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.31306792672445</v>
+        <v>-1.541632250601715</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9166556039632567</v>
+        <v>-1.098861170803623</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7713801501232851</v>
+        <v>-0.8394384844185083</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.25534841491195</v>
+        <v>-1.246659275183035</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.575158039516488</v>
+        <v>-1.614529396881018</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.356917945974992</v>
+        <v>-1.347529675230625</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.514554905340326</v>
+        <v>-1.53554228701713</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.497511873976151</v>
+        <v>-1.474816513228831</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.479276399444323</v>
+        <v>-1.436064612930565</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.665326522246396</v>
+        <v>-1.595666876294224</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.059389340805552</v>
+        <v>-1.957013817370409</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.372346589892082</v>
+        <v>-2.141391228402242</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.104426072651421</v>
+        <v>-1.823942389516006</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.523312622206085</v>
+        <v>-1.197409497495123</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.410763787569302</v>
+        <v>-1.095441022562781</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.508268164819988</v>
+        <v>-1.170603544518066</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.933263816475495</v>
+        <v>-1.544888729682526</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.248680643918895</v>
+        <v>-1.037614747658914</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.00215</t>
+          <t>X &gt; 0.001829</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1540</v>
+        <v>1563</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.633135031169758</v>
+        <v>-5.616653530918512</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.522247705994005</v>
+        <v>-4.713868598913386</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.512742059911872</v>
+        <v>-4.500789886510134</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.583132717538192</v>
+        <v>-3.592207131436368</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.305170957957429</v>
+        <v>-3.387226343271749</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.472068591012302</v>
+        <v>-1.662182787362319</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.692531240918335</v>
+        <v>-1.817878610336734</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.196549137284322</v>
+        <v>-1.447986860654815</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.090545826337362</v>
+        <v>-1.192098897867702</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.891741974686887</v>
+        <v>-1.924170866535533</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.968996758936605</v>
+        <v>-2.035813011240222</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.823819883465163</v>
+        <v>-1.928517806402496</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.810993671041018</v>
+        <v>-2.019737499029212</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.347688166874939</v>
+        <v>-1.628176294947281</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.811656707173945</v>
+        <v>-2.118392097177832</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.864518976169457</v>
+        <v>-2.132903817321697</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.38678562771004</v>
+        <v>-2.620661388355728</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.426901412437374</v>
+        <v>-2.561606913862825</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.952110355137634</v>
+        <v>-2.091226580511027</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.468930054836434</v>
+        <v>-1.620722029246032</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.9370518627475306</v>
+        <v>-1.164494105802717</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.234096778809786</v>
+        <v>-1.495574733964013</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.31089395927377</v>
+        <v>-1.507858354891646</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.089103653355991</v>
+        <v>-1.286120189872086</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.01381</t>
+          <t>X &gt; 0.01346</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1212</v>
+        <v>1232</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-7.719150539206844</v>
+        <v>-7.668840320343605</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.770077419122728</v>
+        <v>-5.811187285497319</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.617724593465837</v>
+        <v>-5.609570707777245</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.084113320124793</v>
+        <v>-3.975710836174187</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.396156872263134</v>
+        <v>-3.317995135894002</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.856435996656302</v>
+        <v>-1.57744985684748</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.829515732741534</v>
+        <v>-2.859149873946379</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.288726358493797</v>
+        <v>-2.308802308802321</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.919638848978764</v>
+        <v>-1.856198074442879</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.138977102585372</v>
+        <v>-3.22043138784403</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.983934660762344</v>
+        <v>-3.110534035577359</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.560878632694298</v>
+        <v>-2.737765340698019</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.652404856478874</v>
+        <v>-2.878631484122813</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.840151120375189</v>
+        <v>-2.152839571529945</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.745004944271543</v>
+        <v>-2.997331615752664</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.972986443381181</v>
+        <v>-3.247715908621316</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-3.68256147509549</v>
+        <v>-4.000946969696969</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.787402178916672</v>
+        <v>-3.890324581352075</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.407037113781833</v>
+        <v>-3.513524691868639</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-3.420943957051826</v>
+        <v>-3.542444740316149</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.811226750532263</v>
+        <v>-2.811187942995588</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.004834625419917</v>
+        <v>-3.048688127288536</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.765875761970378</v>
+        <v>-2.886222473178989</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.629757718762527</v>
+        <v>-2.88602380513079</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.02548</t>
+          <t>X &gt; 0.0251</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-8.682863920154652</v>
+        <v>-8.249739698821898</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.971422231109514</v>
+        <v>-5.880583773019488</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.04560931202203</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.810807506571301</v>
+        <v>-3.69845708964516</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.826981762602578</v>
+        <v>-2.717470727126702</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.634071055734942</v>
+        <v>-1.303992618510811</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.453916941092061</v>
+        <v>-2.41321075639798</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.148179072223179</v>
+        <v>-1.08905769283129</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.106691890308475</v>
+        <v>-1.065950586082188</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.088722363043559</v>
+        <v>-3.11986371652165</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.968135432493881</v>
+        <v>-3.057272307787343</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.765089481265171</v>
+        <v>-2.809745247583585</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.92081081623423</v>
+        <v>-2.037844912204164</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.974942717201657</v>
+        <v>-2.181257170702267</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-3.05771446488837</v>
+        <v>-3.282698764327364</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.675641767998457</v>
+        <v>-2.826216548442709</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-3.764972917714786</v>
+        <v>-3.873493186582806</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.551342283956345</v>
+        <v>-3.69191188293938</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.910822452925864</v>
+        <v>-3.058162444053565</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.617819530431298</v>
+        <v>-2.843575998994581</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.417265910711556</v>
+        <v>-2.572446076895233</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.963429621454495</v>
+        <v>-3.171717613525573</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.096443547134648</v>
+        <v>-2.40397411357214</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.684998706120055</v>
+        <v>-2.146825896121562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.03714</t>
+          <t>X &gt; 0.03673</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-8.990913163630118</v>
+        <v>-8.562183442582565</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-6.023180054450208</v>
+        <v>-5.679015962771444</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.281367828537647</v>
+        <v>-4.717282424506571</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.543815523301873</v>
+        <v>-3.024663807073019</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.289973659699342</v>
+        <v>-0.9503524954752223</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2982839125774674</v>
+        <v>0.7731607449876137</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.6643912271915084</v>
+        <v>-0.4135661758612912</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3871845620979784</v>
+        <v>0.4564481065786552</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2362218730085957</v>
+        <v>-0.1989128009696159</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.264732925422685</v>
+        <v>-2.169899022037519</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.982950247308693</v>
+        <v>-3.203147036153808</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.195032984090027</v>
+        <v>-2.30479426477654</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.374447832432566</v>
+        <v>-1.592010142018438</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.250860380155657</v>
+        <v>-1.579147597707419</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.711142715169373</v>
+        <v>-3.175140099696918</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.98306595365419</v>
+        <v>-2.352739475133127</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.518052609348246</v>
+        <v>-2.848264795474329</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.756583152741619</v>
+        <v>-3.111697203507987</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.139622253100711</v>
+        <v>-2.505590067746027</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.551706924416109</v>
+        <v>-2.029907016942921</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.960563252809948</v>
+        <v>-2.20570660970747</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.360522064908785</v>
+        <v>-2.803062343150998</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.204594822019146</v>
+        <v>-1.906686343512305</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.201977356833716</v>
+        <v>-1.938277034929712</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0488</t>
+          <t>X &gt; 0.04836</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-9.326465842528961</v>
+        <v>-8.932344804395839</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-7.152881436865393</v>
+        <v>-6.856526930315297</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-5.832403429824495</v>
+        <v>-5.291983884611518</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.609818456765574</v>
+        <v>-2.977822555544179</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.000202578853205</v>
+        <v>-0.5955733866734079</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1218851306009938</v>
+        <v>0.7241509169991005</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5549584834794032</v>
+        <v>-0.4031570088548833</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3472685203341328</v>
+        <v>0.4547132454109146</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.634853066722492</v>
+        <v>-1.576826283443189</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.651604484065217</v>
+        <v>-2.705103692283778</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.391058355416803</v>
+        <v>-3.429546418543239</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.980618569675606</v>
+        <v>-1.878885848097589</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.245672528423626</v>
+        <v>-1.166535440631421</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.030306076292909</v>
+        <v>-1.248656545253901</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.87288253800206</v>
+        <v>-3.093601624813367</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.601676665128444</v>
+        <v>-1.701732821940553</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.904798539838573</v>
+        <v>-1.805613233665561</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.009639243659755</v>
+        <v>-2.104610295637798</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.624543125002774</v>
+        <v>-1.724035111681388</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.099287839569428</v>
+        <v>-1.343335709811775</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.472629269802809</v>
+        <v>-1.744667254381881</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.110550426944499</v>
+        <v>-1.487603862715901</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.9060017597561085</v>
+        <v>-1.410082334248152</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.222065929175407</v>
+        <v>-1.904447242158881</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.06047</t>
+          <t>X &gt; 0.06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-10.22520925334966</v>
+        <v>-9.895085744504037</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.88508893235791</v>
+        <v>-7.68197618676529</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.929106878338544</v>
+        <v>-5.657981764066704</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.407588715792706</v>
+        <v>-1.947105274350335</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.975845009738606</v>
+        <v>-0.5833191521545871</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.19345840134438</v>
+        <v>1.827712814499229</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5409876377618303</v>
+        <v>0.6227947366927395</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.925977856210416</v>
+        <v>1.957218555579203</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5273374566773725</v>
+        <v>-0.5787869609661911</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.390343222803956</v>
+        <v>-1.579756488972414</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.741283580642033</v>
+        <v>-1.922275572728736</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2716336825766419</v>
+        <v>0.05524083345569863</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.6068049490538527</v>
+        <v>0.3747749455131242</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8023927392739267</v>
+        <v>0.5363769496537927</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8974172249732959</v>
+        <v>-1.170367596165697</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.5113636363636331</v>
+        <v>-0.6090635773460349</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.1880525599922223</v>
+        <v>0.1067281420764985</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.7082118561710402</v>
+        <v>0.5885981352755536</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.9241032370953661</v>
+        <v>0.8030603624213271</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.527615713730057</v>
+        <v>1.427482873054075</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.9850695457640271</v>
+        <v>0.8600383716733404</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.244992547472535</v>
+        <v>0.989793882504955</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.647436093210764</v>
+        <v>1.233428367783333</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.280822018456476</v>
+        <v>0.661453307920091</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.07213</t>
+          <t>X &gt; 0.07163</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-8.528065158544749</v>
+        <v>-8.133197447713577</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-8.862841956894563</v>
+        <v>-8.627243241233828</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-7.172436930662023</v>
+        <v>-6.904269849328877</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.977982370683726</v>
+        <v>-2.782031849625938</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.664407654822988</v>
+        <v>-1.568756242827007</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.433439492788267</v>
+        <v>1.069566941334855</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.835878780368709</v>
+        <v>1.515179718184022</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.826702868610553</v>
+        <v>2.450954063857289</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1774952286625577</v>
+        <v>-0.6469234780715141</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4427966915010799</v>
+        <v>-0.946697057658092</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.9301583691361017</v>
+        <v>-1.418878916502891</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.329163293405742</v>
+        <v>0.7859287071895764</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.728843866143542</v>
+        <v>1.15987033663707</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.761572096295929</v>
+        <v>1.159775233020341</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.3420074789184184</v>
+        <v>-0.2667960223138408</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.6825872942624187</v>
+        <v>0.2945079965058213</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.056284370482913</v>
+        <v>0.6869055004135589</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.966672093057674</v>
+        <v>1.546577226517464</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.674949260784032</v>
+        <v>1.264761538030491</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.115602177351036</v>
+        <v>1.727486940905855</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.84209154237994</v>
+        <v>2.400737228606999</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.925763024558492</v>
+        <v>2.325574706651715</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.105467004319976</v>
+        <v>2.321070234113719</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.029634751096701</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0838</t>
+          <t>X &gt; 0.08326</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-10.56855795680546</v>
+        <v>-10.25904463855836</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-7.590081743107085</v>
+        <v>-7.818384310083125</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.960470755374708</v>
+        <v>-4.893973934362769</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.490233343891873</v>
+        <v>-2.202794043618752</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.704811695227022</v>
+        <v>-0.3887999449121153</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5634845083705784</v>
+        <v>0.6636560491456791</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.403849561599358</v>
+        <v>2.256633738405483</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.954906409529215</v>
+        <v>3.742758071116278</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3378570060780604</v>
+        <v>0.2885974285615802</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1301806211779422</v>
+        <v>-0.2089466039711922</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.4658770765769944</v>
+        <v>-0.5337265147399961</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4748857150969599</v>
+        <v>0.6822288442215481</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.8761138921432874</v>
+        <v>1.059874040203603</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.264791113257672</v>
+        <v>1.408654904143631</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.6128643794448436</v>
+        <v>-0.4675293284876929</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.5912786400591301</v>
+        <v>0.3922821530185416</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.981751746984095</v>
+        <v>1.78093905472636</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.181789091943401</v>
+        <v>1.946562412251332</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.397680472867727</v>
+        <v>2.161024639397105</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.584526282835753</v>
+        <v>2.375611084456089</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.651736212430698</v>
+        <v>2.405181508448493</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.072832147046057</v>
+        <v>2.628526449179766</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.540549012583405</v>
+        <v>2.872160934458144</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.46471675936013</v>
+        <v>3.008529402855252</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.09546</t>
+          <t>X &gt; 0.0949</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-13.78844858944673</v>
+        <v>-13.32523542376277</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-11.17119586750134</v>
+        <v>-11.03491037540867</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-8.006235553405361</v>
+        <v>-7.941778390343728</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.274745128403666</v>
+        <v>-3.824035661615724</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.64757263798797</v>
+        <v>-1.201043077077372</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.345396577160763</v>
+        <v>1.854441253558392</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.400391243434086</v>
+        <v>3.595591125383642</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.360985768830275</v>
+        <v>5.826902566032999</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.9248610104464703</v>
+        <v>1.244686548180873</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1519453344099801</v>
+        <v>0.08631621238182419</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6933980085027258</v>
+        <v>-0.7284052947529744</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5203899014821118</v>
+        <v>0.806606953674283</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.516630819700616</v>
+        <v>0.4163525173829257</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.041820599970443</v>
+        <v>0.8927561371092381</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7357256826847376</v>
+        <v>-0.8763547665149432</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.9780642243328757</v>
+        <v>0.7719057740438444</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>2.336684400788243</v>
+        <v>1.754981884057976</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.604978025325266</v>
+        <v>1.984416619476086</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.074600749533175</v>
+        <v>1.474241165462431</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.261446559501202</v>
+        <v>2.051146451101133</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.465169048251589</v>
+        <v>1.846020790300109</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.016188758484283</v>
+        <v>1.408539427765113</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.036932127682761</v>
+        <v>2.376811594202898</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.961099874459485</v>
+        <v>2.214672599913435</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.1071</t>
+          <t>X &gt; 0.1065</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-11.74895522154007</v>
+        <v>-11.5072284980221</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.930578866736738</v>
+        <v>-8.655790200982615</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.187398616921371</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.090397885232882</v>
+        <v>-3.423240483983292</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.353790167734914</v>
+        <v>0.2835022608731208</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.270033278749139</v>
+        <v>3.095303123508373</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.683223656710183</v>
+        <v>4.070132615700437</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.601359243920569</v>
+        <v>6.420079428928979</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.07663638017317</v>
+        <v>1.238273825338752</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.847099699570478</v>
+        <v>-0.0002555459867821241</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2487036719662328</v>
+        <v>-0.6129762835948327</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.582135965681665</v>
+        <v>2.65026477078343</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.6324898805607049</v>
+        <v>0.2079390250140705</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.237895022378957</v>
+        <v>1.729616468005744</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.6665097156659812</v>
+        <v>0.1625063339082971</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.717517642175174</v>
+        <v>1.608766104940351</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.779947537161178</v>
+        <v>4.159752949852503</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.305243819641362</v>
+        <v>2.699435216372315</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.064514195999479</v>
+        <v>2.471419567411893</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.621223019666132</v>
+        <v>4.013439640789464</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.6220558471339</v>
+        <v>3.003517263302534</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.546209885724799</v>
+        <v>2.928354741347249</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>4.733926607339271</v>
+        <v>4.056944978838018</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5.114715358682197</v>
+        <v>4.33728386065475</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.1188</t>
+          <t>X &gt; 0.1182</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-13.74447405643715</v>
+        <v>-13.74670836076366</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-11.48857727965743</v>
+        <v>-10.93139070667161</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-8.017809627479444</v>
+        <v>-7.084043992236666</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-6.647430313588842</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.379054119469451</v>
+        <v>-2.849963514817688</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.31620176994381</v>
+        <v>2.409010907506925</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.426314259930557</v>
+        <v>3.144541140172173</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.358629130966953</v>
+        <v>6.921253349824774</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.189589997092185</v>
+        <v>2.457345524815004</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.416674321055694</v>
+        <v>1.661294029595666</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.164418173743925</v>
+        <v>1.423324962567349</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.043563507138046</v>
+        <v>3.697763416259313</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.394085650808243</v>
+        <v>2.072667217175884</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.751954142782701</v>
+        <v>3.865249482273391</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2.04117926625478</v>
+        <v>1.652482855490376</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>2.109250398724086</v>
+        <v>2.213786874310038</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.080596419641346</v>
+        <v>4.150722789115648</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.396808347399116</v>
+        <v>2.48722643905608</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.612699728323442</v>
+        <v>2.701688666201854</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>4.904808696186208</v>
+        <v>4.957091437791455</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.835946738746486</v>
+        <v>3.87944285477807</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.707469198390015</v>
+        <v>2.783872169557476</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.508259700345754</v>
+        <v>3.537710736468505</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.485059026069855</v>
+        <v>4.395979905444349</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.1305</t>
+          <t>X &gt; 0.1298</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-12.53655263490436</v>
+        <v>-12.07921209396426</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-9.190347838162147</v>
+        <v>-9.276338441863246</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-4.796359010195488</v>
+        <v>-4.433471568145073</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.274745128403666</v>
+        <v>-3.19660547427037</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.758683749099077</v>
+        <v>-2.252651419247748</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.749270091319289</v>
+        <v>2.172574869677156</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.446457209898071</v>
+        <v>3.816517247688346</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.489233419465975</v>
+        <v>7.77988948720656</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.444300848294262</v>
+        <v>4.859037909085785</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.671385172257772</v>
+        <v>4.062986413866447</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.328160863802417</v>
+        <v>3.725465330909806</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.901263312206268</v>
+        <v>5.278151669121435</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.77810124535015</v>
+        <v>4.163259551670663</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.79159027013813</v>
+        <v>5.134537685359511</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2.898879071323002</v>
+        <v>3.232871108352498</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.875982042648708</v>
+        <v>3.184419029611185</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.211200708140368</v>
+        <v>5.519563008130085</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.254508152467338</v>
+        <v>3.557410610285551</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.470399533391664</v>
+        <v>3.771872837431324</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>6.12638114582883</v>
+        <v>6.425483672734217</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>5.5838349778628</v>
+        <v>5.858039171353482</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.273421115219129</v>
+        <v>4.563364454276247</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>5.165179778318461</v>
+        <v>5.4167550371156</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.323915426329769</v>
+        <v>6.474128237948086</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.1421</t>
+          <t>X &gt; 0.1414</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>144</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-11.9741804467653</v>
+        <v>-11.87596006144393</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-8.836735022892888</v>
+        <v>-8.649644674925575</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.108087405257216</v>
+        <v>-5.737672110150491</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-4.043263646922178</v>
+        <v>-3.552296531180936</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.990165230580565</v>
+        <v>-2.438965782391385</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.057912066627928</v>
+        <v>2.579078934717813</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.369296716070906</v>
+        <v>3.867330255818423</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.563307493540051</v>
+        <v>7.034632034632025</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.438128008788091</v>
+        <v>2.995894277649469</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.970767888307158</v>
+        <v>1.505398337985689</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.939271974913524</v>
+        <v>2.472077797034466</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.132744793687749</v>
+        <v>5.66771806478539</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.315138282387188</v>
+        <v>3.858381502890175</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.788503850385041</v>
+        <v>4.304591885901509</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.741471663915597</v>
+        <v>2.233548615127567</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.641414141414145</v>
+        <v>2.100408189502787</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.590830337770001</v>
+        <v>4.079861111111107</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.40265630061549</v>
+        <v>1.863643672616178</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.312992125984259</v>
+        <v>2.772550344206394</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.888726824841171</v>
+        <v>4.376025678154264</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>4.040625101319584</v>
+        <v>4.503025621217972</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.27033469546604</v>
+        <v>3.733418654818244</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>4.239253852392537</v>
+        <v>4.671497584541065</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>4.857866043613718</v>
+        <v>5.203803034696058</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.1538</t>
+          <t>X &gt; 0.1531</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-9.73840808904172</v>
+        <v>-9.994239631336406</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.44716862722894</v>
+        <v>-8.627243241233828</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.007138895772123</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-6.533101045296164</v>
+        <v>-6.442081477417496</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.616858997518236</v>
+        <v>-2.68538155300071</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.6351478389856453</v>
+        <v>1.503810117513517</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.302223545339203</v>
+        <v>3.128082943990471</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.463036490830028</v>
+        <v>5.242517339291524</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.065499282500831</v>
+        <v>2.95109141026596</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.292583606464341</v>
+        <v>2.155039915046622</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.05937301153633712</v>
+        <v>0.8143717038445075</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.726918235422168</v>
+        <v>4.570047813889332</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.603756168566051</v>
+        <v>3.45515569643856</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.195685422200754</v>
+        <v>4.013373247908682</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.7144903957049991</v>
+        <v>0.105412414410722</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.9331116038433152</v>
+        <v>-0.1397351796728401</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.37199564942312</v>
+        <v>2.175739247311824</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.3588613145606629</v>
+        <v>0.4299519163437751</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.6700381964449704</v>
+        <v>1.450865756392773</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.482900266575591</v>
+        <v>3.278355427258205</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.753362228690854</v>
+        <v>3.517362538780702</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.86450813720046</v>
+        <v>2.635748403922186</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.764999109845114</v>
+        <v>4.492286115007019</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.315183116784432</v>
+        <v>5.943050346523997</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.1654</t>
+          <t>X &gt; 0.1647</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.344550817135669</v>
+        <v>-7.671067095083075</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.901549837707705</v>
+        <v>-5.164680352805291</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.487717034886842</v>
+        <v>-4.584512069375776</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-5.176914268183999</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.9068318972472298</v>
+        <v>-0.8653164449805786</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.057912066627928</v>
+        <v>2.96134193165971</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.137815234589425</v>
+        <v>4.001122304748094</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.637381567614128</v>
+        <v>6.448495439321121</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.975165045825122</v>
+        <v>2.906699578363025</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.128175295714563</v>
+        <v>3.028079275804245</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>1.465451905087477</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.975337386280344</v>
+        <v>4.858594721258385</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.926249393498303</v>
+        <v>2.826271411147054</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.705170517051712</v>
+        <v>2.578037349713945</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-2.656676484232555</v>
+        <v>-1.773841802813315</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-1.136363636363633</v>
+        <v>-0.295106591333095</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1.507497004436672</v>
+        <v>2.353306574923543</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-2.301047403088219</v>
+        <v>-1.449302300880262</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2333041703120458</v>
+        <v>0.6000223115866135</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>1.805393491507843</v>
+        <v>2.6494711419667</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.188773249467737</v>
+        <v>2.999457833246524</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>1.187001362132712</v>
+        <v>2.006864118630681</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.387402000540689</v>
+        <v>3.167929796569616</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.163421599169261</v>
+        <v>4.840653187601255</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.1771</t>
+          <t>X &gt; 0.1763</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-8.377689218695124</v>
+        <v>-8.750960061443926</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.501939701255466</v>
+        <v>-4.83020023048114</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.887327171339088</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.495018032887096</v>
+        <v>-3.552296531180936</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.484980968249836</v>
+        <v>2.422145328719729</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.671947154347215</v>
+        <v>2.579078934717813</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.057893207298982</v>
+        <v>5.950663589151759</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.990208078335371</v>
+        <v>8.77074314574314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.821168944460609</v>
+        <v>4.732005388760584</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.100884847371482</v>
+        <v>4.97762056020791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.322312910586042</v>
+        <v>4.20818890814558</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.201458243980156</v>
+        <v>7.05660695367429</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.025664598176668</v>
+        <v>4.90004816955684</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.804585721730078</v>
+        <v>4.65181410812373</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.9885476873074097</v>
+        <v>0.8446597262386746</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.582934609250401</v>
+        <v>1.405963745058337</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.554280630167661</v>
+        <v>3.385416666666664</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.7610863894430011</v>
+        <v>-0.914134105161601</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.560068149376072</v>
+        <v>2.425328121984172</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.852177117238831</v>
+        <v>4.723247900376485</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>4.362262528220178</v>
+        <v>5.197470065662429</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>3.2337849878637</v>
+        <v>4.080640877040466</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>4.560891279293131</v>
+        <v>5.365942028985522</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.642953762911951</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.1888</t>
+          <t>X &gt; 0.188</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-16.14084711343197</v>
+        <v>-15.271021789839</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-8.975623911781781</v>
+        <v>-9.344089119370025</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.913642960812773</v>
+        <v>-8.129647418792473</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-6.252913815131556</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.46238745280278</v>
+        <v>-1.590200350292619</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.275421266705401</v>
+        <v>-1.433266744294535</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.702630049404242</v>
+        <v>1.475354947176456</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.424418604651159</v>
+        <v>6.108706108706102</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>2.5329313146865</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.442990110529379</v>
+        <v>4.206015621936302</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.217049752691302</v>
+        <v>2.009114834071497</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.688300349243299</v>
+        <v>5.436236583303909</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.315138282387188</v>
+        <v>3.086776564618567</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.344059405940591</v>
+        <v>4.073110404420028</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>-0.3127476811687373</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.2485563376509248</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.646385893325565</v>
+        <v>1.379243827160494</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.208454810495631</v>
+        <v>-2.457343981704817</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.757436570428709</v>
+        <v>1.460821949144666</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.444282380396722</v>
+        <v>4.144544196672783</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>5.151736212430698</v>
+        <v>4.811667596526618</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>3.82589025102159</v>
+        <v>3.501937173336763</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.350364963503651</v>
+        <v>4.980139559849711</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>10.27453271028038</v>
+        <v>9.756272170498512</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.2004</t>
+          <t>X &gt; 0.1996</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-17.40896305546095</v>
+        <v>-17.82834101382488</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-10.49736304221656</v>
+        <v>-10.93139070667161</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-9.036831366609874</v>
+        <v>-9.328941951420333</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-8.300510023733771</v>
+        <v>-7.064201293085702</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-2.839199047005678</v>
+        <v>-1.625473718899322</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-1.202957498589463</v>
+        <v>-0.03996868432980705</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.372919904476703</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.442534546680143</v>
+        <v>7.431457431457432</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5.034746366276011</v>
+        <v>4.702243483998679</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.160381414877207</v>
+        <v>8.191906274493618</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>5.98516569472028</v>
+        <v>5.606998431955098</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7.155691653591134</v>
+        <v>8.187559334626656</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>6.032529586735016</v>
+        <v>5.644095788604467</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>6.824433155742774</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.8054813257513516</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>1.399868247694343</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.715226473035699</v>
+        <v>2.313988095238095</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-1.737440317741999</v>
+        <v>-2.104610295637798</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.826277150138843</v>
+        <v>2.395566217222267</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>5.911673684744557</v>
+        <v>5.467295519424113</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>6.328422446614795</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>5.293281555369425</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>6.496894409937887</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>12.73830082622241</v>
+        <v>12.04904112993415</v>
       </c>
     </row>
   </sheetData>
@@ -5828,161 +5828,161 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.12726882859701</v>
+        <v>10.74308755760369</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.792492030247196</v>
+        <v>9.068609293328386</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.803748343535055</v>
+        <v>10.67105804857966</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.192243599454628</v>
+        <v>7.221512992628583</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.65355457618273</v>
+        <v>12.66024056681496</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.84052076228011</v>
+        <v>12.81717417281305</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.06857207838976</v>
+        <v>12.02209216058033</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.993259184361307</v>
+        <v>6.002886002885994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.034746366276011</v>
+        <v>6.130814912570102</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.711106052558357</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.98516569472028</v>
+        <v>7.035569860526536</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.706416291272284</v>
+        <v>6.758987906055239</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.931080311372703</v>
+        <v>9.929810074318745</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.710001434926113</v>
+        <v>9.681576012885635</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>8.051858137345555</v>
+        <v>8.99942163100058</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>8.132154221248811</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>7.063052559992215</v>
+        <v>8.028273809523803</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>7.895389704362202</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.72482787477653</v>
+        <v>6.681280502936545</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>4.462398322425706</v>
+        <v>5.467295519424113</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>3.919852154459676</v>
+        <v>4.899851018043378</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>8.191832280007112</v>
+        <v>9.110402781802371</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>1.219930180894963</v>
+        <v>2.21118012422361</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>5.491924014628204</v>
+        <v>6.334755415648424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.1262</t>
+          <t>X &lt; -0.1261</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>98</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.624459009017016</v>
+        <v>9.722679394338385</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.248865884136585</v>
+        <v>7.435956232103898</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.892479488166821</v>
+        <v>10.26289478327354</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.057076489132243</v>
+        <v>3.548043604873484</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.843734996176806</v>
+        <v>9.394934444365987</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.010293019008884</v>
+        <v>8.531459887098769</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.279160661649136</v>
+        <v>9.777194201396654</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.87850023730423</v>
+        <v>3.349824778396204</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.919987419218934</v>
+        <v>3.477753688080313</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.167479906447745</v>
+        <v>3.702110356126276</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.502764038405594</v>
+        <v>7.035569860526536</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5.203606471692289</v>
+        <v>5.738579742789931</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.1824852211627</v>
+        <v>9.725728441665687</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.940998181450794</v>
+        <v>8.457086216967262</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>7.282854883870236</v>
+        <v>7.774931835082207</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.836425479282624</v>
+        <v>6.295419527371266</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>5.702508342305151</v>
+        <v>6.191539115646258</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>6.618075801749271</v>
+        <v>7.079063173749958</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>5.813559019408295</v>
+        <v>6.27311723763043</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.939180339580403</v>
+        <v>3.426479192893495</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.396634171614373</v>
+        <v>2.859034691512761</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>5.382012700001191</v>
+        <v>5.845096659353395</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.5544465961567155</v>
+        <v>0.9866903283052437</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>3.539838832729359</v>
+        <v>3.885775823811699</v>
       </c>
     </row>
     <row r="8">
@@ -5995,2290 +5995,2290 @@
         <v>129</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.47543195633548</v>
+        <v>11.57365234165685</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.48949236728798</v>
+        <v>6.676582715255293</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.02821750430351</v>
+        <v>12.39863279941023</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.214488291062324</v>
+        <v>8.705455406803566</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.20427921386387</v>
+        <v>10.75547866205305</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.616051601511643</v>
+        <v>10.13721846960153</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12.72007190986935</v>
+        <v>13.21810544961687</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.015503875969003</v>
+        <v>7.486828417060977</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.832184856333313</v>
+        <v>8.389951125194692</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.658910217807581</v>
+        <v>10.19171603992852</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.05457941901075</v>
+        <v>7.589552690108391</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.807386344402694</v>
+        <v>10.35062956490568</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.035919871056876</v>
+        <v>8.552007906573344</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>7.377776573476318</v>
+        <v>7.869853524688288</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>4.871388301620868</v>
+        <v>5.33038234970951</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.287858761542608</v>
+        <v>6.776889534883715</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>6.183018057721426</v>
+        <v>6.644005429722114</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.073328043296918</v>
+        <v>4.532886261519053</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.15939865946649</v>
+        <v>1.646697512779582</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.6168524915004596</v>
+        <v>1.079253011398848</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>3.641781723889814</v>
+        <v>4.104865683242018</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.04028744412379837</v>
+        <v>0.4725311762723265</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.065230384698978</v>
+        <v>3.411167375781318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1028</t>
+          <t>X &lt; -0.1029</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>169</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10.85619430668637</v>
+        <v>10.95441469200774</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.70484946099928</v>
+        <v>11.8919398089666</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.63369431729374</v>
+        <v>13.00410961240046</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.962160416194195</v>
+        <v>9.453127531935436</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.218085919978279</v>
+        <v>9.769285368167459</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.8133361297443</v>
+        <v>9.334502997834186</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>12.77511525650484</v>
+        <v>13.27314879625236</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.763176001100874</v>
+        <v>8.234500542192848</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.804663183015577</v>
+        <v>8.362429451876956</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.623463483310445</v>
+        <v>8.158093932988976</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.48923910180374</v>
+        <v>9.022044923924682</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.435341769361642</v>
+        <v>6.970315040459283</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.862475560493699</v>
+        <v>9.405718780996686</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>8.049680707715751</v>
+        <v>8.565768743232219</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>7.391537410135193</v>
+        <v>7.883614361347163</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>5.027344450421367</v>
+        <v>5.486338498510008</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.668575242437996</v>
+        <v>7.157606015779102</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>7.747166491279529</v>
+        <v>8.208153863280216</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>6.187909943209768</v>
+        <v>6.647468161431902</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.824459895189626</v>
+        <v>3.311758748502719</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.281913727223596</v>
+        <v>2.744314247121984</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>3.981215694808583</v>
+        <v>4.444299654160787</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.888826501965191</v>
+        <v>2.321070234113719</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>3.588142177735996</v>
+        <v>3.934079168818336</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.09116</t>
+          <t>X &lt; -0.09124</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.975975316474567</v>
+        <v>9.074195701795936</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10.97764711625561</v>
+        <v>11.16473746422292</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>12.34336638498163</v>
+        <v>12.71378168008835</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.826674047781879</v>
+        <v>9.31764116352312</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.490883575234605</v>
+        <v>9.042083023423785</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.743270322079638</v>
+        <v>8.264437190169524</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11.64421883445097</v>
+        <v>12.14225237419849</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.627689632688558</v>
+        <v>8.099014173780532</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.734597375350916</v>
+        <v>7.292363644212294</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.896261138566771</v>
+        <v>7.430891588245302</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.235741341476349</v>
+        <v>6.76854716359729</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.68596390064517</v>
+        <v>3.220937171742811</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.833829871172235</v>
+        <v>5.377073091675221</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.612750994725644</v>
+        <v>5.128839030242112</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3.954607697145086</v>
+        <v>4.446684648357056</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>2.212546020957234</v>
+        <v>2.671540069045875</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.837700447316173</v>
+        <v>3.03494937694704</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>5.385884812145889</v>
+        <v>5.238513869916275</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.714983740240022</v>
+        <v>3.583817218557371</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.071640870962767</v>
+        <v>0.994665345859346</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.529094702996737</v>
+        <v>0.4272208444786116</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.868343081210277</v>
+        <v>1.753927481401838</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.671119680484779</v>
+        <v>1.530272247054043</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.5386836536766</v>
+        <v>2.302712692016918</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.0795</t>
+          <t>X &lt; -0.07961</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.089780192841104</v>
+        <v>9.188000578162473</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.07603660482339</v>
+        <v>12.2631269527907</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.7450286259031</v>
+        <v>12.11544392100982</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.080045086165143</v>
+        <v>8.571012201906385</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.113258303654774</v>
+        <v>8.664457751843955</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.086202349530751</v>
+        <v>6.607369217620636</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.742297946083205</v>
+        <v>10.24033148583072</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.881060671071822</v>
+        <v>7.352385212163796</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.815536782875832</v>
+        <v>6.37330305173721</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.67361741680245</v>
+        <v>5.208247866480981</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.20966967889057</v>
+        <v>4.742475501011512</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.085901825258063</v>
+        <v>2.620875096355704</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.283772968734048</v>
+        <v>4.827016189237035</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.431697782324363</v>
+        <v>4.947785817840831</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3.4045507947069</v>
+        <v>3.89662774591887</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.415911886391591</v>
+        <v>1.874905934480232</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.729719226658887</v>
+        <v>3.985047662976626</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>4.232065635601025</v>
+        <v>4.221167247851923</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.589220957045804</v>
+        <v>2.590611024813199</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.9173307075342834</v>
+        <v>0.9601790196876792</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.003037327672338108</v>
+        <v>0.02373082827003969</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.6706857900550531</v>
+        <v>0.6865756863885579</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.5734132906412057</v>
+        <v>0.5612064816300375</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.8693282493138312</v>
+        <v>0.7680711773774718</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.06783</t>
+          <t>X &lt; -0.06797</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.061855589270742</v>
+        <v>8.752455239102517</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.267619331461461</v>
+        <v>9.052996490830346</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.721492174322357</v>
+        <v>10.25731878238138</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.765294911636381</v>
+        <v>6.113004015267151</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.051126060710722</v>
+        <v>7.476790137462899</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.535389544105406</v>
+        <v>4.901483306302509</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.736413833188031</v>
+        <v>7.111865774944114</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.566310496543061</v>
+        <v>5.167601069240412</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.986176056836136</v>
+        <v>3.656185716629437</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.753800921340193</v>
+        <v>3.406582308841791</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.298130833772383</v>
+        <v>3.952041367161975</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2238618129188552</v>
+        <v>0.3967708881005052</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.355678822927736</v>
+        <v>2.014119207808207</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.675140487021679</v>
+        <v>2.039109190090947</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.4764566489005873</v>
+        <v>0.8105067207741996</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.8253626521621626</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.456006489531525</v>
+        <v>2.634050546448087</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>3.063284319939157</v>
+        <v>3.047614528718178</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.377001787820014</v>
+        <v>1.349508449853026</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.2051519456141264</v>
+        <v>0.1979746763327697</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.8808724832214736</v>
+        <v>-0.9159179124796566</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.4132401837610047</v>
+        <v>-0.4446323470032496</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.4105046017137468</v>
+        <v>-0.4742219054407215</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.6006196668021175</v>
+        <v>0.4565352751332057</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.05617</t>
+          <t>X &lt; -0.05634</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>498</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.959152886568035</v>
+        <v>10.18482818170904</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8.224376088218222</v>
+        <v>8.536115734782719</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9.586357039187227</v>
+        <v>9.886632053732832</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.873403019744487</v>
+        <v>6.488618632479714</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.937612547197212</v>
+        <v>7.415465301999618</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.924578733294588</v>
+        <v>3.363982074330373</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.952630049404242</v>
+        <v>5.374511284542535</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.474418604651163</v>
+        <v>3.867186031514692</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.915905786565865</v>
+        <v>3.393912536389173</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.342990110529378</v>
+        <v>3.800265850789067</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.0170497526913</v>
+        <v>3.471298460583796</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.7383003492433033</v>
+        <v>1.190708490080432</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.215138282387187</v>
+        <v>2.681026793471332</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.394059405940595</v>
+        <v>2.833594335244634</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.335916108360038</v>
+        <v>1.750638350153167</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1303030303030255</v>
+        <v>0.5083351545439783</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2.520634390319543</v>
+        <v>2.933609437751009</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>3.343754024845737</v>
+        <v>3.603938183995027</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.756432554364444</v>
+        <v>2.81438434688377</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.7344430229670138</v>
+        <v>0.8201354505772898</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.008906357850428037</v>
+        <v>0.05188773634514376</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.5176573192946847</v>
+        <v>0.5791348529440867</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.1897223932225245</v>
+        <v>0.2203596996682364</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.3146933528506608</v>
+        <v>0.2590239182301843</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.04451</t>
+          <t>X &lt; -0.04471</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.76092541241737</v>
+        <v>11.05914318339382</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.062780814953818</v>
+        <v>8.453354341790252</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>9.874392489704213</v>
+        <v>10.29600537264204</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.650360183703135</v>
+        <v>7.048735917196645</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.757701173489686</v>
+        <v>7.068163027834778</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.104194686027235</v>
+        <v>3.537780999614569</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.66164038913837</v>
+        <v>4.217625241069165</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.531139431829899</v>
+        <v>4.060197423029273</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.98178466396616</v>
+        <v>3.450663205869731</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.947421425152719</v>
+        <v>3.097089586756589</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.369191554759254</v>
+        <v>3.51681722672965</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.465626789420561</v>
+        <v>1.47032376783357</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.705832521678175</v>
+        <v>3.010298907019973</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.780174620120803</v>
+        <v>2.90955747095559</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.712873272318689</v>
+        <v>2.817373590545458</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.125576294704807</v>
+        <v>2.198736606415274</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.4141373726155</v>
+        <v>3.514663343180693</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>3.698952596911788</v>
+        <v>3.770284040795005</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.877806940799069</v>
+        <v>3.189217010873058</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.17576386187821</v>
+        <v>2.457545625401217</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.188773249467729</v>
+        <v>1.444997266453719</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.261075436206788</v>
+        <v>1.518202697020691</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.091105704244391</v>
+        <v>1.316733324732304</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.7189771547248185</v>
+        <v>0.8578584253983266</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.03284</t>
+          <t>X &lt; -0.03307</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>10.323116850532</v>
+        <v>10.29665898617511</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.835186899029033</v>
+        <v>7.483787864756962</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.311582264412451</v>
+        <v>7.903200905722521</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.346375992717455</v>
+        <v>4.74383442120002</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.573648583233251</v>
+        <v>4.914704852529255</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.382236390952251</v>
+        <v>1.946638458527339</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.736413833188024</v>
+        <v>2.156020732008898</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.458202388434948</v>
+        <v>1.851100288600279</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.499689570349652</v>
+        <v>1.755814912570109</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.289836957376224</v>
+        <v>1.406191988779341</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.901734437375985</v>
+        <v>2.013248431955105</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.510372421315374</v>
+        <v>1.625059334626656</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.189012156261064</v>
+        <v>2.295881502890175</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.855320667201852</v>
+        <v>1.936040298599927</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.760240432684363</v>
+        <v>1.923528773857718</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.678951678951684</v>
+        <v>1.883151826995018</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.966848125569072</v>
+        <v>3.301524049217001</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.722696431039367</v>
+        <v>3.798445215480427</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.445289677773332</v>
+        <v>3.41094097699164</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.954169386046445</v>
+        <v>2.909976295438213</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.185634517515446</v>
+        <v>2.187170440194251</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>2.335777256671314</v>
+        <v>2.336727019362563</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>2.723246319435859</v>
+        <v>2.76236122658581</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.421425365647615</v>
+        <v>2.557406638299653</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02118</t>
+          <t>X &lt; -0.02144</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>8.730286907186589</v>
+        <v>8.914711155848444</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>7.106850315022349</v>
+        <v>7.474265070997816</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>6.527937795200977</v>
+        <v>6.987489057843433</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.92494941149706</v>
+        <v>4.347305289069347</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.932801550633634</v>
+        <v>4.498368309379565</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.71426945494408</v>
+        <v>2.095574952920309</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.285963382737577</v>
+        <v>1.727114101097143</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.007751937984501</v>
+        <v>1.336869425606622</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.306971078662094</v>
+        <v>1.635446799454556</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.650893890598105</v>
+        <v>1.863286089218143</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.612238756127724</v>
+        <v>2.903439192559688</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.903936088074921</v>
+        <v>2.200236077678831</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.155344467954201</v>
+        <v>2.502702595973005</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.535640161954348</v>
+        <v>2.852248210030936</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.446664173708285</v>
+        <v>2.597079310639472</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.66455432118083</v>
+        <v>2.784168873263468</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.531614144832886</v>
+        <v>3.588581765041347</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.084648637780241</v>
+        <v>4.108696945066704</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.665331307270804</v>
+        <v>3.606240718385202</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.90308307064695</v>
+        <v>2.931152417243268</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.619380733569606</v>
+        <v>2.674222569238957</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.974941156975014</v>
+        <v>3.114081506511148</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.508259700345754</v>
+        <v>3.497385327954582</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.742177231419284</v>
+        <v>2.873264198353255</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.009514</t>
+          <t>X &lt; -0.009805</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1502</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>7.061604841505073</v>
+        <v>7.183445879150128</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.600254153161885</v>
+        <v>5.683413630905008</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.891194680008965</v>
+        <v>4.824759132973824</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.250473927630509</v>
+        <v>3.242257924264614</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.179759664493432</v>
+        <v>3.362739388125675</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.577461437071925</v>
+        <v>1.803501376962032</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.534472329059646</v>
+        <v>1.839038754277254</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.029856270433662</v>
+        <v>1.269917518266261</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.844638367853193</v>
+        <v>1.001545239046798</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.465219705751679</v>
+        <v>1.460447508688759</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.871993349240739</v>
+        <v>1.930833117744875</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.593243945792743</v>
+        <v>1.588200965122979</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.797221892208022</v>
+        <v>1.834257246446029</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.775214017752148</v>
+        <v>1.758295589605218</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.755305218585804</v>
+        <v>1.711910994714295</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.992097050236588</v>
+        <v>1.916449396272469</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>2.497449723112787</v>
+        <v>2.383097249834321</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.899662288639441</v>
+        <v>2.688872084051489</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.558035771493948</v>
+        <v>2.34722040245309</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.812791035523233</v>
+        <v>1.606548033178612</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.669712244388087</v>
+        <v>1.544369290468616</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.793599971394435</v>
+        <v>1.709186976331246</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.334386268430414</v>
+        <v>2.193121004368081</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.459619261545356</v>
+        <v>1.47266677193528</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.00215</t>
+          <t>X &lt; 0.001829</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.630626905656051</v>
+        <v>4.615268008731512</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.712605144421829</v>
+        <v>3.926053060724762</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.653165098572174</v>
+        <v>3.702820806369822</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.834166540423169</v>
+        <v>2.89967045160796</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.60442060658216</v>
+        <v>2.782173428473861</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.094674173379424</v>
+        <v>1.305808825831264</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.277126337845381</v>
+        <v>1.38424292494512</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8707050767997089</v>
+        <v>1.079322481536501</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7838463385828547</v>
+        <v>0.9213513803217666</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.444051681654649</v>
+        <v>1.474982037780471</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.505797098763495</v>
+        <v>1.567173420641176</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.386283364105303</v>
+        <v>1.480141026574437</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.377770978777853</v>
+        <v>1.559227168852118</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9974564335414442</v>
+        <v>1.237064416602493</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.380419560298435</v>
+        <v>1.644924276503225</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.422970405435869</v>
+        <v>1.65631666547479</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.853057876313336</v>
+        <v>2.061264124293785</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.887289870355438</v>
+        <v>2.066787993407551</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.497324808853399</v>
+        <v>1.730515467335884</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.098752843408967</v>
+        <v>1.393782825221756</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.6626462709724734</v>
+        <v>1.070612316193206</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.9061190961519827</v>
+        <v>1.399303472190049</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.9677146175749698</v>
+        <v>1.409601256757391</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.7854427688221506</v>
+        <v>1.173367096365375</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.01381</t>
+          <t>X &lt; 0.01346</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2207</v>
+        <v>2212</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.256264799925432</v>
+        <v>4.234154984126071</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.180132295893166</v>
+        <v>3.251825180580148</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.051368325868943</v>
+        <v>3.099437206433926</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.157827398976991</v>
+        <v>2.148129668908794</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.776890199567418</v>
+        <v>1.827708361469838</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9254816678318392</v>
+        <v>0.8181996166379619</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.462788062948263</v>
+        <v>1.484774899744224</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.165836852166983</v>
+        <v>1.179854456335605</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.9626296907683027</v>
+        <v>0.9746150280361405</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.635714918482378</v>
+        <v>1.686964675212401</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.548274334706669</v>
+        <v>1.626260069194259</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.314712459500875</v>
+        <v>1.42111534695966</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.366426126942088</v>
+        <v>1.502331120524005</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9194096092844717</v>
+        <v>1.101146541367058</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.418737084851898</v>
+        <v>1.571622055519782</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.543419267299868</v>
+        <v>1.710017799112393</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.934847431787098</v>
+        <v>2.129220181763557</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.993672849078841</v>
+        <v>2.114119576834184</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.784610483472186</v>
+        <v>1.950305568984625</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.790296873150353</v>
+        <v>2.011906143457111</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.45667504342299</v>
+        <v>1.652511450162038</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.562070586318377</v>
+        <v>1.830753794836312</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.428751914115338</v>
+        <v>1.740584294386927</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.352919660892063</v>
+        <v>1.696419068451327</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.02548</t>
+          <t>X &lt; 0.0251</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2480</v>
+        <v>2490</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.306944051226665</v>
+        <v>3.128022415656829</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.271865039604322</v>
+        <v>2.267243328615805</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.878442213956205</v>
+        <v>1.911734470603236</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.366372083625556</v>
+        <v>1.359188788335473</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.990404833255873</v>
+        <v>1.026611038448593</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.5345425741945462</v>
+        <v>0.4483782300242822</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8473668915095089</v>
+        <v>0.8329461110990835</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3512674792492376</v>
+        <v>0.3285045184486464</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3355278211456891</v>
+        <v>0.3595003987406216</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.090557460750532</v>
+        <v>1.103818643275005</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.042944404882697</v>
+        <v>1.079859570017994</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9652404377032937</v>
+        <v>0.9864630687822</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6462601159215708</v>
+        <v>0.6946469966926543</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6664357629972884</v>
+        <v>0.7501474414570666</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.078313533943302</v>
+        <v>1.172290778659644</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.9327175172245603</v>
+        <v>0.997303483515779</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.346466408623471</v>
+        <v>1.39803180483247</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.266172656278442</v>
+        <v>1.369519740992246</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.023149704997593</v>
+        <v>1.167395590254038</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.911936552101686</v>
+        <v>1.12544651037382</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.8372200833984351</v>
+        <v>1.063394654511193</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.043632186505462</v>
+        <v>1.333516746489373</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.7132681893101065</v>
+        <v>1.039533625399272</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.5567907747965037</v>
+        <v>0.9015941993546832</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.03714</t>
+          <t>X &lt; 0.03673</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2674</v>
+        <v>2678</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.523026257145311</v>
+        <v>2.420336234852364</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.687565357964871</v>
+        <v>1.639402708879125</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.441796681512116</v>
+        <v>1.331864995524491</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9151317827847194</v>
+        <v>0.813591781149178</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.2812787170928885</v>
+        <v>0.262338135542123</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1651381072419156</v>
+        <v>-0.264640155292085</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1061322848736879</v>
+        <v>0.03693446113691579</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1880487826019106</v>
+        <v>-0.2098619025122446</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.01340070112988201</v>
+        <v>0.0133675622969065</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.5559655020282577</v>
+        <v>0.5385418083505584</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7554539286793727</v>
+        <v>0.8323527877442416</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.5358385812462956</v>
+        <v>0.5773628396718067</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3078648769414585</v>
+        <v>0.3766038903948257</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2732835760263868</v>
+        <v>0.3735402985999272</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6821847650764568</v>
+        <v>0.829928303338292</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.4780447249652156</v>
+        <v>0.5946582101861608</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.627901950084329</v>
+        <v>0.7364408752327734</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.6949818723583121</v>
+        <v>0.8494029042770421</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5223842535378225</v>
+        <v>0.7135471554044699</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.3578337822658924</v>
+        <v>0.6148399958276443</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.4733517696483531</v>
+        <v>0.7036555685842174</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.5844915973192855</v>
+        <v>0.9121085387320136</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2606117847452367</v>
+        <v>0.6556956684032045</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.2595738471539732</v>
+        <v>0.6279379612581621</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0488</t>
+          <t>X &lt; 0.04836</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2831</v>
+        <v>2842</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.949870186146093</v>
+        <v>1.869384445073763</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.493950481464786</v>
+        <v>1.468190152566947</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.181503011751424</v>
+        <v>1.106318106481233</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6795936634307367</v>
+        <v>0.5837971096296855</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1327585197614098</v>
+        <v>0.1181723588956558</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1023646363853246</v>
+        <v>-0.1948138391749552</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.04021358791989371</v>
+        <v>0.008900735006953653</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1475377641032338</v>
+        <v>-0.1712617527873022</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.266064181497228</v>
+        <v>0.2915229479718775</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4787169672699676</v>
+        <v>0.4958278431210772</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6325427104377894</v>
+        <v>0.6482793926756401</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3391457173306591</v>
+        <v>0.3219071171874859</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1879360272779564</v>
+        <v>0.1736636620209211</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1430375595699189</v>
+        <v>0.1914938650194742</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.5280909409296513</v>
+        <v>0.5823248729708226</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.2623199555498559</v>
+        <v>0.2875426924267543</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.3258391561121528</v>
+        <v>0.3097760910260945</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.3480024936680977</v>
+        <v>0.4084314379095559</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.2674083318123905</v>
+        <v>0.3628500749170769</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.1575592165549224</v>
+        <v>0.3172101866261983</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.2365119100640385</v>
+        <v>0.4383898079002648</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.1606659486549376</v>
+        <v>0.4194242806972923</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.1172317950119535</v>
+        <v>0.4027282876324847</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.1826923711775876</v>
+        <v>0.4726864501311852</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.06047</t>
+          <t>X &lt; 0.06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2942</v>
+        <v>2956</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.670384280343406</v>
+        <v>1.610109089277792</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.286643431703837</v>
+        <v>1.281983561773181</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.931534704161848</v>
+        <v>0.9191505674145404</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3201035273586967</v>
+        <v>0.2783486301093774</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.08583589745102671</v>
+        <v>0.08881199538640061</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.268653077196106</v>
+        <v>-0.3406700004985126</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1607371248766398</v>
+        <v>-0.1753034475115456</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3858386736155879</v>
+        <v>-0.3939607573524242</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.01356917972537275</v>
+        <v>0.05590026141849336</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1549779195371741</v>
+        <v>0.1880582706456195</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2116296984907677</v>
+        <v>0.2439613343272384</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.1152408232405904</v>
+        <v>-0.08063473545419697</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1679125650704378</v>
+        <v>-0.1313387532608203</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.199429912472425</v>
+        <v>-0.1575531654208859</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.07838557918771727</v>
+        <v>0.124451744226306</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.01452427224398889</v>
+        <v>0.03113243601649884</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.09920134360586985</v>
+        <v>-0.08657118348520498</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.1838368138912116</v>
+        <v>-0.1320049131742067</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.2194656034843447</v>
+        <v>-0.1339846102009048</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.3182898248360289</v>
+        <v>-0.2035539014253089</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2289571934156669</v>
+        <v>-0.07528536973242694</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.2708126721599129</v>
+        <v>-0.06278373418333416</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.3362427863264017</v>
+        <v>-0.1034244460454872</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.2761131088902502</v>
+        <v>-0.0425884853761147</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.07213</t>
+          <t>X &lt; 0.07163</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3027</v>
+        <v>3041</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.107756238523336</v>
+        <v>1.059200948129615</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.15258121642335</v>
+        <v>1.157597680064079</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.8979941200550741</v>
+        <v>0.9005998979778198</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3165325397970804</v>
+        <v>0.3264740231041614</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1451076162307459</v>
+        <v>0.1999231064975078</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1281497348184857</v>
+        <v>-0.1805374976675012</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3083824423774857</v>
+        <v>-0.2707229379901648</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.4364002049509352</v>
+        <v>-0.3936745840573153</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.04725210817098002</v>
+        <v>0.04723226485132415</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.01160021523567423</v>
+        <v>0.05536196773654467</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.05115113517977932</v>
+        <v>0.1172426082110647</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2414823310332821</v>
+        <v>-0.1733035169011146</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2915810852017415</v>
+        <v>-0.2209107644754909</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.2955616813740676</v>
+        <v>-0.2205638007586046</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.1102275963202501</v>
+        <v>-0.03102333387061407</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1554866169109488</v>
+        <v>-0.1061440498470887</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.2038779589171895</v>
+        <v>-0.1578904199475133</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.3221136689581812</v>
+        <v>-0.2386062635687836</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.284642637492091</v>
+        <v>-0.1689211667004429</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.342363377279078</v>
+        <v>-0.1977291111177735</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.4361105511095928</v>
+        <v>-0.2531431625460741</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.4459063143681021</v>
+        <v>-0.2102863877201813</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.4686574935637182</v>
+        <v>-0.210159220192665</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.4588666950714568</v>
+        <v>-0.2213586445761209</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0838</t>
+          <t>X &lt; 0.08326</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3093</v>
+        <v>3109</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.117995330297937</v>
+        <v>1.087002901519028</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.8008315401320161</v>
+        <v>0.8585440471724368</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4885764023265011</v>
+        <v>0.5158777656038609</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1937632641960789</v>
+        <v>0.1969044915100184</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.004794014378681766</v>
+        <v>0.03510355548869626</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1299901212742611</v>
+        <v>-0.1098668066743613</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3227882260140333</v>
+        <v>-0.3113325720766511</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4861864806401144</v>
+        <v>-0.4702568542568599</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.1044419275358663</v>
+        <v>-0.06819734278017364</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.05378927755435825</v>
+        <v>-0.04559429730089448</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.01877498957674106</v>
+        <v>-0.01119503377199749</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1177744171118391</v>
+        <v>-0.1412729993322301</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1584271592633613</v>
+        <v>-0.1800800355713577</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1992330803541407</v>
+        <v>-0.2172010676804774</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.000432237392296031</v>
+        <v>-0.014598345174619</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.1279738332013309</v>
+        <v>-0.107911776276282</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.2750150104833509</v>
+        <v>-0.2570737056054782</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.2961202932208451</v>
+        <v>-0.2426520291851375</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.3194368145842148</v>
+        <v>-0.2340328285617588</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3396433061945459</v>
+        <v>-0.2254216573920118</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.3460013441303857</v>
+        <v>-0.1956319052030437</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.3895266849835721</v>
+        <v>-0.1874803058589194</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4382581780606642</v>
+        <v>-0.2141758702642207</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.4302846191732286</v>
+        <v>-0.2608426177109422</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.09546</t>
+          <t>X &lt; 0.0949</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3151</v>
+        <v>3168</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.168361338160594</v>
+        <v>1.142424979817946</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.9455117349059208</v>
+        <v>0.9763567183171915</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.6431393735720832</v>
+        <v>0.6795694493770483</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2949871156737984</v>
+        <v>0.2928519422611373</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.07170345628811958</v>
+        <v>0.09759768725962203</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1832495495336985</v>
+        <v>-0.1986988430599652</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.3554507586765681</v>
+        <v>-0.3797916698749333</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5210345055477603</v>
+        <v>-0.5728498190809788</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1457492987152449</v>
+        <v>-0.1444869140983513</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.07912679310410908</v>
+        <v>-0.07423361955325447</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.007981852871274953</v>
+        <v>-0.003995415442396677</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.1103876052302866</v>
+        <v>-0.1367892727408133</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.1083278782706216</v>
+        <v>-0.1011969809097693</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1525397715348831</v>
+        <v>-0.1422125333698716</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.0007927523994553098</v>
+        <v>0.01250675173443483</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.1471265360154277</v>
+        <v>-0.1316097226158917</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.2622588185173811</v>
+        <v>-0.2169455380577432</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.2849514845532752</v>
+        <v>-0.2052494170708599</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.240345432106146</v>
+        <v>-0.1297590720488131</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.2565892519329012</v>
+        <v>-0.1488096868450413</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.273121111602272</v>
+        <v>-0.09857219230037373</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.2349248457116673</v>
+        <v>-0.02884913347478602</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.322223868983663</v>
+        <v>-0.1135730651556486</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.3157560869268679</v>
+        <v>-0.1307929248999145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.1071</t>
+          <t>X &lt; 0.1065</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3200</v>
+        <v>3218</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.8001466753879143</v>
+        <v>0.7924550367767864</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6065444634900388</v>
+        <v>0.6250466830991144</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.31795070181537</v>
+        <v>0.3442376013516864</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2127442254623304</v>
+        <v>0.2013065159675094</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.04336351745929079</v>
+        <v>-0.0261092279685684</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2915853947750406</v>
+        <v>-0.2536363516439479</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3174973985286158</v>
+        <v>-0.3515002439239794</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5158799028115197</v>
+        <v>-0.5153576582148034</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2078889257202832</v>
+        <v>-0.1225543596670917</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1229713082634092</v>
+        <v>-0.06569627147525381</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.04874545428037891</v>
+        <v>-0.0232796774316455</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3095203232349064</v>
+        <v>-0.251184583993421</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1066929228448288</v>
+        <v>-0.07859588949137475</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2159094414114335</v>
+        <v>-0.1847720133136832</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.1077111898637071</v>
+        <v>-0.07402119515374039</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.180420161716917</v>
+        <v>-0.176232989804241</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3893952105098037</v>
+        <v>-0.3548934108527178</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.2886170063783453</v>
+        <v>-0.2214128479242135</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.2725946308193414</v>
+        <v>-0.1747985715725662</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3793755471937814</v>
+        <v>-0.2523107588413893</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3103305999327048</v>
+        <v>-0.1496012372455766</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.3051216165611663</v>
+        <v>-0.1131997026696752</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.3869046397453317</v>
+        <v>-0.1928495211853445</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.4129672897196244</v>
+        <v>-0.2434209139262862</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.1188</t>
+          <t>X &lt; 0.1182</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3229</v>
+        <v>3248</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.8066752011263603</v>
+        <v>0.8138391844543662</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.6733908665433432</v>
+        <v>0.6762982404668776</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4361107337685084</v>
+        <v>0.417157773266112</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3255126594118707</v>
+        <v>0.3007226446656617</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1919563549606096</v>
+        <v>0.1647226167515612</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1447989623307961</v>
+        <v>-0.1816885688543479</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.2081832592833734</v>
+        <v>-0.2553088457640129</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4380621349482112</v>
+        <v>-0.4817078346490149</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1940818829778976</v>
+        <v>-0.1832694094823424</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1476666887305598</v>
+        <v>-0.1649300222568328</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1333512343537322</v>
+        <v>-0.1510950538292803</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3017490182358671</v>
+        <v>-0.2874625759780685</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2033802361313306</v>
+        <v>-0.1881051494571722</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.2827544254888466</v>
+        <v>-0.295622969838206</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.1814402844750376</v>
+        <v>-0.1615064798814814</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1864099755665976</v>
+        <v>-0.1962066071120177</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.3020071845483585</v>
+        <v>-0.3127400153609869</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.2030452278062853</v>
+        <v>-0.1817022264482233</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.2161255817048868</v>
+        <v>-0.1642686604730557</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.3511862246140964</v>
+        <v>-0.2698332804353285</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.2876202232128691</v>
+        <v>-0.1733132830507884</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.2212313831473907</v>
+        <v>-0.07641040501081875</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.2688300829359775</v>
+        <v>-0.1222851178288877</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.3262724925688048</v>
+        <v>-0.2046534513466511</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.1305</t>
+          <t>X &lt; 0.1298</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3257</v>
+        <v>3280</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.6134987237134979</v>
+        <v>0.5899799930519833</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4478050082914322</v>
+        <v>0.481605745694921</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.199535806728413</v>
+        <v>0.2127553697377493</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1443825742150437</v>
+        <v>0.1219458930614934</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.06996907955374354</v>
+        <v>0.1057868362472618</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1532838621252566</v>
+        <v>-0.1447941196585774</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.236129877290935</v>
+        <v>-0.2557361682034127</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.435877759540702</v>
+        <v>-0.4525578251306399</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2853167073216554</v>
+        <v>-0.2771625424483162</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.245942937468179</v>
+        <v>-0.2667631677823792</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.2294334277368293</v>
+        <v>-0.2504480996487359</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3070346155777415</v>
+        <v>-0.3274554197562622</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2497331986409677</v>
+        <v>-0.2703027875990429</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.2997269423912101</v>
+        <v>-0.3184239871143575</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.2049289620624961</v>
+        <v>-0.2226606345599436</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.2047658824075427</v>
+        <v>-0.2211652087129465</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3205258713803261</v>
+        <v>-0.3375830291045574</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.2233184329289628</v>
+        <v>-0.2091229467116165</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.234439579172772</v>
+        <v>-0.1897784229168948</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.3667418453009077</v>
+        <v>-0.2922311901635055</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.3390613335815686</v>
+        <v>-0.2326497434552621</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.2739103012950608</v>
+        <v>-0.1374426086389917</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.318757197331216</v>
+        <v>-0.1805123040430345</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.3763730311995133</v>
+        <v>-0.263676640100698</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.1421</t>
+          <t>X &lt; 0.1414</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3275</v>
+        <v>3300</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.5131856336874989</v>
+        <v>0.5049206688198851</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.3768177018063312</v>
+        <v>0.3956928058423586</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2295609226823672</v>
+        <v>0.241325179822411</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.1101253262695181</v>
+        <v>0.117382183678501</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.06463136929800584</v>
+        <v>0.09965863594077007</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1563808780020963</v>
+        <v>-0.1484677801706837</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2126190392956318</v>
+        <v>-0.2333882649332537</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3520171291683454</v>
+        <v>-0.370541534594615</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1716322073551098</v>
+        <v>-0.1652419717220752</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1062649822039745</v>
+        <v>-0.129500743352736</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.149130295970501</v>
+        <v>-0.1719675462260923</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2886543206684706</v>
+        <v>-0.3105428047798213</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2073814985014337</v>
+        <v>-0.2302624113351328</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2278584022785779</v>
+        <v>-0.2493691748571294</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.1371654994353264</v>
+        <v>-0.1582867832808148</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.1337237744487183</v>
+        <v>-0.1533873230593485</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.2190924735239221</v>
+        <v>-0.2394699375062999</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.1229625825163509</v>
+        <v>-0.1125612073999633</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1632951368883724</v>
+        <v>-0.1222639102901653</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2328295439704604</v>
+        <v>-0.1622444321497483</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2387457887895508</v>
+        <v>-0.1366958441165664</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2048543324388845</v>
+        <v>-0.0727762438963353</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.2479256347869452</v>
+        <v>-0.1140892746598468</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.275085610330315</v>
+        <v>-0.1674090865160665</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.1538</t>
+          <t>X &lt; 0.1531</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3296</v>
+        <v>3320</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.3513192017232001</v>
+        <v>0.3610526018325686</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.3040626463857876</v>
+        <v>0.3407303500095864</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1486120889309746</v>
+        <v>0.1797594638958699</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1761774467649957</v>
+        <v>0.2026934887791469</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.06853260752903623</v>
+        <v>0.09360384923485299</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.08954317376635856</v>
+        <v>-0.09218130095225519</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1502978105414314</v>
+        <v>-0.1813412055740429</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2301707673295041</v>
+        <v>-0.2595326336333557</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1412370705769916</v>
+        <v>-0.1446187991454693</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1113905541231901</v>
+        <v>-0.1438551446511127</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.06158427571606495</v>
+        <v>-0.09442885363060327</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.2019656725221068</v>
+        <v>-0.233809212792309</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1585538857410285</v>
+        <v>-0.1907028561611597</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1802902613310238</v>
+        <v>-0.2111738798642619</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.03382670555826905</v>
+        <v>-0.06464737299032208</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.02659769608921891</v>
+        <v>-0.05637599853140074</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.1122426262021463</v>
+        <v>-0.1425364442440653</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.04764318118005662</v>
+        <v>-0.04722690933077445</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.08632289639953683</v>
+        <v>-0.05556160232659835</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1542024680881156</v>
+        <v>-0.09399036677153561</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1635108321282601</v>
+        <v>-0.07199026135131703</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.130295315988711</v>
+        <v>-0.008888522919392017</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.2016520216343523</v>
+        <v>-0.07857769398950154</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2594478722439035</v>
+        <v>-0.1626628287577674</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.1654</t>
+          <t>X &lt; 0.1647</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3311</v>
+        <v>3335</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2283790413370781</v>
+        <v>0.2393863749269229</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1497886294723472</v>
+        <v>0.1882314049075973</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1085659227406524</v>
+        <v>0.14151607684461</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1327845868414528</v>
+        <v>0.1318813128329666</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.03596102637636278</v>
+        <v>0.02202606813535368</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1324353850592743</v>
+        <v>-0.1324232026715961</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1663603352111451</v>
+        <v>-0.1949211363852328</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2471323421477507</v>
+        <v>-0.2741315185361799</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1283515796397836</v>
+        <v>-0.1293130191996141</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1321978593954327</v>
+        <v>-0.161973348421526</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.08138586704396289</v>
+        <v>-0.1115542220814234</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1923045258695453</v>
+        <v>-0.2216770817803564</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1240549746868567</v>
+        <v>-0.1538719340494552</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1165699225749037</v>
+        <v>-0.145457939708848</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.02627755414317789</v>
+        <v>-0.002628949997365737</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.02408082025436187</v>
+        <v>-0.05168407625983917</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1099432205984954</v>
+        <v>-0.1379226511071252</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.01418613011335879</v>
+        <v>0.01622606644370705</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.05348019676068105</v>
+        <v>-0.02102916344497174</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.1201972576123183</v>
+        <v>-0.0583109495785834</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.1319089293918694</v>
+        <v>-0.03894894771884339</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.09917766325548882</v>
+        <v>0.02354118669983762</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.1387654712789512</v>
+        <v>-0.01475341465957314</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.1966240399461441</v>
+        <v>-0.09917047854732886</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.1771</t>
+          <t>X &lt; 0.1763</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3324</v>
+        <v>3348</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2282894267532711</v>
+        <v>0.2396337287271422</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1188172119480484</v>
+        <v>0.1580539732775179</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1020521064518007</v>
+        <v>0.1363508442375547</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.03369010108419701</v>
+        <v>0.06508272455936037</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1357347456535152</v>
+        <v>-0.07513216855777216</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1413698005175021</v>
+        <v>-0.1095722833451731</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2081002708591555</v>
+        <v>-0.2343289814277369</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.319593371396742</v>
+        <v>-0.3144233227467481</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2011352436827138</v>
+        <v>-0.1696820926548241</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2079985054083124</v>
+        <v>-0.2053062690603866</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.186306555369832</v>
+        <v>-0.1837951243844245</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2679346627471091</v>
+        <v>-0.2648216177542935</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2043519724853695</v>
+        <v>-0.2016065888037772</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1977822257330644</v>
+        <v>-0.1942003846298874</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.08808629187998207</v>
+        <v>-0.08436916860791399</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1059514714976828</v>
+        <v>-0.1012869502138116</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1620049802859711</v>
+        <v>-0.157802409339304</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.03878514082595785</v>
+        <v>-0.004772149288022831</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1053600651976083</v>
+        <v>-0.07088173983111545</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1711022349878846</v>
+        <v>-0.1072015825192949</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1849034028383088</v>
+        <v>-0.09013065054169545</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1526124549315</v>
+        <v>-0.02818996873067192</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1909884199549907</v>
+        <v>-0.0654056369844298</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.279017229551151</v>
+        <v>-0.1501396176337053</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.1888</t>
+          <t>X &lt; 0.188</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3339</v>
+        <v>3363</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.3746198705061659</v>
+        <v>0.3557784697630026</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2046795693250374</v>
+        <v>0.2439627434233387</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1518332296634171</v>
+        <v>0.1872687881946646</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.08060754490077926</v>
+        <v>0.1137050453290556</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.02998721456574316</v>
+        <v>0.03204085404990309</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.03473017346739482</v>
+        <v>-0.00151852165604538</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1045809160308053</v>
+        <v>-0.09963226883640175</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2167885488510635</v>
+        <v>-0.2102793461183623</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.128459150822323</v>
+        <v>-0.09518525659169796</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1685517922442514</v>
+        <v>-0.1637771300497093</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1158858081678815</v>
+        <v>-0.1115188327706989</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1983752699748393</v>
+        <v>-0.193393046325717</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1400855982098221</v>
+        <v>-0.1353944307197779</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1643759478963673</v>
+        <v>-0.1587526474845262</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.05811017598882273</v>
+        <v>-0.0524339866913337</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.07322251496138676</v>
+        <v>-0.06676937073321199</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.09972887057163859</v>
+        <v>-0.09381181998021759</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.007408472677980171</v>
+        <v>0.02828204206308982</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.1026112764612535</v>
+        <v>-0.03656815671732971</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1672192648321058</v>
+        <v>-0.07176001963144074</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.183392453039076</v>
+        <v>-0.05728335085569825</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1515865523306914</v>
+        <v>0.004055933999360661</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1885571921849802</v>
+        <v>-0.03189784418135133</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.3064795688451056</v>
+        <v>-0.1764378216821854</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.2004</t>
+          <t>X &lt; 0.1996</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3350</v>
+        <v>3374</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.3467010632653285</v>
+        <v>0.3578737134554899</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2058707501399226</v>
+        <v>0.2456242689299302</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1485047698309572</v>
+        <v>0.1850492120553682</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.104857025679209</v>
+        <v>0.1098032527514903</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.006465814334397635</v>
+        <v>0.02750931339404872</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.04026687240611437</v>
+        <v>-0.03491477597401627</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1124130156388219</v>
+        <v>-0.1352992536674691</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1954566181652382</v>
+        <v>-0.2170887126639371</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.166709369451965</v>
+        <v>-0.13146220246594</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2092096516584903</v>
+        <v>-0.2319426039007126</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1855669585783986</v>
+        <v>-0.1789900112521252</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2092308821665654</v>
+        <v>-0.231983320001639</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1845641871159316</v>
+        <v>-0.1778075665337582</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2095120226308325</v>
+        <v>-0.2019092961315891</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.07599219768342635</v>
+        <v>-0.06860759073836675</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.08911328893461246</v>
+        <v>-0.08107548222334771</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1159763348543663</v>
+        <v>-0.1083721532091104</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.02430701550159142</v>
+        <v>0.01288759109085902</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.118494875174882</v>
+        <v>-0.05105788965635583</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.1822829147732108</v>
+        <v>-0.08544067274370803</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2001874380315769</v>
+        <v>-0.07286356379172787</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1687398205774429</v>
+        <v>-0.01197365692478058</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2046932280809557</v>
+        <v>-0.04702093397744989</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3224822150927551</v>
+        <v>-0.1916227704807909</v>
       </c>
     </row>
   </sheetData>
